--- a/01.Study Plan/02_aspnet_study_plan_v2.xlsx
+++ b/01.Study Plan/02_aspnet_study_plan_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22118" windowHeight="8524" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="22118" windowHeight="8524" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="📚 Study Plan" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="321">
   <si>
     <t>🎯  ASP.NET Core Web API — Complete Study Plan</t>
   </si>
@@ -82,19 +82,22 @@
     <t>1/5</t>
   </si>
   <si>
+    <t>✅ Done</t>
+  </si>
+  <si>
+    <t>HTTP (HyperText Transport Protocol)</t>
+  </si>
+  <si>
+    <t>2/5</t>
+  </si>
+  <si>
+    <t>Creating ASP.NET Core Web API Project using .NET Core CLI</t>
+  </si>
+  <si>
+    <t>3/5</t>
+  </si>
+  <si>
     <t>⬜ Not Started</t>
-  </si>
-  <si>
-    <t>HTTP (HyperText Transport Protocol)</t>
-  </si>
-  <si>
-    <t>2/5</t>
-  </si>
-  <si>
-    <t>Creating ASP.NET Core Web API Project using .NET Core CLI</t>
-  </si>
-  <si>
-    <t>3/5</t>
   </si>
   <si>
     <t>How to Test ASP.NET Core Web API Using Postman</t>
@@ -3389,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="H8" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I8" s="97"/>
     </row>
@@ -3402,7 +3405,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="94" t="s">
         <v>15</v>
@@ -3411,10 +3414,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I9" s="100"/>
     </row>
@@ -3427,7 +3430,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="93" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="94" t="s">
         <v>15</v>
@@ -3436,16 +3439,16 @@
         <v>1</v>
       </c>
       <c r="G10" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I10" s="97"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:9">
       <c r="A11" s="89" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="89"/>
       <c r="C11" s="89"/>
@@ -3465,10 +3468,10 @@
         <v>13</v>
       </c>
       <c r="D12" s="93" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" s="94">
         <v>2</v>
@@ -3477,7 +3480,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I12" s="97"/>
     </row>
@@ -3490,10 +3493,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="94" t="s">
         <v>29</v>
-      </c>
-      <c r="E13" s="94" t="s">
-        <v>28</v>
       </c>
       <c r="F13" s="94">
         <v>2</v>
@@ -3502,7 +3505,7 @@
         <v>19</v>
       </c>
       <c r="H13" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I13" s="100"/>
     </row>
@@ -3515,10 +3518,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="93" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="94">
         <v>2</v>
@@ -3527,7 +3530,7 @@
         <v>21</v>
       </c>
       <c r="H14" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I14" s="97"/>
     </row>
@@ -3540,19 +3543,19 @@
         <v>13</v>
       </c>
       <c r="D15" s="99" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F15" s="94">
         <v>2</v>
       </c>
       <c r="G15" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I15" s="100"/>
     </row>
@@ -3565,25 +3568,25 @@
         <v>13</v>
       </c>
       <c r="D16" s="93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16" s="94">
         <v>2</v>
       </c>
       <c r="G16" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H16" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I16" s="97"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:9">
       <c r="A17" s="89" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="89"/>
       <c r="C17" s="89"/>
@@ -3603,10 +3606,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F18" s="94">
         <v>3</v>
@@ -3615,7 +3618,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I18" s="97"/>
     </row>
@@ -3628,10 +3631,10 @@
         <v>13</v>
       </c>
       <c r="D19" s="99" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="94" t="s">
         <v>36</v>
-      </c>
-      <c r="E19" s="94" t="s">
-        <v>35</v>
       </c>
       <c r="F19" s="94">
         <v>3</v>
@@ -3640,7 +3643,7 @@
         <v>19</v>
       </c>
       <c r="H19" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I19" s="100"/>
     </row>
@@ -3653,10 +3656,10 @@
         <v>13</v>
       </c>
       <c r="D20" s="93" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E20" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" s="94">
         <v>3</v>
@@ -3665,7 +3668,7 @@
         <v>21</v>
       </c>
       <c r="H20" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I20" s="97"/>
     </row>
@@ -3678,19 +3681,19 @@
         <v>13</v>
       </c>
       <c r="D21" s="99" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E21" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F21" s="94">
         <v>3</v>
       </c>
       <c r="G21" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I21" s="100"/>
     </row>
@@ -3703,25 +3706,25 @@
         <v>13</v>
       </c>
       <c r="D22" s="93" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E22" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22" s="94">
         <v>3</v>
       </c>
       <c r="G22" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H22" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I22" s="97"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:9">
       <c r="A23" s="89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" s="89"/>
       <c r="C23" s="89"/>
@@ -3741,10 +3744,10 @@
         <v>13</v>
       </c>
       <c r="D24" s="93" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E24" s="94" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="94">
         <v>4</v>
@@ -3753,7 +3756,7 @@
         <v>16</v>
       </c>
       <c r="H24" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I24" s="97"/>
     </row>
@@ -3766,10 +3769,10 @@
         <v>13</v>
       </c>
       <c r="D25" s="99" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="94" t="s">
         <v>43</v>
-      </c>
-      <c r="E25" s="94" t="s">
-        <v>42</v>
       </c>
       <c r="F25" s="94">
         <v>4</v>
@@ -3778,7 +3781,7 @@
         <v>19</v>
       </c>
       <c r="H25" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I25" s="100"/>
     </row>
@@ -3791,10 +3794,10 @@
         <v>13</v>
       </c>
       <c r="D26" s="93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E26" s="94" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" s="94">
         <v>4</v>
@@ -3803,7 +3806,7 @@
         <v>21</v>
       </c>
       <c r="H26" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I26" s="97"/>
     </row>
@@ -3816,19 +3819,19 @@
         <v>13</v>
       </c>
       <c r="D27" s="99" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E27" s="94" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F27" s="94">
         <v>4</v>
       </c>
       <c r="G27" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I27" s="100"/>
     </row>
@@ -3838,28 +3841,28 @@
         <v>20</v>
       </c>
       <c r="C28" s="92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D28" s="93" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28" s="94" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F28" s="94">
         <v>4</v>
       </c>
       <c r="G28" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H28" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I28" s="97"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:9">
       <c r="A29" s="102" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B29" s="102"/>
       <c r="C29" s="102"/>
@@ -3876,13 +3879,13 @@
         <v>21</v>
       </c>
       <c r="C30" s="92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" s="93" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F30" s="94">
         <v>5</v>
@@ -3891,7 +3894,7 @@
         <v>16</v>
       </c>
       <c r="H30" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I30" s="97"/>
     </row>
@@ -3901,13 +3904,13 @@
         <v>22</v>
       </c>
       <c r="C31" s="92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" s="99" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="94" t="s">
         <v>51</v>
-      </c>
-      <c r="E31" s="94" t="s">
-        <v>50</v>
       </c>
       <c r="F31" s="94">
         <v>5</v>
@@ -3916,7 +3919,7 @@
         <v>19</v>
       </c>
       <c r="H31" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I31" s="100"/>
     </row>
@@ -3926,13 +3929,13 @@
         <v>23</v>
       </c>
       <c r="C32" s="92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D32" s="93" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" s="94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F32" s="94">
         <v>5</v>
@@ -3941,7 +3944,7 @@
         <v>21</v>
       </c>
       <c r="H32" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I32" s="97"/>
     </row>
@@ -3951,22 +3954,22 @@
         <v>24</v>
       </c>
       <c r="C33" s="92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D33" s="99" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E33" s="94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F33" s="94">
         <v>5</v>
       </c>
       <c r="G33" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H33" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I33" s="100"/>
     </row>
@@ -3976,28 +3979,28 @@
         <v>25</v>
       </c>
       <c r="C34" s="92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D34" s="93" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E34" s="94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F34" s="94">
         <v>5</v>
       </c>
       <c r="G34" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H34" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I34" s="97"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:9">
       <c r="A35" s="102" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B35" s="102"/>
       <c r="C35" s="102"/>
@@ -4014,13 +4017,13 @@
         <v>26</v>
       </c>
       <c r="C36" s="92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D36" s="93" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E36" s="94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F36" s="94">
         <v>6</v>
@@ -4029,7 +4032,7 @@
         <v>16</v>
       </c>
       <c r="H36" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I36" s="97"/>
     </row>
@@ -4039,13 +4042,13 @@
         <v>27</v>
       </c>
       <c r="C37" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="99" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="94" t="s">
         <v>58</v>
-      </c>
-      <c r="D37" s="99" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="94" t="s">
-        <v>57</v>
       </c>
       <c r="F37" s="94">
         <v>6</v>
@@ -4054,7 +4057,7 @@
         <v>19</v>
       </c>
       <c r="H37" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I37" s="100"/>
     </row>
@@ -4064,13 +4067,13 @@
         <v>28</v>
       </c>
       <c r="C38" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" s="94" t="s">
         <v>58</v>
-      </c>
-      <c r="D38" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" s="94" t="s">
-        <v>57</v>
       </c>
       <c r="F38" s="94">
         <v>6</v>
@@ -4079,7 +4082,7 @@
         <v>21</v>
       </c>
       <c r="H38" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I38" s="97"/>
     </row>
@@ -4089,22 +4092,22 @@
         <v>29</v>
       </c>
       <c r="C39" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="99" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="94" t="s">
         <v>58</v>
-      </c>
-      <c r="D39" s="99" t="s">
-        <v>61</v>
-      </c>
-      <c r="E39" s="94" t="s">
-        <v>57</v>
       </c>
       <c r="F39" s="94">
         <v>6</v>
       </c>
       <c r="G39" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H39" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I39" s="100"/>
     </row>
@@ -4114,28 +4117,28 @@
         <v>30</v>
       </c>
       <c r="C40" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" s="94" t="s">
         <v>58</v>
-      </c>
-      <c r="D40" s="93" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="94" t="s">
-        <v>57</v>
       </c>
       <c r="F40" s="94">
         <v>6</v>
       </c>
       <c r="G40" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H40" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I40" s="97"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:9">
       <c r="A41" s="104" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B41" s="104"/>
       <c r="C41" s="104"/>
@@ -4152,13 +4155,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D42" s="93" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E42" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F42" s="94">
         <v>7</v>
@@ -4167,7 +4170,7 @@
         <v>16</v>
       </c>
       <c r="H42" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I42" s="97"/>
     </row>
@@ -4177,13 +4180,13 @@
         <v>32</v>
       </c>
       <c r="C43" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D43" s="99" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="94" t="s">
         <v>66</v>
-      </c>
-      <c r="E43" s="94" t="s">
-        <v>65</v>
       </c>
       <c r="F43" s="94">
         <v>7</v>
@@ -4192,7 +4195,7 @@
         <v>19</v>
       </c>
       <c r="H43" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I43" s="100"/>
     </row>
@@ -4202,13 +4205,13 @@
         <v>33</v>
       </c>
       <c r="C44" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D44" s="93" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E44" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F44" s="94">
         <v>7</v>
@@ -4217,7 +4220,7 @@
         <v>21</v>
       </c>
       <c r="H44" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I44" s="97"/>
     </row>
@@ -4227,22 +4230,22 @@
         <v>34</v>
       </c>
       <c r="C45" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D45" s="99" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E45" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F45" s="94">
         <v>7</v>
       </c>
       <c r="G45" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H45" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I45" s="100"/>
     </row>
@@ -4252,28 +4255,28 @@
         <v>35</v>
       </c>
       <c r="C46" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D46" s="93" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E46" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F46" s="94">
         <v>7</v>
       </c>
       <c r="G46" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H46" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I46" s="97"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:9">
       <c r="A47" s="104" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B47" s="104"/>
       <c r="C47" s="104"/>
@@ -4290,13 +4293,13 @@
         <v>36</v>
       </c>
       <c r="C48" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D48" s="93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E48" s="94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F48" s="94">
         <v>8</v>
@@ -4305,7 +4308,7 @@
         <v>16</v>
       </c>
       <c r="H48" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I48" s="97"/>
     </row>
@@ -4315,13 +4318,13 @@
         <v>37</v>
       </c>
       <c r="C49" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D49" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="E49" s="94" t="s">
         <v>73</v>
-      </c>
-      <c r="E49" s="94" t="s">
-        <v>72</v>
       </c>
       <c r="F49" s="94">
         <v>8</v>
@@ -4330,7 +4333,7 @@
         <v>19</v>
       </c>
       <c r="H49" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I49" s="100"/>
     </row>
@@ -4340,13 +4343,13 @@
         <v>38</v>
       </c>
       <c r="C50" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D50" s="93" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E50" s="94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F50" s="94">
         <v>8</v>
@@ -4355,7 +4358,7 @@
         <v>21</v>
       </c>
       <c r="H50" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I50" s="97"/>
     </row>
@@ -4365,22 +4368,22 @@
         <v>39</v>
       </c>
       <c r="C51" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D51" s="99" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E51" s="94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F51" s="94">
         <v>8</v>
       </c>
       <c r="G51" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H51" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I51" s="100"/>
     </row>
@@ -4390,28 +4393,28 @@
         <v>40</v>
       </c>
       <c r="C52" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D52" s="93" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E52" s="94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F52" s="94">
         <v>8</v>
       </c>
       <c r="G52" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H52" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I52" s="97"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:9">
       <c r="A53" s="104" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B53" s="104"/>
       <c r="C53" s="104"/>
@@ -4428,13 +4431,13 @@
         <v>41</v>
       </c>
       <c r="C54" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D54" s="93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E54" s="94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F54" s="94">
         <v>9</v>
@@ -4443,7 +4446,7 @@
         <v>16</v>
       </c>
       <c r="H54" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I54" s="97"/>
     </row>
@@ -4453,13 +4456,13 @@
         <v>42</v>
       </c>
       <c r="C55" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D55" s="99" t="s">
+        <v>81</v>
+      </c>
+      <c r="E55" s="94" t="s">
         <v>80</v>
-      </c>
-      <c r="E55" s="94" t="s">
-        <v>79</v>
       </c>
       <c r="F55" s="94">
         <v>9</v>
@@ -4468,7 +4471,7 @@
         <v>19</v>
       </c>
       <c r="H55" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I55" s="100"/>
     </row>
@@ -4478,13 +4481,13 @@
         <v>43</v>
       </c>
       <c r="C56" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D56" s="93" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E56" s="94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F56" s="94">
         <v>9</v>
@@ -4493,7 +4496,7 @@
         <v>21</v>
       </c>
       <c r="H56" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I56" s="97"/>
     </row>
@@ -4503,22 +4506,22 @@
         <v>44</v>
       </c>
       <c r="C57" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D57" s="99" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E57" s="94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F57" s="94">
         <v>9</v>
       </c>
       <c r="G57" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H57" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I57" s="100"/>
     </row>
@@ -4528,28 +4531,28 @@
         <v>45</v>
       </c>
       <c r="C58" s="92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D58" s="93" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E58" s="94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F58" s="94">
         <v>9</v>
       </c>
       <c r="G58" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H58" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I58" s="97"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:9">
       <c r="A59" s="105" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B59" s="105"/>
       <c r="C59" s="105"/>
@@ -4566,13 +4569,13 @@
         <v>46</v>
       </c>
       <c r="C60" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D60" s="93" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E60" s="94" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F60" s="94">
         <v>10</v>
@@ -4581,7 +4584,7 @@
         <v>16</v>
       </c>
       <c r="H60" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I60" s="97"/>
     </row>
@@ -4591,13 +4594,13 @@
         <v>47</v>
       </c>
       <c r="C61" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D61" s="99" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="94" t="s">
         <v>88</v>
-      </c>
-      <c r="E61" s="94" t="s">
-        <v>87</v>
       </c>
       <c r="F61" s="94">
         <v>10</v>
@@ -4606,7 +4609,7 @@
         <v>19</v>
       </c>
       <c r="H61" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I61" s="100"/>
     </row>
@@ -4616,13 +4619,13 @@
         <v>48</v>
       </c>
       <c r="C62" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D62" s="93" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E62" s="94" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F62" s="94">
         <v>10</v>
@@ -4631,7 +4634,7 @@
         <v>21</v>
       </c>
       <c r="H62" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I62" s="97"/>
     </row>
@@ -4641,22 +4644,22 @@
         <v>49</v>
       </c>
       <c r="C63" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D63" s="99" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E63" s="94" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F63" s="94">
         <v>10</v>
       </c>
       <c r="G63" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H63" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I63" s="100"/>
     </row>
@@ -4666,28 +4669,28 @@
         <v>50</v>
       </c>
       <c r="C64" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D64" s="93" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E64" s="94" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F64" s="94">
         <v>10</v>
       </c>
       <c r="G64" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H64" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I64" s="97"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:9">
       <c r="A65" s="105" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B65" s="105"/>
       <c r="C65" s="105"/>
@@ -4704,13 +4707,13 @@
         <v>51</v>
       </c>
       <c r="C66" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D66" s="93" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E66" s="94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F66" s="94">
         <v>11</v>
@@ -4719,7 +4722,7 @@
         <v>16</v>
       </c>
       <c r="H66" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I66" s="97"/>
     </row>
@@ -4729,13 +4732,13 @@
         <v>52</v>
       </c>
       <c r="C67" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D67" s="99" t="s">
+        <v>96</v>
+      </c>
+      <c r="E67" s="94" t="s">
         <v>95</v>
-      </c>
-      <c r="E67" s="94" t="s">
-        <v>94</v>
       </c>
       <c r="F67" s="94">
         <v>11</v>
@@ -4744,7 +4747,7 @@
         <v>19</v>
       </c>
       <c r="H67" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I67" s="100"/>
     </row>
@@ -4754,13 +4757,13 @@
         <v>53</v>
       </c>
       <c r="C68" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D68" s="93" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E68" s="94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F68" s="94">
         <v>11</v>
@@ -4769,7 +4772,7 @@
         <v>21</v>
       </c>
       <c r="H68" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I68" s="97"/>
     </row>
@@ -4779,22 +4782,22 @@
         <v>54</v>
       </c>
       <c r="C69" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D69" s="99" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E69" s="94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F69" s="94">
         <v>11</v>
       </c>
       <c r="G69" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H69" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I69" s="100"/>
     </row>
@@ -4804,28 +4807,28 @@
         <v>55</v>
       </c>
       <c r="C70" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D70" s="93" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E70" s="94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F70" s="94">
         <v>11</v>
       </c>
       <c r="G70" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H70" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I70" s="97"/>
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="1:9">
       <c r="A71" s="105" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B71" s="105"/>
       <c r="C71" s="105"/>
@@ -4842,13 +4845,13 @@
         <v>56</v>
       </c>
       <c r="C72" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D72" s="93" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E72" s="94" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F72" s="94">
         <v>12</v>
@@ -4857,7 +4860,7 @@
         <v>16</v>
       </c>
       <c r="H72" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I72" s="97"/>
     </row>
@@ -4867,13 +4870,13 @@
         <v>57</v>
       </c>
       <c r="C73" s="92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D73" s="99" t="s">
+        <v>103</v>
+      </c>
+      <c r="E73" s="94" t="s">
         <v>102</v>
-      </c>
-      <c r="E73" s="94" t="s">
-        <v>101</v>
       </c>
       <c r="F73" s="94">
         <v>12</v>
@@ -4882,7 +4885,7 @@
         <v>19</v>
       </c>
       <c r="H73" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I73" s="100"/>
     </row>
@@ -4892,13 +4895,13 @@
         <v>58</v>
       </c>
       <c r="C74" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D74" s="93" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E74" s="94" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F74" s="94">
         <v>12</v>
@@ -4907,7 +4910,7 @@
         <v>21</v>
       </c>
       <c r="H74" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I74" s="97"/>
     </row>
@@ -4917,22 +4920,22 @@
         <v>59</v>
       </c>
       <c r="C75" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D75" s="99" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E75" s="94" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F75" s="94">
         <v>12</v>
       </c>
       <c r="G75" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H75" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I75" s="100"/>
     </row>
@@ -4942,28 +4945,28 @@
         <v>60</v>
       </c>
       <c r="C76" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D76" s="93" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E76" s="94" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F76" s="94">
         <v>12</v>
       </c>
       <c r="G76" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H76" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I76" s="97"/>
     </row>
     <row r="77" ht="16.5" customHeight="1" spans="1:9">
       <c r="A77" s="108" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B77" s="108"/>
       <c r="C77" s="108"/>
@@ -4980,13 +4983,13 @@
         <v>61</v>
       </c>
       <c r="C78" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D78" s="93" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E78" s="94" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F78" s="94">
         <v>13</v>
@@ -4995,7 +4998,7 @@
         <v>16</v>
       </c>
       <c r="H78" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I78" s="97"/>
     </row>
@@ -5005,13 +5008,13 @@
         <v>62</v>
       </c>
       <c r="C79" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D79" s="99" t="s">
+        <v>111</v>
+      </c>
+      <c r="E79" s="94" t="s">
         <v>110</v>
-      </c>
-      <c r="E79" s="94" t="s">
-        <v>109</v>
       </c>
       <c r="F79" s="94">
         <v>13</v>
@@ -5020,7 +5023,7 @@
         <v>19</v>
       </c>
       <c r="H79" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I79" s="100"/>
     </row>
@@ -5030,13 +5033,13 @@
         <v>63</v>
       </c>
       <c r="C80" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D80" s="93" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E80" s="94" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F80" s="94">
         <v>13</v>
@@ -5045,7 +5048,7 @@
         <v>21</v>
       </c>
       <c r="H80" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I80" s="97"/>
     </row>
@@ -5055,22 +5058,22 @@
         <v>64</v>
       </c>
       <c r="C81" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D81" s="99" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E81" s="94" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F81" s="94">
         <v>13</v>
       </c>
       <c r="G81" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H81" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I81" s="100"/>
     </row>
@@ -5080,28 +5083,28 @@
         <v>65</v>
       </c>
       <c r="C82" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D82" s="93" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E82" s="94" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F82" s="94">
         <v>13</v>
       </c>
       <c r="G82" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H82" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I82" s="97"/>
     </row>
     <row r="83" ht="16.5" customHeight="1" spans="1:9">
       <c r="A83" s="108" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B83" s="108"/>
       <c r="C83" s="108"/>
@@ -5118,13 +5121,13 @@
         <v>66</v>
       </c>
       <c r="C84" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D84" s="93" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E84" s="94" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F84" s="94">
         <v>14</v>
@@ -5133,7 +5136,7 @@
         <v>16</v>
       </c>
       <c r="H84" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I84" s="97"/>
     </row>
@@ -5143,13 +5146,13 @@
         <v>67</v>
       </c>
       <c r="C85" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D85" s="99" t="s">
+        <v>118</v>
+      </c>
+      <c r="E85" s="94" t="s">
         <v>117</v>
-      </c>
-      <c r="E85" s="94" t="s">
-        <v>116</v>
       </c>
       <c r="F85" s="94">
         <v>14</v>
@@ -5158,7 +5161,7 @@
         <v>19</v>
       </c>
       <c r="H85" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I85" s="100"/>
     </row>
@@ -5168,13 +5171,13 @@
         <v>68</v>
       </c>
       <c r="C86" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D86" s="93" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E86" s="94" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F86" s="94">
         <v>14</v>
@@ -5183,7 +5186,7 @@
         <v>21</v>
       </c>
       <c r="H86" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I86" s="97"/>
     </row>
@@ -5193,22 +5196,22 @@
         <v>69</v>
       </c>
       <c r="C87" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D87" s="99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E87" s="94" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F87" s="94">
         <v>14</v>
       </c>
       <c r="G87" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H87" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I87" s="100"/>
     </row>
@@ -5218,28 +5221,28 @@
         <v>70</v>
       </c>
       <c r="C88" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D88" s="93" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E88" s="94" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F88" s="94">
         <v>14</v>
       </c>
       <c r="G88" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H88" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I88" s="97"/>
     </row>
     <row r="89" ht="16.5" customHeight="1" spans="1:9">
       <c r="A89" s="108" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B89" s="108"/>
       <c r="C89" s="108"/>
@@ -5256,13 +5259,13 @@
         <v>71</v>
       </c>
       <c r="C90" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D90" s="93" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E90" s="94" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F90" s="94">
         <v>15</v>
@@ -5271,7 +5274,7 @@
         <v>16</v>
       </c>
       <c r="H90" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I90" s="97"/>
     </row>
@@ -5281,13 +5284,13 @@
         <v>72</v>
       </c>
       <c r="C91" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D91" s="99" t="s">
+        <v>125</v>
+      </c>
+      <c r="E91" s="94" t="s">
         <v>124</v>
-      </c>
-      <c r="E91" s="94" t="s">
-        <v>123</v>
       </c>
       <c r="F91" s="94">
         <v>15</v>
@@ -5296,7 +5299,7 @@
         <v>19</v>
       </c>
       <c r="H91" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I91" s="100"/>
     </row>
@@ -5306,13 +5309,13 @@
         <v>73</v>
       </c>
       <c r="C92" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D92" s="93" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E92" s="94" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F92" s="94">
         <v>15</v>
@@ -5321,7 +5324,7 @@
         <v>21</v>
       </c>
       <c r="H92" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I92" s="97"/>
     </row>
@@ -5331,22 +5334,22 @@
         <v>74</v>
       </c>
       <c r="C93" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D93" s="99" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E93" s="94" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F93" s="94">
         <v>15</v>
       </c>
       <c r="G93" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H93" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I93" s="100"/>
     </row>
@@ -5356,28 +5359,28 @@
         <v>75</v>
       </c>
       <c r="C94" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D94" s="93" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E94" s="94" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F94" s="94">
         <v>15</v>
       </c>
       <c r="G94" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H94" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I94" s="97"/>
     </row>
     <row r="95" ht="16.5" customHeight="1" spans="1:9">
       <c r="A95" s="110" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B95" s="110"/>
       <c r="C95" s="110"/>
@@ -5394,13 +5397,13 @@
         <v>76</v>
       </c>
       <c r="C96" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D96" s="93" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E96" s="94" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F96" s="94">
         <v>16</v>
@@ -5409,7 +5412,7 @@
         <v>16</v>
       </c>
       <c r="H96" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I96" s="97"/>
     </row>
@@ -5419,13 +5422,13 @@
         <v>77</v>
       </c>
       <c r="C97" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D97" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="E97" s="94" t="s">
         <v>132</v>
-      </c>
-      <c r="E97" s="94" t="s">
-        <v>131</v>
       </c>
       <c r="F97" s="94">
         <v>16</v>
@@ -5434,7 +5437,7 @@
         <v>19</v>
       </c>
       <c r="H97" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I97" s="100"/>
     </row>
@@ -5444,13 +5447,13 @@
         <v>78</v>
       </c>
       <c r="C98" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D98" s="93" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E98" s="94" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F98" s="94">
         <v>16</v>
@@ -5459,7 +5462,7 @@
         <v>21</v>
       </c>
       <c r="H98" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I98" s="97"/>
     </row>
@@ -5469,22 +5472,22 @@
         <v>79</v>
       </c>
       <c r="C99" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D99" s="99" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E99" s="94" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F99" s="94">
         <v>16</v>
       </c>
       <c r="G99" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H99" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I99" s="100"/>
     </row>
@@ -5494,28 +5497,28 @@
         <v>80</v>
       </c>
       <c r="C100" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D100" s="93" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E100" s="94" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F100" s="94">
         <v>16</v>
       </c>
       <c r="G100" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H100" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I100" s="97"/>
     </row>
     <row r="101" ht="16.5" customHeight="1" spans="1:9">
       <c r="A101" s="110" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B101" s="110"/>
       <c r="C101" s="110"/>
@@ -5532,13 +5535,13 @@
         <v>81</v>
       </c>
       <c r="C102" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D102" s="93" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E102" s="94" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F102" s="94">
         <v>17</v>
@@ -5547,7 +5550,7 @@
         <v>16</v>
       </c>
       <c r="H102" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I102" s="97"/>
     </row>
@@ -5557,13 +5560,13 @@
         <v>82</v>
       </c>
       <c r="C103" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D103" s="99" t="s">
+        <v>140</v>
+      </c>
+      <c r="E103" s="94" t="s">
         <v>139</v>
-      </c>
-      <c r="E103" s="94" t="s">
-        <v>138</v>
       </c>
       <c r="F103" s="94">
         <v>17</v>
@@ -5572,7 +5575,7 @@
         <v>19</v>
       </c>
       <c r="H103" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I103" s="100"/>
     </row>
@@ -5582,13 +5585,13 @@
         <v>83</v>
       </c>
       <c r="C104" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D104" s="93" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E104" s="94" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F104" s="94">
         <v>17</v>
@@ -5597,7 +5600,7 @@
         <v>21</v>
       </c>
       <c r="H104" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I104" s="97"/>
     </row>
@@ -5607,22 +5610,22 @@
         <v>84</v>
       </c>
       <c r="C105" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D105" s="99" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E105" s="94" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F105" s="94">
         <v>17</v>
       </c>
       <c r="G105" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H105" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I105" s="100"/>
     </row>
@@ -5632,28 +5635,28 @@
         <v>85</v>
       </c>
       <c r="C106" s="92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D106" s="93" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E106" s="94" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F106" s="94">
         <v>17</v>
       </c>
       <c r="G106" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H106" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I106" s="97"/>
     </row>
     <row r="107" ht="16.5" customHeight="1" spans="1:9">
       <c r="A107" s="111" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B107" s="111"/>
       <c r="C107" s="111"/>
@@ -5670,13 +5673,13 @@
         <v>86</v>
       </c>
       <c r="C108" s="92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D108" s="93" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E108" s="94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F108" s="94">
         <v>18</v>
@@ -5685,7 +5688,7 @@
         <v>16</v>
       </c>
       <c r="H108" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I108" s="97"/>
     </row>
@@ -5695,13 +5698,13 @@
         <v>87</v>
       </c>
       <c r="C109" s="92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D109" s="99" t="s">
+        <v>147</v>
+      </c>
+      <c r="E109" s="94" t="s">
         <v>146</v>
-      </c>
-      <c r="E109" s="94" t="s">
-        <v>145</v>
       </c>
       <c r="F109" s="94">
         <v>18</v>
@@ -5710,7 +5713,7 @@
         <v>19</v>
       </c>
       <c r="H109" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I109" s="100"/>
     </row>
@@ -5720,13 +5723,13 @@
         <v>88</v>
       </c>
       <c r="C110" s="92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D110" s="93" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E110" s="94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F110" s="94">
         <v>18</v>
@@ -5735,7 +5738,7 @@
         <v>21</v>
       </c>
       <c r="H110" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I110" s="97"/>
     </row>
@@ -5745,22 +5748,22 @@
         <v>89</v>
       </c>
       <c r="C111" s="92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D111" s="99" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E111" s="94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F111" s="94">
         <v>18</v>
       </c>
       <c r="G111" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H111" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I111" s="100"/>
     </row>
@@ -5770,28 +5773,28 @@
         <v>90</v>
       </c>
       <c r="C112" s="92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D112" s="93" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E112" s="94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F112" s="94">
         <v>18</v>
       </c>
       <c r="G112" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H112" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I112" s="97"/>
     </row>
     <row r="113" ht="16.5" customHeight="1" spans="1:9">
       <c r="A113" s="111" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B113" s="111"/>
       <c r="C113" s="111"/>
@@ -5808,13 +5811,13 @@
         <v>91</v>
       </c>
       <c r="C114" s="92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D114" s="93" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E114" s="94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F114" s="94">
         <v>19</v>
@@ -5823,7 +5826,7 @@
         <v>16</v>
       </c>
       <c r="H114" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I114" s="97"/>
     </row>
@@ -5833,13 +5836,13 @@
         <v>92</v>
       </c>
       <c r="C115" s="92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D115" s="99" t="s">
+        <v>154</v>
+      </c>
+      <c r="E115" s="94" t="s">
         <v>153</v>
-      </c>
-      <c r="E115" s="94" t="s">
-        <v>152</v>
       </c>
       <c r="F115" s="94">
         <v>19</v>
@@ -5848,7 +5851,7 @@
         <v>19</v>
       </c>
       <c r="H115" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I115" s="100"/>
     </row>
@@ -5858,13 +5861,13 @@
         <v>93</v>
       </c>
       <c r="C116" s="92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D116" s="93" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E116" s="94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F116" s="94">
         <v>19</v>
@@ -5873,7 +5876,7 @@
         <v>21</v>
       </c>
       <c r="H116" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I116" s="97"/>
     </row>
@@ -5883,22 +5886,22 @@
         <v>94</v>
       </c>
       <c r="C117" s="92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D117" s="99" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E117" s="94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F117" s="94">
         <v>19</v>
       </c>
       <c r="G117" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H117" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I117" s="100"/>
     </row>
@@ -5908,28 +5911,28 @@
         <v>95</v>
       </c>
       <c r="C118" s="92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D118" s="93" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E118" s="94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F118" s="94">
         <v>19</v>
       </c>
       <c r="G118" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H118" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I118" s="97"/>
     </row>
     <row r="119" ht="16.5" customHeight="1" spans="1:9">
       <c r="A119" s="114" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B119" s="114"/>
       <c r="C119" s="114"/>
@@ -5946,13 +5949,13 @@
         <v>96</v>
       </c>
       <c r="C120" s="92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D120" s="93" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E120" s="94" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F120" s="94">
         <v>20</v>
@@ -5961,7 +5964,7 @@
         <v>16</v>
       </c>
       <c r="H120" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I120" s="97"/>
     </row>
@@ -5971,13 +5974,13 @@
         <v>97</v>
       </c>
       <c r="C121" s="92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D121" s="99" t="s">
+        <v>162</v>
+      </c>
+      <c r="E121" s="94" t="s">
         <v>161</v>
-      </c>
-      <c r="E121" s="94" t="s">
-        <v>160</v>
       </c>
       <c r="F121" s="94">
         <v>20</v>
@@ -5986,7 +5989,7 @@
         <v>19</v>
       </c>
       <c r="H121" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I121" s="100"/>
     </row>
@@ -5996,13 +5999,13 @@
         <v>98</v>
       </c>
       <c r="C122" s="92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D122" s="93" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E122" s="94" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F122" s="94">
         <v>20</v>
@@ -6011,7 +6014,7 @@
         <v>21</v>
       </c>
       <c r="H122" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I122" s="97"/>
     </row>
@@ -6021,22 +6024,22 @@
         <v>99</v>
       </c>
       <c r="C123" s="92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D123" s="99" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E123" s="94" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F123" s="94">
         <v>20</v>
       </c>
       <c r="G123" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H123" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I123" s="100"/>
     </row>
@@ -6046,28 +6049,28 @@
         <v>100</v>
       </c>
       <c r="C124" s="92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D124" s="93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E124" s="94" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F124" s="94">
         <v>20</v>
       </c>
       <c r="G124" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H124" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I124" s="97"/>
     </row>
     <row r="125" ht="16.5" customHeight="1" spans="1:9">
       <c r="A125" s="115" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B125" s="115"/>
       <c r="C125" s="115"/>
@@ -6084,13 +6087,13 @@
         <v>101</v>
       </c>
       <c r="C126" s="92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D126" s="93" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E126" s="94" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F126" s="94">
         <v>21</v>
@@ -6099,7 +6102,7 @@
         <v>16</v>
       </c>
       <c r="H126" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I126" s="97"/>
     </row>
@@ -6109,13 +6112,13 @@
         <v>102</v>
       </c>
       <c r="C127" s="92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D127" s="99" t="s">
+        <v>170</v>
+      </c>
+      <c r="E127" s="94" t="s">
         <v>169</v>
-      </c>
-      <c r="E127" s="94" t="s">
-        <v>168</v>
       </c>
       <c r="F127" s="94">
         <v>21</v>
@@ -6124,7 +6127,7 @@
         <v>19</v>
       </c>
       <c r="H127" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I127" s="100"/>
     </row>
@@ -6134,13 +6137,13 @@
         <v>103</v>
       </c>
       <c r="C128" s="92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D128" s="93" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E128" s="94" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F128" s="94">
         <v>21</v>
@@ -6149,7 +6152,7 @@
         <v>21</v>
       </c>
       <c r="H128" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I128" s="97"/>
     </row>
@@ -6159,22 +6162,22 @@
         <v>104</v>
       </c>
       <c r="C129" s="92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D129" s="99" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E129" s="94" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F129" s="94">
         <v>21</v>
       </c>
       <c r="G129" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H129" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I129" s="100"/>
     </row>
@@ -6184,28 +6187,28 @@
         <v>105</v>
       </c>
       <c r="C130" s="92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D130" s="93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E130" s="94" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F130" s="94">
         <v>21</v>
       </c>
       <c r="G130" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H130" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I130" s="97"/>
     </row>
     <row r="131" ht="16.5" customHeight="1" spans="1:9">
       <c r="A131" s="115" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B131" s="115"/>
       <c r="C131" s="115"/>
@@ -6222,13 +6225,13 @@
         <v>106</v>
       </c>
       <c r="C132" s="92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D132" s="93" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E132" s="94" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F132" s="94">
         <v>22</v>
@@ -6237,7 +6240,7 @@
         <v>16</v>
       </c>
       <c r="H132" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I132" s="97"/>
     </row>
@@ -6247,13 +6250,13 @@
         <v>107</v>
       </c>
       <c r="C133" s="92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D133" s="99" t="s">
+        <v>177</v>
+      </c>
+      <c r="E133" s="94" t="s">
         <v>176</v>
-      </c>
-      <c r="E133" s="94" t="s">
-        <v>175</v>
       </c>
       <c r="F133" s="94">
         <v>22</v>
@@ -6262,7 +6265,7 @@
         <v>19</v>
       </c>
       <c r="H133" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I133" s="100"/>
     </row>
@@ -6272,13 +6275,13 @@
         <v>108</v>
       </c>
       <c r="C134" s="92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D134" s="93" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E134" s="94" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F134" s="94">
         <v>22</v>
@@ -6287,7 +6290,7 @@
         <v>21</v>
       </c>
       <c r="H134" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I134" s="97"/>
     </row>
@@ -6297,22 +6300,22 @@
         <v>109</v>
       </c>
       <c r="C135" s="92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D135" s="99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E135" s="94" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F135" s="94">
         <v>22</v>
       </c>
       <c r="G135" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H135" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I135" s="100"/>
     </row>
@@ -6322,28 +6325,28 @@
         <v>110</v>
       </c>
       <c r="C136" s="92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D136" s="93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E136" s="94" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F136" s="94">
         <v>22</v>
       </c>
       <c r="G136" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H136" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I136" s="97"/>
     </row>
     <row r="137" ht="16.5" customHeight="1" spans="1:9">
       <c r="A137" s="118" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B137" s="118"/>
       <c r="C137" s="118"/>
@@ -6360,13 +6363,13 @@
         <v>111</v>
       </c>
       <c r="C138" s="92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D138" s="93" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E138" s="94" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F138" s="94">
         <v>23</v>
@@ -6375,7 +6378,7 @@
         <v>16</v>
       </c>
       <c r="H138" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I138" s="97"/>
     </row>
@@ -6385,13 +6388,13 @@
         <v>112</v>
       </c>
       <c r="C139" s="92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D139" s="99" t="s">
+        <v>185</v>
+      </c>
+      <c r="E139" s="94" t="s">
         <v>184</v>
-      </c>
-      <c r="E139" s="94" t="s">
-        <v>183</v>
       </c>
       <c r="F139" s="94">
         <v>23</v>
@@ -6400,7 +6403,7 @@
         <v>19</v>
       </c>
       <c r="H139" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I139" s="100"/>
     </row>
@@ -6410,13 +6413,13 @@
         <v>113</v>
       </c>
       <c r="C140" s="92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D140" s="93" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E140" s="94" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F140" s="94">
         <v>23</v>
@@ -6425,7 +6428,7 @@
         <v>21</v>
       </c>
       <c r="H140" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I140" s="97"/>
     </row>
@@ -6435,22 +6438,22 @@
         <v>114</v>
       </c>
       <c r="C141" s="92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D141" s="99" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E141" s="94" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F141" s="94">
         <v>23</v>
       </c>
       <c r="G141" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H141" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I141" s="100"/>
     </row>
@@ -6460,28 +6463,28 @@
         <v>115</v>
       </c>
       <c r="C142" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D142" s="93" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E142" s="94" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F142" s="94">
         <v>23</v>
       </c>
       <c r="G142" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H142" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I142" s="97"/>
     </row>
     <row r="143" ht="16.5" customHeight="1" spans="1:9">
       <c r="A143" s="120" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B143" s="120"/>
       <c r="C143" s="120"/>
@@ -6498,13 +6501,13 @@
         <v>116</v>
       </c>
       <c r="C144" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D144" s="93" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E144" s="94" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F144" s="94">
         <v>24</v>
@@ -6513,7 +6516,7 @@
         <v>16</v>
       </c>
       <c r="H144" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I144" s="97"/>
     </row>
@@ -6523,13 +6526,13 @@
         <v>117</v>
       </c>
       <c r="C145" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D145" s="99" t="s">
+        <v>193</v>
+      </c>
+      <c r="E145" s="94" t="s">
         <v>192</v>
-      </c>
-      <c r="E145" s="94" t="s">
-        <v>191</v>
       </c>
       <c r="F145" s="94">
         <v>24</v>
@@ -6538,7 +6541,7 @@
         <v>19</v>
       </c>
       <c r="H145" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I145" s="100"/>
     </row>
@@ -6548,13 +6551,13 @@
         <v>118</v>
       </c>
       <c r="C146" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D146" s="93" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E146" s="94" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F146" s="94">
         <v>24</v>
@@ -6563,7 +6566,7 @@
         <v>21</v>
       </c>
       <c r="H146" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I146" s="97"/>
     </row>
@@ -6573,22 +6576,22 @@
         <v>119</v>
       </c>
       <c r="C147" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D147" s="99" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E147" s="94" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F147" s="94">
         <v>24</v>
       </c>
       <c r="G147" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H147" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I147" s="100"/>
     </row>
@@ -6598,28 +6601,28 @@
         <v>120</v>
       </c>
       <c r="C148" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D148" s="93" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E148" s="94" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F148" s="94">
         <v>24</v>
       </c>
       <c r="G148" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H148" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I148" s="97"/>
     </row>
     <row r="149" ht="16.5" customHeight="1" spans="1:9">
       <c r="A149" s="120" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B149" s="120"/>
       <c r="C149" s="120"/>
@@ -6636,13 +6639,13 @@
         <v>121</v>
       </c>
       <c r="C150" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D150" s="93" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E150" s="94" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F150" s="94">
         <v>25</v>
@@ -6651,7 +6654,7 @@
         <v>16</v>
       </c>
       <c r="H150" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I150" s="97"/>
     </row>
@@ -6661,13 +6664,13 @@
         <v>122</v>
       </c>
       <c r="C151" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D151" s="99" t="s">
+        <v>200</v>
+      </c>
+      <c r="E151" s="94" t="s">
         <v>199</v>
-      </c>
-      <c r="E151" s="94" t="s">
-        <v>198</v>
       </c>
       <c r="F151" s="94">
         <v>25</v>
@@ -6676,7 +6679,7 @@
         <v>19</v>
       </c>
       <c r="H151" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I151" s="100"/>
     </row>
@@ -6686,13 +6689,13 @@
         <v>123</v>
       </c>
       <c r="C152" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D152" s="93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E152" s="94" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F152" s="94">
         <v>25</v>
@@ -6701,7 +6704,7 @@
         <v>21</v>
       </c>
       <c r="H152" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I152" s="97"/>
     </row>
@@ -6711,22 +6714,22 @@
         <v>124</v>
       </c>
       <c r="C153" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D153" s="99" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E153" s="94" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F153" s="94">
         <v>25</v>
       </c>
       <c r="G153" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H153" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I153" s="100"/>
     </row>
@@ -6736,28 +6739,28 @@
         <v>125</v>
       </c>
       <c r="C154" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D154" s="93" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E154" s="94" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F154" s="94">
         <v>25</v>
       </c>
       <c r="G154" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H154" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I154" s="97"/>
     </row>
     <row r="155" ht="16.5" customHeight="1" spans="1:9">
       <c r="A155" s="122" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B155" s="122"/>
       <c r="C155" s="122"/>
@@ -6774,13 +6777,13 @@
         <v>126</v>
       </c>
       <c r="C156" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D156" s="93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E156" s="94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F156" s="94">
         <v>26</v>
@@ -6789,7 +6792,7 @@
         <v>16</v>
       </c>
       <c r="H156" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I156" s="97"/>
     </row>
@@ -6799,13 +6802,13 @@
         <v>127</v>
       </c>
       <c r="C157" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D157" s="99" t="s">
+        <v>208</v>
+      </c>
+      <c r="E157" s="94" t="s">
         <v>207</v>
-      </c>
-      <c r="E157" s="94" t="s">
-        <v>206</v>
       </c>
       <c r="F157" s="94">
         <v>26</v>
@@ -6814,7 +6817,7 @@
         <v>19</v>
       </c>
       <c r="H157" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I157" s="100"/>
     </row>
@@ -6824,13 +6827,13 @@
         <v>128</v>
       </c>
       <c r="C158" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D158" s="93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E158" s="94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F158" s="94">
         <v>26</v>
@@ -6839,7 +6842,7 @@
         <v>21</v>
       </c>
       <c r="H158" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I158" s="97"/>
     </row>
@@ -6849,22 +6852,22 @@
         <v>129</v>
       </c>
       <c r="C159" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D159" s="99" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E159" s="94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F159" s="94">
         <v>26</v>
       </c>
       <c r="G159" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H159" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I159" s="100"/>
     </row>
@@ -6874,28 +6877,28 @@
         <v>130</v>
       </c>
       <c r="C160" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D160" s="93" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E160" s="94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F160" s="94">
         <v>26</v>
       </c>
       <c r="G160" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H160" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I160" s="97"/>
     </row>
     <row r="161" ht="16.5" customHeight="1" spans="1:9">
       <c r="A161" s="122" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B161" s="122"/>
       <c r="C161" s="122"/>
@@ -6912,13 +6915,13 @@
         <v>131</v>
       </c>
       <c r="C162" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D162" s="93" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E162" s="94" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F162" s="94">
         <v>27</v>
@@ -6927,7 +6930,7 @@
         <v>16</v>
       </c>
       <c r="H162" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I162" s="97"/>
     </row>
@@ -6937,13 +6940,13 @@
         <v>132</v>
       </c>
       <c r="C163" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D163" s="99" t="s">
+        <v>215</v>
+      </c>
+      <c r="E163" s="94" t="s">
         <v>214</v>
-      </c>
-      <c r="E163" s="94" t="s">
-        <v>213</v>
       </c>
       <c r="F163" s="94">
         <v>27</v>
@@ -6952,7 +6955,7 @@
         <v>19</v>
       </c>
       <c r="H163" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I163" s="100"/>
     </row>
@@ -6962,13 +6965,13 @@
         <v>133</v>
       </c>
       <c r="C164" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D164" s="93" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E164" s="94" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F164" s="94">
         <v>27</v>
@@ -6977,7 +6980,7 @@
         <v>21</v>
       </c>
       <c r="H164" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I164" s="97"/>
     </row>
@@ -6987,22 +6990,22 @@
         <v>134</v>
       </c>
       <c r="C165" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D165" s="99" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E165" s="94" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F165" s="94">
         <v>27</v>
       </c>
       <c r="G165" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H165" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I165" s="100"/>
     </row>
@@ -7012,28 +7015,28 @@
         <v>135</v>
       </c>
       <c r="C166" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D166" s="93" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E166" s="94" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F166" s="94">
         <v>27</v>
       </c>
       <c r="G166" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H166" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I166" s="97"/>
     </row>
     <row r="167" ht="16.5" customHeight="1" spans="1:9">
       <c r="A167" s="122" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B167" s="122"/>
       <c r="C167" s="122"/>
@@ -7050,13 +7053,13 @@
         <v>136</v>
       </c>
       <c r="C168" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D168" s="93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E168" s="94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F168" s="94">
         <v>28</v>
@@ -7065,7 +7068,7 @@
         <v>16</v>
       </c>
       <c r="H168" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I168" s="97"/>
     </row>
@@ -7075,13 +7078,13 @@
         <v>137</v>
       </c>
       <c r="C169" s="92" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D169" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="E169" s="94" t="s">
         <v>221</v>
-      </c>
-      <c r="E169" s="94" t="s">
-        <v>220</v>
       </c>
       <c r="F169" s="94">
         <v>28</v>
@@ -7090,7 +7093,7 @@
         <v>19</v>
       </c>
       <c r="H169" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I169" s="100"/>
     </row>
@@ -7100,13 +7103,13 @@
         <v>138</v>
       </c>
       <c r="C170" s="92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D170" s="93" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E170" s="94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F170" s="94">
         <v>28</v>
@@ -7115,7 +7118,7 @@
         <v>21</v>
       </c>
       <c r="H170" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I170" s="97"/>
     </row>
@@ -7125,22 +7128,22 @@
         <v>139</v>
       </c>
       <c r="C171" s="92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D171" s="99" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E171" s="94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F171" s="94">
         <v>28</v>
       </c>
       <c r="G171" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H171" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I171" s="100"/>
     </row>
@@ -7150,28 +7153,28 @@
         <v>140</v>
       </c>
       <c r="C172" s="92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D172" s="93" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E172" s="94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F172" s="94">
         <v>28</v>
       </c>
       <c r="G172" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H172" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I172" s="97"/>
     </row>
     <row r="173" ht="16.5" customHeight="1" spans="1:9">
       <c r="A173" s="124" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B173" s="124"/>
       <c r="C173" s="124"/>
@@ -7188,13 +7191,13 @@
         <v>141</v>
       </c>
       <c r="C174" s="92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D174" s="93" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E174" s="94" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F174" s="94">
         <v>29</v>
@@ -7203,7 +7206,7 @@
         <v>16</v>
       </c>
       <c r="H174" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I174" s="97"/>
     </row>
@@ -7213,13 +7216,13 @@
         <v>142</v>
       </c>
       <c r="C175" s="92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D175" s="99" t="s">
+        <v>230</v>
+      </c>
+      <c r="E175" s="94" t="s">
         <v>229</v>
-      </c>
-      <c r="E175" s="94" t="s">
-        <v>228</v>
       </c>
       <c r="F175" s="94">
         <v>29</v>
@@ -7228,7 +7231,7 @@
         <v>19</v>
       </c>
       <c r="H175" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I175" s="100"/>
     </row>
@@ -7238,13 +7241,13 @@
         <v>143</v>
       </c>
       <c r="C176" s="92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D176" s="93" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E176" s="94" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F176" s="94">
         <v>29</v>
@@ -7253,7 +7256,7 @@
         <v>21</v>
       </c>
       <c r="H176" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I176" s="97"/>
     </row>
@@ -7263,22 +7266,22 @@
         <v>144</v>
       </c>
       <c r="C177" s="92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D177" s="99" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E177" s="94" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F177" s="94">
         <v>29</v>
       </c>
       <c r="G177" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H177" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I177" s="100"/>
     </row>
@@ -7288,28 +7291,28 @@
         <v>145</v>
       </c>
       <c r="C178" s="92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D178" s="93" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E178" s="94" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F178" s="94">
         <v>29</v>
       </c>
       <c r="G178" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H178" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I178" s="97"/>
     </row>
     <row r="179" ht="16.5" customHeight="1" spans="1:9">
       <c r="A179" s="126" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B179" s="126"/>
       <c r="C179" s="126"/>
@@ -7326,13 +7329,13 @@
         <v>146</v>
       </c>
       <c r="C180" s="92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D180" s="93" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E180" s="94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F180" s="94">
         <v>30</v>
@@ -7341,7 +7344,7 @@
         <v>16</v>
       </c>
       <c r="H180" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I180" s="97"/>
     </row>
@@ -7351,13 +7354,13 @@
         <v>147</v>
       </c>
       <c r="C181" s="92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D181" s="99" t="s">
+        <v>238</v>
+      </c>
+      <c r="E181" s="94" t="s">
         <v>237</v>
-      </c>
-      <c r="E181" s="94" t="s">
-        <v>236</v>
       </c>
       <c r="F181" s="94">
         <v>30</v>
@@ -7366,7 +7369,7 @@
         <v>19</v>
       </c>
       <c r="H181" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I181" s="100"/>
     </row>
@@ -7376,13 +7379,13 @@
         <v>148</v>
       </c>
       <c r="C182" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D182" s="93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E182" s="94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F182" s="94">
         <v>30</v>
@@ -7391,7 +7394,7 @@
         <v>21</v>
       </c>
       <c r="H182" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I182" s="97"/>
     </row>
@@ -7401,22 +7404,22 @@
         <v>149</v>
       </c>
       <c r="C183" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D183" s="99" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E183" s="94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F183" s="94">
         <v>30</v>
       </c>
       <c r="G183" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H183" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I183" s="100"/>
     </row>
@@ -7426,28 +7429,28 @@
         <v>150</v>
       </c>
       <c r="C184" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D184" s="93" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E184" s="94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F184" s="94">
         <v>30</v>
       </c>
       <c r="G184" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H184" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I184" s="97"/>
     </row>
     <row r="185" ht="16.5" customHeight="1" spans="1:9">
       <c r="A185" s="128" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B185" s="128"/>
       <c r="C185" s="128"/>
@@ -7464,13 +7467,13 @@
         <v>151</v>
       </c>
       <c r="C186" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D186" s="93" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E186" s="94" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F186" s="94">
         <v>31</v>
@@ -7479,7 +7482,7 @@
         <v>16</v>
       </c>
       <c r="H186" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I186" s="97"/>
     </row>
@@ -7489,13 +7492,13 @@
         <v>152</v>
       </c>
       <c r="C187" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D187" s="99" t="s">
+        <v>246</v>
+      </c>
+      <c r="E187" s="94" t="s">
         <v>245</v>
-      </c>
-      <c r="E187" s="94" t="s">
-        <v>244</v>
       </c>
       <c r="F187" s="94">
         <v>31</v>
@@ -7504,7 +7507,7 @@
         <v>19</v>
       </c>
       <c r="H187" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I187" s="100"/>
     </row>
@@ -7514,13 +7517,13 @@
         <v>153</v>
       </c>
       <c r="C188" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D188" s="93" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E188" s="94" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F188" s="94">
         <v>31</v>
@@ -7529,7 +7532,7 @@
         <v>21</v>
       </c>
       <c r="H188" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I188" s="97"/>
     </row>
@@ -7539,22 +7542,22 @@
         <v>154</v>
       </c>
       <c r="C189" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D189" s="99" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E189" s="94" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F189" s="94">
         <v>31</v>
       </c>
       <c r="G189" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H189" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I189" s="100"/>
     </row>
@@ -7564,28 +7567,28 @@
         <v>155</v>
       </c>
       <c r="C190" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D190" s="93" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E190" s="94" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F190" s="94">
         <v>31</v>
       </c>
       <c r="G190" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H190" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I190" s="97"/>
     </row>
     <row r="191" ht="16.5" customHeight="1" spans="1:9">
       <c r="A191" s="89" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B191" s="89"/>
       <c r="C191" s="89"/>
@@ -7602,13 +7605,13 @@
         <v>156</v>
       </c>
       <c r="C192" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D192" s="93" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E192" s="94" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F192" s="94">
         <v>32</v>
@@ -7617,7 +7620,7 @@
         <v>16</v>
       </c>
       <c r="H192" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I192" s="97"/>
     </row>
@@ -7627,13 +7630,13 @@
         <v>157</v>
       </c>
       <c r="C193" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D193" s="99" t="s">
+        <v>254</v>
+      </c>
+      <c r="E193" s="94" t="s">
         <v>253</v>
-      </c>
-      <c r="E193" s="94" t="s">
-        <v>252</v>
       </c>
       <c r="F193" s="94">
         <v>32</v>
@@ -7642,7 +7645,7 @@
         <v>19</v>
       </c>
       <c r="H193" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I193" s="100"/>
     </row>
@@ -7652,13 +7655,13 @@
         <v>158</v>
       </c>
       <c r="C194" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D194" s="93" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E194" s="94" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F194" s="94">
         <v>32</v>
@@ -7667,7 +7670,7 @@
         <v>21</v>
       </c>
       <c r="H194" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I194" s="97"/>
     </row>
@@ -7677,22 +7680,22 @@
         <v>159</v>
       </c>
       <c r="C195" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D195" s="99" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E195" s="94" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F195" s="94">
         <v>32</v>
       </c>
       <c r="G195" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H195" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I195" s="100"/>
     </row>
@@ -7702,28 +7705,28 @@
         <v>160</v>
       </c>
       <c r="C196" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D196" s="93" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E196" s="94" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F196" s="94">
         <v>32</v>
       </c>
       <c r="G196" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H196" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I196" s="97"/>
     </row>
     <row r="197" ht="16.5" customHeight="1" spans="1:9">
       <c r="A197" s="89" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B197" s="89"/>
       <c r="C197" s="89"/>
@@ -7740,13 +7743,13 @@
         <v>161</v>
       </c>
       <c r="C198" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D198" s="93" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E198" s="94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F198" s="94">
         <v>33</v>
@@ -7755,7 +7758,7 @@
         <v>16</v>
       </c>
       <c r="H198" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I198" s="97"/>
     </row>
@@ -7765,13 +7768,13 @@
         <v>162</v>
       </c>
       <c r="C199" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D199" s="99" t="s">
+        <v>261</v>
+      </c>
+      <c r="E199" s="94" t="s">
         <v>260</v>
-      </c>
-      <c r="E199" s="94" t="s">
-        <v>259</v>
       </c>
       <c r="F199" s="94">
         <v>33</v>
@@ -7780,7 +7783,7 @@
         <v>19</v>
       </c>
       <c r="H199" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I199" s="100"/>
     </row>
@@ -7790,13 +7793,13 @@
         <v>163</v>
       </c>
       <c r="C200" s="92" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D200" s="93" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E200" s="94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F200" s="94">
         <v>33</v>
@@ -7805,7 +7808,7 @@
         <v>21</v>
       </c>
       <c r="H200" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I200" s="97"/>
     </row>
@@ -7815,22 +7818,22 @@
         <v>164</v>
       </c>
       <c r="C201" s="92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D201" s="99" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E201" s="94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F201" s="94">
         <v>33</v>
       </c>
       <c r="G201" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H201" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I201" s="100"/>
     </row>
@@ -7840,28 +7843,28 @@
         <v>165</v>
       </c>
       <c r="C202" s="92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D202" s="93" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E202" s="94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F202" s="94">
         <v>33</v>
       </c>
       <c r="G202" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H202" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I202" s="97"/>
     </row>
     <row r="203" ht="16.5" customHeight="1" spans="1:9">
       <c r="A203" s="102" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B203" s="102"/>
       <c r="C203" s="102"/>
@@ -7878,13 +7881,13 @@
         <v>166</v>
       </c>
       <c r="C204" s="92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D204" s="93" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E204" s="94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F204" s="94">
         <v>34</v>
@@ -7893,7 +7896,7 @@
         <v>16</v>
       </c>
       <c r="H204" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I204" s="97"/>
     </row>
@@ -7903,13 +7906,13 @@
         <v>167</v>
       </c>
       <c r="C205" s="92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D205" s="99" t="s">
+        <v>269</v>
+      </c>
+      <c r="E205" s="94" t="s">
         <v>268</v>
-      </c>
-      <c r="E205" s="94" t="s">
-        <v>267</v>
       </c>
       <c r="F205" s="94">
         <v>34</v>
@@ -7918,7 +7921,7 @@
         <v>19</v>
       </c>
       <c r="H205" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I205" s="100"/>
     </row>
@@ -7928,13 +7931,13 @@
         <v>168</v>
       </c>
       <c r="C206" s="92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D206" s="93" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E206" s="94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F206" s="94">
         <v>34</v>
@@ -7943,7 +7946,7 @@
         <v>21</v>
       </c>
       <c r="H206" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I206" s="97"/>
     </row>
@@ -7953,22 +7956,22 @@
         <v>169</v>
       </c>
       <c r="C207" s="92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D207" s="99" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E207" s="94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F207" s="94">
         <v>34</v>
       </c>
       <c r="G207" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H207" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I207" s="100"/>
     </row>
@@ -7978,28 +7981,28 @@
         <v>170</v>
       </c>
       <c r="C208" s="92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D208" s="93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E208" s="94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F208" s="94">
         <v>34</v>
       </c>
       <c r="G208" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H208" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I208" s="97"/>
     </row>
     <row r="209" ht="16.5" customHeight="1" spans="1:9">
       <c r="A209" s="104" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B209" s="104"/>
       <c r="C209" s="104"/>
@@ -8016,13 +8019,13 @@
         <v>171</v>
       </c>
       <c r="C210" s="92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D210" s="93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E210" s="94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F210" s="94">
         <v>35</v>
@@ -8031,7 +8034,7 @@
         <v>16</v>
       </c>
       <c r="H210" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I210" s="97"/>
     </row>
@@ -8041,13 +8044,13 @@
         <v>172</v>
       </c>
       <c r="C211" s="92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D211" s="99" t="s">
+        <v>277</v>
+      </c>
+      <c r="E211" s="94" t="s">
         <v>276</v>
-      </c>
-      <c r="E211" s="94" t="s">
-        <v>275</v>
       </c>
       <c r="F211" s="94">
         <v>35</v>
@@ -8056,7 +8059,7 @@
         <v>19</v>
       </c>
       <c r="H211" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I211" s="100"/>
     </row>
@@ -8066,13 +8069,13 @@
         <v>173</v>
       </c>
       <c r="C212" s="92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D212" s="93" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E212" s="94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F212" s="94">
         <v>35</v>
@@ -8081,7 +8084,7 @@
         <v>21</v>
       </c>
       <c r="H212" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I212" s="97"/>
     </row>
@@ -8091,22 +8094,22 @@
         <v>174</v>
       </c>
       <c r="C213" s="92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D213" s="99" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E213" s="94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F213" s="94">
         <v>35</v>
       </c>
       <c r="G213" s="95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H213" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I213" s="100"/>
     </row>
@@ -8116,28 +8119,28 @@
         <v>175</v>
       </c>
       <c r="C214" s="92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D214" s="93" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E214" s="94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F214" s="94">
         <v>35</v>
       </c>
       <c r="G214" s="95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H214" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I214" s="97"/>
     </row>
     <row r="215" ht="16.5" customHeight="1" spans="1:9">
       <c r="A215" s="104" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B215" s="104"/>
       <c r="C215" s="104"/>
@@ -8154,13 +8157,13 @@
         <v>176</v>
       </c>
       <c r="C216" s="92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D216" s="93" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E216" s="94" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F216" s="94">
         <v>36</v>
@@ -8169,7 +8172,7 @@
         <v>16</v>
       </c>
       <c r="H216" s="96" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I216" s="97"/>
     </row>
@@ -8241,7 +8244,7 @@
   <sheetData>
     <row r="1" ht="25.9" spans="1:10">
       <c r="A1" s="42" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -8255,19 +8258,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="C4" s="43" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D4" s="43"/>
       <c r="E4" s="44" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="45" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H4" s="45"/>
       <c r="I4" s="46" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J4" s="46"/>
     </row>
@@ -8283,12 +8286,12 @@
     </row>
     <row r="6" ht="32.8" spans="1:10">
       <c r="C6" s="47" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D6" s="47"/>
       <c r="E6" s="48">
         <f>COUNTIF('📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="49">
@@ -8298,13 +8301,13 @@
       <c r="H6" s="49"/>
       <c r="I6" s="50">
         <f>COUNTIF('📚 Study Plan'!H:H,"⬜ Not Started")</f>
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J6" s="50"/>
     </row>
     <row r="8" spans="1:10">
       <c r="C8" s="51" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D8" s="51"/>
       <c r="E8" s="51"/>
@@ -8317,7 +8320,7 @@
     <row r="9" ht="35.1" spans="1:10">
       <c r="C9" s="52">
         <f>COUNTIF('📚 Study Plan'!H:H,"✅ Done")/176</f>
-        <v>0</v>
+        <v>0.0113636363636364</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -8329,7 +8332,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="C11" s="51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
@@ -8344,22 +8347,22 @@
         <v>5</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H12" s="53" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I12" s="53" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J12" s="53"/>
     </row>
@@ -8372,7 +8375,7 @@
       </c>
       <c r="E13" s="55">
         <f>COUNTIFS('📚 Study Plan'!C:C,C13,'📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="56">
         <f>COUNTIFS('📚 Study Plan'!C:C,C13,'📚 Study Plan'!H:H,"🔄 In Progress")</f>
@@ -8388,13 +8391,13 @@
       </c>
       <c r="I13" s="59">
         <f t="shared" ref="I13:I30" si="0">D13-E13-F13-G13-H13</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J13" s="59"/>
     </row>
     <row r="14" ht="24.2" spans="1:10">
       <c r="C14" s="60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="9">
         <v>7</v>
@@ -8423,7 +8426,7 @@
     </row>
     <row r="15" ht="36.3" spans="1:10">
       <c r="C15" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" s="5">
         <v>19</v>
@@ -8452,7 +8455,7 @@
     </row>
     <row r="16" ht="24.2" spans="1:10">
       <c r="C16" s="67" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D16" s="9">
         <v>12</v>
@@ -8481,7 +8484,7 @@
     </row>
     <row r="17" ht="24.2" spans="3:10">
       <c r="C17" s="68" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" s="5">
         <v>17</v>
@@ -8510,7 +8513,7 @@
     </row>
     <row r="18" ht="24.2" spans="3:10">
       <c r="C18" s="69" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D18" s="9">
         <v>11</v>
@@ -8539,7 +8542,7 @@
     </row>
     <row r="19" ht="24.2" spans="3:10">
       <c r="C19" s="70" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D19" s="5">
         <v>8</v>
@@ -8568,7 +8571,7 @@
     </row>
     <row r="20" ht="24.2" spans="3:10">
       <c r="C20" s="71" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D20" s="9">
         <v>7</v>
@@ -8597,7 +8600,7 @@
     </row>
     <row r="21" ht="24.2" spans="3:10">
       <c r="C21" s="72" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D21" s="5">
         <v>9</v>
@@ -8626,7 +8629,7 @@
     </row>
     <row r="22" ht="24.2" spans="3:10">
       <c r="C22" s="73" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D22" s="9">
         <v>5</v>
@@ -8655,7 +8658,7 @@
     </row>
     <row r="23" ht="24.2" spans="3:10">
       <c r="C23" s="74" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D23" s="5">
         <v>9</v>
@@ -8684,7 +8687,7 @@
     </row>
     <row r="24" ht="24.2" spans="3:10">
       <c r="C24" s="75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D24" s="9">
         <v>14</v>
@@ -8713,7 +8716,7 @@
     </row>
     <row r="25" spans="3:10">
       <c r="C25" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D25" s="5">
         <v>5</v>
@@ -8742,7 +8745,7 @@
     </row>
     <row r="26" ht="24.2" spans="3:10">
       <c r="C26" s="77" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D26" s="9">
         <v>5</v>
@@ -8771,7 +8774,7 @@
     </row>
     <row r="27" ht="24.2" spans="3:10">
       <c r="C27" s="78" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D27" s="5">
         <v>6</v>
@@ -8800,7 +8803,7 @@
     </row>
     <row r="28" ht="24.2" spans="3:10">
       <c r="C28" s="54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D28" s="9">
         <v>10</v>
@@ -8829,7 +8832,7 @@
     </row>
     <row r="29" ht="24.2" spans="3:10">
       <c r="C29" s="60" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D29" s="5">
         <v>7</v>
@@ -8858,7 +8861,7 @@
     </row>
     <row r="30" ht="24.2" spans="3:10">
       <c r="C30" s="66" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D30" s="9">
         <v>6</v>
@@ -8887,7 +8890,7 @@
     </row>
     <row r="31" spans="3:10">
       <c r="C31" s="41" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D31" s="41">
         <f t="shared" ref="D31:I31" si="1">SUM(D13:D30)</f>
@@ -8895,7 +8898,7 @@
       </c>
       <c r="E31" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" s="41">
         <f t="shared" si="1"/>
@@ -8911,13 +8914,13 @@
       </c>
       <c r="I31" s="41">
         <f t="shared" si="1"/>
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J31" s="41"/>
     </row>
     <row r="33" spans="3:10">
       <c r="C33" s="79" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D33" s="79"/>
       <c r="E33" s="79"/>
@@ -8983,7 +8986,7 @@
   <sheetData>
     <row r="1" ht="20.7" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8996,13 +8999,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -9017,13 +9020,13 @@
         <v>4</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7"/>
       <c r="B4" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="9">
         <v>7</v>
@@ -9032,13 +9035,13 @@
         <v>2</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" ht="24.2" spans="1:5">
       <c r="A5" s="11"/>
       <c r="B5" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="5">
         <v>19</v>
@@ -9047,13 +9050,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="9">
         <v>12</v>
@@ -9062,13 +9065,13 @@
         <v>3</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="15"/>
       <c r="B7" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="5">
         <v>17</v>
@@ -9077,13 +9080,13 @@
         <v>4</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="9">
         <v>11</v>
@@ -9092,13 +9095,13 @@
         <v>3</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="19"/>
       <c r="B9" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C9" s="5">
         <v>8</v>
@@ -9107,13 +9110,13 @@
         <v>2</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="21"/>
       <c r="B10" s="22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C10" s="9">
         <v>7</v>
@@ -9122,13 +9125,13 @@
         <v>2</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="23"/>
       <c r="B11" s="24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" s="5">
         <v>9</v>
@@ -9137,13 +9140,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="25"/>
       <c r="B12" s="26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C12" s="9">
         <v>5</v>
@@ -9152,13 +9155,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="27"/>
       <c r="B13" s="28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C13" s="5">
         <v>9</v>
@@ -9167,13 +9170,13 @@
         <v>2</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="29"/>
       <c r="B14" s="30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C14" s="9">
         <v>14</v>
@@ -9182,13 +9185,13 @@
         <v>3</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="31"/>
       <c r="B15" s="32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C15" s="5">
         <v>5</v>
@@ -9197,13 +9200,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="33"/>
       <c r="B16" s="34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C16" s="9">
         <v>5</v>
@@ -9212,13 +9215,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="35"/>
       <c r="B17" s="36" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C17" s="5">
         <v>6</v>
@@ -9227,13 +9230,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3"/>
       <c r="B18" s="37" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C18" s="9">
         <v>10</v>
@@ -9242,13 +9245,13 @@
         <v>2</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7"/>
       <c r="B19" s="38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C19" s="5">
         <v>7</v>
@@ -9257,13 +9260,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="11"/>
       <c r="B20" s="39" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C20" s="9">
         <v>6</v>
@@ -9272,13 +9275,13 @@
         <v>2</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="40"/>
       <c r="B21" s="41" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C21" s="41">
         <v>176</v>

--- a/01.Study Plan/02_aspnet_study_plan_v2.xlsx
+++ b/01.Study Plan/02_aspnet_study_plan_v2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="322">
   <si>
     <t>🎯  ASP.NET Core Web API — Complete Study Plan</t>
   </si>
@@ -97,76 +97,79 @@
     <t>3/5</t>
   </si>
   <si>
+    <t>❌ Skipped</t>
+  </si>
+  <si>
+    <t>How to Test ASP.NET Core Web API Using Postman</t>
+  </si>
+  <si>
+    <t>4/5</t>
+  </si>
+  <si>
+    <t>Creating ASP.NET Core Web API Project in Visual Studio</t>
+  </si>
+  <si>
+    <t>5/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 2  —  Tuesday, 19 May 2026   ·   Topics 6 – 10</t>
+  </si>
+  <si>
+    <t>Default ASP.NET Core Web API Files and Folders</t>
+  </si>
+  <si>
+    <t>19-May-2026</t>
+  </si>
+  <si>
+    <t>ASP.NET Core Web API Project File</t>
+  </si>
+  <si>
+    <t>ASP.NET Core Web API Main Method</t>
+  </si>
+  <si>
+    <t>Controllers in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>Models in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 3  —  Wednesday, 20 May 2026   ·   Topics 11 – 15</t>
+  </si>
+  <si>
+    <t>Services in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>20-May-2026</t>
+  </si>
+  <si>
+    <t>ASP.NET Core Web API AppSettings.json file</t>
+  </si>
+  <si>
+    <t>ASP.NET Core In-Process Hosting Model</t>
+  </si>
+  <si>
+    <t>ASP.NET Core Kestrel Web Server</t>
+  </si>
+  <si>
+    <t>ASP.NET Core Out of Process Hosting Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 4  —  Thursday, 21 May 2026   ·   Topics 16 – 20</t>
+  </si>
+  <si>
+    <t>Hosting Model Interview Questions and Answers</t>
+  </si>
+  <si>
+    <t>21-May-2026</t>
+  </si>
+  <si>
+    <t>Dependency Injection in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>Singleton vs Scoped vs Transient in ASP.NET Core Web API</t>
+  </si>
+  <si>
     <t>⬜ Not Started</t>
-  </si>
-  <si>
-    <t>How to Test ASP.NET Core Web API Using Postman</t>
-  </si>
-  <si>
-    <t>4/5</t>
-  </si>
-  <si>
-    <t>Creating ASP.NET Core Web API Project in Visual Studio</t>
-  </si>
-  <si>
-    <t>5/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 2  —  Tuesday, 19 May 2026   ·   Topics 6 – 10</t>
-  </si>
-  <si>
-    <t>Default ASP.NET Core Web API Files and Folders</t>
-  </si>
-  <si>
-    <t>19-May-2026</t>
-  </si>
-  <si>
-    <t>ASP.NET Core Web API Project File</t>
-  </si>
-  <si>
-    <t>ASP.NET Core Web API Main Method</t>
-  </si>
-  <si>
-    <t>Controllers in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>Models in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 3  —  Wednesday, 20 May 2026   ·   Topics 11 – 15</t>
-  </si>
-  <si>
-    <t>Services in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>20-May-2026</t>
-  </si>
-  <si>
-    <t>ASP.NET Core Web API AppSettings.json file</t>
-  </si>
-  <si>
-    <t>ASP.NET Core In-Process Hosting Model</t>
-  </si>
-  <si>
-    <t>ASP.NET Core Kestrel Web Server</t>
-  </si>
-  <si>
-    <t>ASP.NET Core Out of Process Hosting Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 4  —  Thursday, 21 May 2026   ·   Topics 16 – 20</t>
-  </si>
-  <si>
-    <t>Hosting Model Interview Questions and Answers</t>
-  </si>
-  <si>
-    <t>21-May-2026</t>
-  </si>
-  <si>
-    <t>Dependency Injection in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>Singleton vs Scoped vs Transient in ASP.NET Core Web API</t>
   </si>
   <si>
     <t>Swagger API in ASP.NET Core Web API</t>
@@ -1416,7 +1419,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="64">
+  <fills count="65">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1599,7 +1602,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF2F8"/>
+        <fgColor rgb="FF00B050"/>
         <bgColor rgb="FFFAFAFA"/>
       </patternFill>
     </fill>
@@ -1607,6 +1610,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFAFAFA"/>
         <bgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF2F8"/>
+        <bgColor rgb="FFFAFAFA"/>
       </patternFill>
     </fill>
     <fill>
@@ -2227,7 +2236,7 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="33" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="34" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2251,16 +2260,16 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="35" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="35" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="35" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="36" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="36" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="37" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2269,89 +2278,89 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="53" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="54" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="55" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="57" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="57" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="57" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="57" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="57" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="57" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2620,6 +2629,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2757,7 +2769,17 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2951,25 +2973,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3391,7 +3413,7 @@
       <c r="G8" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="96" t="s">
+      <c r="H8" s="101" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="97"/>
@@ -3416,7 +3438,7 @@
       <c r="G9" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="96" t="s">
+      <c r="H9" s="101" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="100"/>
@@ -3441,7 +3463,7 @@
       <c r="G10" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="96" t="s">
+      <c r="H10" s="101" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="97"/>
@@ -3480,7 +3502,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I12" s="97"/>
     </row>
@@ -3505,7 +3527,7 @@
         <v>19</v>
       </c>
       <c r="H13" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I13" s="100"/>
     </row>
@@ -3530,7 +3552,7 @@
         <v>21</v>
       </c>
       <c r="H14" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I14" s="97"/>
     </row>
@@ -3555,7 +3577,7 @@
         <v>24</v>
       </c>
       <c r="H15" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I15" s="100"/>
     </row>
@@ -3580,7 +3602,7 @@
         <v>26</v>
       </c>
       <c r="H16" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I16" s="97"/>
     </row>
@@ -3618,7 +3640,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I18" s="97"/>
     </row>
@@ -3643,7 +3665,7 @@
         <v>19</v>
       </c>
       <c r="H19" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I19" s="100"/>
     </row>
@@ -3668,7 +3690,7 @@
         <v>21</v>
       </c>
       <c r="H20" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I20" s="97"/>
     </row>
@@ -3693,7 +3715,7 @@
         <v>24</v>
       </c>
       <c r="H21" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I21" s="100"/>
     </row>
@@ -3718,7 +3740,7 @@
         <v>26</v>
       </c>
       <c r="H22" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I22" s="97"/>
     </row>
@@ -3755,7 +3777,7 @@
       <c r="G24" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="96" t="s">
+      <c r="H24" s="101" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="97"/>
@@ -3781,7 +3803,7 @@
         <v>19</v>
       </c>
       <c r="H25" s="96" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I25" s="100"/>
     </row>
@@ -3805,8 +3827,8 @@
       <c r="G26" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="96" t="s">
-        <v>22</v>
+      <c r="H26" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I26" s="97"/>
     </row>
@@ -3819,7 +3841,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="99" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" s="94" t="s">
         <v>43</v>
@@ -3830,21 +3852,21 @@
       <c r="G27" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H27" s="96" t="s">
-        <v>22</v>
+      <c r="H27" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I27" s="100"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:9">
-      <c r="A28" s="101"/>
+      <c r="A28" s="102"/>
       <c r="B28" s="91">
         <v>20</v>
       </c>
       <c r="C28" s="92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D28" s="93" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" s="94" t="s">
         <v>43</v>
@@ -3855,37 +3877,37 @@
       <c r="G28" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="96" t="s">
-        <v>22</v>
+      <c r="H28" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I28" s="97"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A29" s="102" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="102"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="102"/>
-      <c r="F29" s="102"/>
-      <c r="G29" s="102"/>
-      <c r="H29" s="102"/>
-      <c r="I29" s="102"/>
+      <c r="A29" s="103" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="103"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="103"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:9">
-      <c r="A30" s="101"/>
+      <c r="A30" s="102"/>
       <c r="B30" s="91">
         <v>21</v>
       </c>
       <c r="C30" s="92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D30" s="93" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F30" s="94">
         <v>5</v>
@@ -3893,24 +3915,24 @@
       <c r="G30" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H30" s="96" t="s">
-        <v>22</v>
+      <c r="H30" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I30" s="97"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:9">
-      <c r="A31" s="101"/>
+      <c r="A31" s="102"/>
       <c r="B31" s="98">
         <v>22</v>
       </c>
       <c r="C31" s="92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D31" s="99" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="94" t="s">
         <v>52</v>
-      </c>
-      <c r="E31" s="94" t="s">
-        <v>51</v>
       </c>
       <c r="F31" s="94">
         <v>5</v>
@@ -3918,24 +3940,24 @@
       <c r="G31" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H31" s="96" t="s">
-        <v>22</v>
+      <c r="H31" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I31" s="100"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:9">
-      <c r="A32" s="101"/>
+      <c r="A32" s="102"/>
       <c r="B32" s="91">
         <v>23</v>
       </c>
       <c r="C32" s="92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D32" s="93" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E32" s="94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F32" s="94">
         <v>5</v>
@@ -3943,24 +3965,24 @@
       <c r="G32" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="96" t="s">
-        <v>22</v>
+      <c r="H32" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I32" s="97"/>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:9">
-      <c r="A33" s="101"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="98">
         <v>24</v>
       </c>
       <c r="C33" s="92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D33" s="99" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E33" s="94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F33" s="94">
         <v>5</v>
@@ -3968,24 +3990,24 @@
       <c r="G33" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H33" s="96" t="s">
-        <v>22</v>
+      <c r="H33" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I33" s="100"/>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:9">
-      <c r="A34" s="101"/>
+      <c r="A34" s="102"/>
       <c r="B34" s="91">
         <v>25</v>
       </c>
       <c r="C34" s="92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D34" s="93" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E34" s="94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F34" s="94">
         <v>5</v>
@@ -3993,37 +4015,37 @@
       <c r="G34" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H34" s="96" t="s">
-        <v>22</v>
+      <c r="H34" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I34" s="97"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A35" s="102" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="102"/>
-      <c r="C35" s="102"/>
-      <c r="D35" s="102"/>
-      <c r="E35" s="102"/>
-      <c r="F35" s="102"/>
-      <c r="G35" s="102"/>
-      <c r="H35" s="102"/>
-      <c r="I35" s="102"/>
+      <c r="A35" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="103"/>
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="103"/>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:9">
-      <c r="A36" s="101"/>
+      <c r="A36" s="102"/>
       <c r="B36" s="91">
         <v>26</v>
       </c>
       <c r="C36" s="92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D36" s="93" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E36" s="94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F36" s="94">
         <v>6</v>
@@ -4031,24 +4053,24 @@
       <c r="G36" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H36" s="96" t="s">
-        <v>22</v>
+      <c r="H36" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I36" s="97"/>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:9">
-      <c r="A37" s="103"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="98">
         <v>27</v>
       </c>
       <c r="C37" s="92" t="s">
+        <v>60</v>
+      </c>
+      <c r="D37" s="99" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="94" t="s">
         <v>59</v>
-      </c>
-      <c r="D37" s="99" t="s">
-        <v>60</v>
-      </c>
-      <c r="E37" s="94" t="s">
-        <v>58</v>
       </c>
       <c r="F37" s="94">
         <v>6</v>
@@ -4056,24 +4078,24 @@
       <c r="G37" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H37" s="96" t="s">
-        <v>22</v>
+      <c r="H37" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I37" s="100"/>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:9">
-      <c r="A38" s="103"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="91">
         <v>28</v>
       </c>
       <c r="C38" s="92" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="94" t="s">
         <v>59</v>
-      </c>
-      <c r="D38" s="93" t="s">
-        <v>61</v>
-      </c>
-      <c r="E38" s="94" t="s">
-        <v>58</v>
       </c>
       <c r="F38" s="94">
         <v>6</v>
@@ -4081,24 +4103,24 @@
       <c r="G38" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H38" s="96" t="s">
-        <v>22</v>
+      <c r="H38" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I38" s="97"/>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:9">
-      <c r="A39" s="103"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="98">
         <v>29</v>
       </c>
       <c r="C39" s="92" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" s="99" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="94" t="s">
         <v>59</v>
-      </c>
-      <c r="D39" s="99" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" s="94" t="s">
-        <v>58</v>
       </c>
       <c r="F39" s="94">
         <v>6</v>
@@ -4106,24 +4128,24 @@
       <c r="G39" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="96" t="s">
-        <v>22</v>
+      <c r="H39" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I39" s="100"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:9">
-      <c r="A40" s="103"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="91">
         <v>30</v>
       </c>
       <c r="C40" s="92" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="94" t="s">
         <v>59</v>
-      </c>
-      <c r="D40" s="93" t="s">
-        <v>63</v>
-      </c>
-      <c r="E40" s="94" t="s">
-        <v>58</v>
       </c>
       <c r="F40" s="94">
         <v>6</v>
@@ -4131,37 +4153,37 @@
       <c r="G40" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H40" s="96" t="s">
-        <v>22</v>
+      <c r="H40" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I40" s="97"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A41" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" s="104"/>
-      <c r="C41" s="104"/>
-      <c r="D41" s="104"/>
-      <c r="E41" s="104"/>
-      <c r="F41" s="104"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="104"/>
-      <c r="I41" s="104"/>
+      <c r="A41" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="105"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
     </row>
     <row r="42" ht="18" customHeight="1" spans="1:9">
-      <c r="A42" s="103"/>
+      <c r="A42" s="104"/>
       <c r="B42" s="91">
         <v>31</v>
       </c>
       <c r="C42" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D42" s="93" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E42" s="94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F42" s="94">
         <v>7</v>
@@ -4169,24 +4191,24 @@
       <c r="G42" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="96" t="s">
-        <v>22</v>
+      <c r="H42" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I42" s="97"/>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:9">
-      <c r="A43" s="103"/>
+      <c r="A43" s="104"/>
       <c r="B43" s="98">
         <v>32</v>
       </c>
       <c r="C43" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D43" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="94" t="s">
         <v>67</v>
-      </c>
-      <c r="E43" s="94" t="s">
-        <v>66</v>
       </c>
       <c r="F43" s="94">
         <v>7</v>
@@ -4194,24 +4216,24 @@
       <c r="G43" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H43" s="96" t="s">
-        <v>22</v>
+      <c r="H43" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I43" s="100"/>
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:9">
-      <c r="A44" s="103"/>
+      <c r="A44" s="104"/>
       <c r="B44" s="91">
         <v>33</v>
       </c>
       <c r="C44" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D44" s="93" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E44" s="94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F44" s="94">
         <v>7</v>
@@ -4219,24 +4241,24 @@
       <c r="G44" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H44" s="96" t="s">
-        <v>22</v>
+      <c r="H44" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I44" s="97"/>
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:9">
-      <c r="A45" s="103"/>
+      <c r="A45" s="104"/>
       <c r="B45" s="98">
         <v>34</v>
       </c>
       <c r="C45" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D45" s="99" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E45" s="94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F45" s="94">
         <v>7</v>
@@ -4244,24 +4266,24 @@
       <c r="G45" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="96" t="s">
-        <v>22</v>
+      <c r="H45" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I45" s="100"/>
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:9">
-      <c r="A46" s="103"/>
+      <c r="A46" s="104"/>
       <c r="B46" s="91">
         <v>35</v>
       </c>
       <c r="C46" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D46" s="93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E46" s="94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F46" s="94">
         <v>7</v>
@@ -4269,37 +4291,37 @@
       <c r="G46" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H46" s="96" t="s">
-        <v>22</v>
+      <c r="H46" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I46" s="97"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A47" s="104" t="s">
-        <v>71</v>
-      </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
+      <c r="A47" s="105" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="105"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="105"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="105"/>
+      <c r="H47" s="105"/>
+      <c r="I47" s="105"/>
     </row>
     <row r="48" ht="18" customHeight="1" spans="1:9">
-      <c r="A48" s="103"/>
+      <c r="A48" s="104"/>
       <c r="B48" s="91">
         <v>36</v>
       </c>
       <c r="C48" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D48" s="93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E48" s="94" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F48" s="94">
         <v>8</v>
@@ -4307,24 +4329,24 @@
       <c r="G48" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="96" t="s">
-        <v>22</v>
+      <c r="H48" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I48" s="97"/>
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:9">
-      <c r="A49" s="103"/>
+      <c r="A49" s="104"/>
       <c r="B49" s="98">
         <v>37</v>
       </c>
       <c r="C49" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D49" s="99" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="94" t="s">
         <v>74</v>
-      </c>
-      <c r="E49" s="94" t="s">
-        <v>73</v>
       </c>
       <c r="F49" s="94">
         <v>8</v>
@@ -4332,24 +4354,24 @@
       <c r="G49" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H49" s="96" t="s">
-        <v>22</v>
+      <c r="H49" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I49" s="100"/>
     </row>
     <row r="50" ht="18" customHeight="1" spans="1:9">
-      <c r="A50" s="103"/>
+      <c r="A50" s="104"/>
       <c r="B50" s="91">
         <v>38</v>
       </c>
       <c r="C50" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D50" s="93" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E50" s="94" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F50" s="94">
         <v>8</v>
@@ -4357,24 +4379,24 @@
       <c r="G50" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H50" s="96" t="s">
-        <v>22</v>
+      <c r="H50" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I50" s="97"/>
     </row>
     <row r="51" ht="18" customHeight="1" spans="1:9">
-      <c r="A51" s="103"/>
+      <c r="A51" s="104"/>
       <c r="B51" s="98">
         <v>39</v>
       </c>
       <c r="C51" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D51" s="99" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E51" s="94" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F51" s="94">
         <v>8</v>
@@ -4382,24 +4404,24 @@
       <c r="G51" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="96" t="s">
-        <v>22</v>
+      <c r="H51" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I51" s="100"/>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:9">
-      <c r="A52" s="103"/>
+      <c r="A52" s="104"/>
       <c r="B52" s="91">
         <v>40</v>
       </c>
       <c r="C52" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D52" s="93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E52" s="94" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F52" s="94">
         <v>8</v>
@@ -4407,37 +4429,37 @@
       <c r="G52" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H52" s="96" t="s">
-        <v>22</v>
+      <c r="H52" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I52" s="97"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A53" s="104" t="s">
-        <v>78</v>
-      </c>
-      <c r="B53" s="104"/>
-      <c r="C53" s="104"/>
-      <c r="D53" s="104"/>
-      <c r="E53" s="104"/>
-      <c r="F53" s="104"/>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="104"/>
+      <c r="A53" s="105" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="105"/>
+      <c r="C53" s="105"/>
+      <c r="D53" s="105"/>
+      <c r="E53" s="105"/>
+      <c r="F53" s="105"/>
+      <c r="G53" s="105"/>
+      <c r="H53" s="105"/>
+      <c r="I53" s="105"/>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:9">
-      <c r="A54" s="103"/>
+      <c r="A54" s="104"/>
       <c r="B54" s="91">
         <v>41</v>
       </c>
       <c r="C54" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D54" s="93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E54" s="94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54" s="94">
         <v>9</v>
@@ -4445,24 +4467,24 @@
       <c r="G54" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H54" s="96" t="s">
-        <v>22</v>
+      <c r="H54" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I54" s="97"/>
     </row>
     <row r="55" ht="18" customHeight="1" spans="1:9">
-      <c r="A55" s="103"/>
+      <c r="A55" s="104"/>
       <c r="B55" s="98">
         <v>42</v>
       </c>
       <c r="C55" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D55" s="99" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="94" t="s">
         <v>81</v>
-      </c>
-      <c r="E55" s="94" t="s">
-        <v>80</v>
       </c>
       <c r="F55" s="94">
         <v>9</v>
@@ -4470,24 +4492,24 @@
       <c r="G55" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H55" s="96" t="s">
-        <v>22</v>
+      <c r="H55" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I55" s="100"/>
     </row>
     <row r="56" ht="18" customHeight="1" spans="1:9">
-      <c r="A56" s="103"/>
+      <c r="A56" s="104"/>
       <c r="B56" s="91">
         <v>43</v>
       </c>
       <c r="C56" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D56" s="93" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E56" s="94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F56" s="94">
         <v>9</v>
@@ -4495,24 +4517,24 @@
       <c r="G56" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H56" s="96" t="s">
-        <v>22</v>
+      <c r="H56" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I56" s="97"/>
     </row>
     <row r="57" ht="18" customHeight="1" spans="1:9">
-      <c r="A57" s="103"/>
+      <c r="A57" s="104"/>
       <c r="B57" s="98">
         <v>44</v>
       </c>
       <c r="C57" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D57" s="99" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E57" s="94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F57" s="94">
         <v>9</v>
@@ -4520,24 +4542,24 @@
       <c r="G57" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H57" s="96" t="s">
-        <v>22</v>
+      <c r="H57" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I57" s="100"/>
     </row>
     <row r="58" ht="18" customHeight="1" spans="1:9">
-      <c r="A58" s="103"/>
+      <c r="A58" s="104"/>
       <c r="B58" s="91">
         <v>45</v>
       </c>
       <c r="C58" s="92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D58" s="93" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E58" s="94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F58" s="94">
         <v>9</v>
@@ -4545,37 +4567,37 @@
       <c r="G58" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H58" s="96" t="s">
-        <v>22</v>
+      <c r="H58" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I58" s="97"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A59" s="105" t="s">
-        <v>85</v>
-      </c>
-      <c r="B59" s="105"/>
-      <c r="C59" s="105"/>
-      <c r="D59" s="105"/>
-      <c r="E59" s="105"/>
-      <c r="F59" s="105"/>
-      <c r="G59" s="105"/>
-      <c r="H59" s="105"/>
-      <c r="I59" s="105"/>
+      <c r="A59" s="106" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" s="106"/>
+      <c r="C59" s="106"/>
+      <c r="D59" s="106"/>
+      <c r="E59" s="106"/>
+      <c r="F59" s="106"/>
+      <c r="G59" s="106"/>
+      <c r="H59" s="106"/>
+      <c r="I59" s="106"/>
     </row>
     <row r="60" ht="18" customHeight="1" spans="1:9">
-      <c r="A60" s="106"/>
+      <c r="A60" s="107"/>
       <c r="B60" s="91">
         <v>46</v>
       </c>
       <c r="C60" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D60" s="93" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E60" s="94" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F60" s="94">
         <v>10</v>
@@ -4583,24 +4605,24 @@
       <c r="G60" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H60" s="96" t="s">
-        <v>22</v>
+      <c r="H60" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I60" s="97"/>
     </row>
     <row r="61" ht="18" customHeight="1" spans="1:9">
-      <c r="A61" s="106"/>
+      <c r="A61" s="107"/>
       <c r="B61" s="98">
         <v>47</v>
       </c>
       <c r="C61" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D61" s="99" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" s="94" t="s">
         <v>89</v>
-      </c>
-      <c r="E61" s="94" t="s">
-        <v>88</v>
       </c>
       <c r="F61" s="94">
         <v>10</v>
@@ -4608,24 +4630,24 @@
       <c r="G61" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H61" s="96" t="s">
-        <v>22</v>
+      <c r="H61" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I61" s="100"/>
     </row>
     <row r="62" ht="18" customHeight="1" spans="1:9">
-      <c r="A62" s="106"/>
+      <c r="A62" s="107"/>
       <c r="B62" s="91">
         <v>48</v>
       </c>
       <c r="C62" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D62" s="93" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E62" s="94" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F62" s="94">
         <v>10</v>
@@ -4633,24 +4655,24 @@
       <c r="G62" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H62" s="96" t="s">
-        <v>22</v>
+      <c r="H62" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I62" s="97"/>
     </row>
     <row r="63" ht="18" customHeight="1" spans="1:9">
-      <c r="A63" s="106"/>
+      <c r="A63" s="107"/>
       <c r="B63" s="98">
         <v>49</v>
       </c>
       <c r="C63" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D63" s="99" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E63" s="94" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F63" s="94">
         <v>10</v>
@@ -4658,24 +4680,24 @@
       <c r="G63" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H63" s="96" t="s">
-        <v>22</v>
+      <c r="H63" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I63" s="100"/>
     </row>
     <row r="64" ht="18" customHeight="1" spans="1:9">
-      <c r="A64" s="106"/>
+      <c r="A64" s="107"/>
       <c r="B64" s="91">
         <v>50</v>
       </c>
       <c r="C64" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D64" s="93" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E64" s="94" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F64" s="94">
         <v>10</v>
@@ -4683,37 +4705,37 @@
       <c r="G64" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H64" s="96" t="s">
-        <v>22</v>
+      <c r="H64" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I64" s="97"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A65" s="105" t="s">
-        <v>93</v>
-      </c>
-      <c r="B65" s="105"/>
-      <c r="C65" s="105"/>
-      <c r="D65" s="105"/>
-      <c r="E65" s="105"/>
-      <c r="F65" s="105"/>
-      <c r="G65" s="105"/>
-      <c r="H65" s="105"/>
-      <c r="I65" s="105"/>
+      <c r="A65" s="106" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" s="106"/>
+      <c r="C65" s="106"/>
+      <c r="D65" s="106"/>
+      <c r="E65" s="106"/>
+      <c r="F65" s="106"/>
+      <c r="G65" s="106"/>
+      <c r="H65" s="106"/>
+      <c r="I65" s="106"/>
     </row>
     <row r="66" ht="18" customHeight="1" spans="1:9">
-      <c r="A66" s="106"/>
+      <c r="A66" s="107"/>
       <c r="B66" s="91">
         <v>51</v>
       </c>
       <c r="C66" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D66" s="93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E66" s="94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F66" s="94">
         <v>11</v>
@@ -4721,24 +4743,24 @@
       <c r="G66" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H66" s="96" t="s">
-        <v>22</v>
+      <c r="H66" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I66" s="97"/>
     </row>
     <row r="67" ht="18" customHeight="1" spans="1:9">
-      <c r="A67" s="106"/>
+      <c r="A67" s="107"/>
       <c r="B67" s="98">
         <v>52</v>
       </c>
       <c r="C67" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D67" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="E67" s="94" t="s">
         <v>96</v>
-      </c>
-      <c r="E67" s="94" t="s">
-        <v>95</v>
       </c>
       <c r="F67" s="94">
         <v>11</v>
@@ -4746,24 +4768,24 @@
       <c r="G67" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H67" s="96" t="s">
-        <v>22</v>
+      <c r="H67" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I67" s="100"/>
     </row>
-    <row r="68" ht="18" customHeight="1" spans="1:9">
-      <c r="A68" s="106"/>
+    <row r="68" ht="33" customHeight="1" spans="1:9">
+      <c r="A68" s="107"/>
       <c r="B68" s="91">
         <v>53</v>
       </c>
       <c r="C68" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D68" s="93" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E68" s="94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F68" s="94">
         <v>11</v>
@@ -4771,24 +4793,24 @@
       <c r="G68" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H68" s="96" t="s">
-        <v>22</v>
+      <c r="H68" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I68" s="97"/>
     </row>
     <row r="69" ht="18" customHeight="1" spans="1:9">
-      <c r="A69" s="106"/>
+      <c r="A69" s="107"/>
       <c r="B69" s="98">
         <v>54</v>
       </c>
       <c r="C69" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D69" s="99" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E69" s="94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F69" s="94">
         <v>11</v>
@@ -4796,24 +4818,24 @@
       <c r="G69" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H69" s="96" t="s">
-        <v>22</v>
+      <c r="H69" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I69" s="100"/>
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:9">
-      <c r="A70" s="106"/>
+      <c r="A70" s="107"/>
       <c r="B70" s="91">
         <v>55</v>
       </c>
       <c r="C70" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D70" s="93" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E70" s="94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F70" s="94">
         <v>11</v>
@@ -4821,37 +4843,37 @@
       <c r="G70" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H70" s="96" t="s">
-        <v>22</v>
+      <c r="H70" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I70" s="97"/>
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A71" s="105" t="s">
-        <v>100</v>
-      </c>
-      <c r="B71" s="105"/>
-      <c r="C71" s="105"/>
-      <c r="D71" s="105"/>
-      <c r="E71" s="105"/>
-      <c r="F71" s="105"/>
-      <c r="G71" s="105"/>
-      <c r="H71" s="105"/>
-      <c r="I71" s="105"/>
+      <c r="A71" s="106" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" s="106"/>
+      <c r="C71" s="106"/>
+      <c r="D71" s="106"/>
+      <c r="E71" s="106"/>
+      <c r="F71" s="106"/>
+      <c r="G71" s="106"/>
+      <c r="H71" s="106"/>
+      <c r="I71" s="106"/>
     </row>
     <row r="72" ht="18" customHeight="1" spans="1:9">
-      <c r="A72" s="106"/>
+      <c r="A72" s="107"/>
       <c r="B72" s="91">
         <v>56</v>
       </c>
       <c r="C72" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D72" s="93" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E72" s="94" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F72" s="94">
         <v>12</v>
@@ -4859,24 +4881,24 @@
       <c r="G72" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H72" s="96" t="s">
-        <v>22</v>
+      <c r="H72" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I72" s="97"/>
     </row>
     <row r="73" ht="18" customHeight="1" spans="1:9">
-      <c r="A73" s="106"/>
+      <c r="A73" s="107"/>
       <c r="B73" s="98">
         <v>57</v>
       </c>
       <c r="C73" s="92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D73" s="99" t="s">
+        <v>104</v>
+      </c>
+      <c r="E73" s="94" t="s">
         <v>103</v>
-      </c>
-      <c r="E73" s="94" t="s">
-        <v>102</v>
       </c>
       <c r="F73" s="94">
         <v>12</v>
@@ -4884,24 +4906,24 @@
       <c r="G73" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H73" s="96" t="s">
-        <v>22</v>
+      <c r="H73" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I73" s="100"/>
     </row>
     <row r="74" ht="18" customHeight="1" spans="1:9">
-      <c r="A74" s="107"/>
+      <c r="A74" s="108"/>
       <c r="B74" s="91">
         <v>58</v>
       </c>
       <c r="C74" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D74" s="93" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E74" s="94" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F74" s="94">
         <v>12</v>
@@ -4909,24 +4931,24 @@
       <c r="G74" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H74" s="96" t="s">
-        <v>22</v>
+      <c r="H74" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I74" s="97"/>
     </row>
     <row r="75" ht="18" customHeight="1" spans="1:9">
-      <c r="A75" s="107"/>
+      <c r="A75" s="108"/>
       <c r="B75" s="98">
         <v>59</v>
       </c>
       <c r="C75" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D75" s="99" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E75" s="94" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F75" s="94">
         <v>12</v>
@@ -4934,24 +4956,24 @@
       <c r="G75" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H75" s="96" t="s">
-        <v>22</v>
+      <c r="H75" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I75" s="100"/>
     </row>
     <row r="76" ht="18" customHeight="1" spans="1:9">
-      <c r="A76" s="107"/>
+      <c r="A76" s="108"/>
       <c r="B76" s="91">
         <v>60</v>
       </c>
       <c r="C76" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D76" s="93" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E76" s="94" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F76" s="94">
         <v>12</v>
@@ -4959,37 +4981,37 @@
       <c r="G76" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H76" s="96" t="s">
-        <v>22</v>
+      <c r="H76" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I76" s="97"/>
     </row>
     <row r="77" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A77" s="108" t="s">
-        <v>108</v>
-      </c>
-      <c r="B77" s="108"/>
-      <c r="C77" s="108"/>
-      <c r="D77" s="108"/>
-      <c r="E77" s="108"/>
-      <c r="F77" s="108"/>
-      <c r="G77" s="108"/>
-      <c r="H77" s="108"/>
-      <c r="I77" s="108"/>
+      <c r="A77" s="109" t="s">
+        <v>109</v>
+      </c>
+      <c r="B77" s="109"/>
+      <c r="C77" s="109"/>
+      <c r="D77" s="109"/>
+      <c r="E77" s="109"/>
+      <c r="F77" s="109"/>
+      <c r="G77" s="109"/>
+      <c r="H77" s="109"/>
+      <c r="I77" s="109"/>
     </row>
     <row r="78" ht="18" customHeight="1" spans="1:9">
-      <c r="A78" s="107"/>
+      <c r="A78" s="108"/>
       <c r="B78" s="91">
         <v>61</v>
       </c>
       <c r="C78" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D78" s="93" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E78" s="94" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F78" s="94">
         <v>13</v>
@@ -4997,24 +5019,24 @@
       <c r="G78" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H78" s="96" t="s">
-        <v>22</v>
+      <c r="H78" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I78" s="97"/>
     </row>
     <row r="79" ht="18" customHeight="1" spans="1:9">
-      <c r="A79" s="107"/>
+      <c r="A79" s="108"/>
       <c r="B79" s="98">
         <v>62</v>
       </c>
       <c r="C79" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D79" s="99" t="s">
+        <v>112</v>
+      </c>
+      <c r="E79" s="94" t="s">
         <v>111</v>
-      </c>
-      <c r="E79" s="94" t="s">
-        <v>110</v>
       </c>
       <c r="F79" s="94">
         <v>13</v>
@@ -5022,24 +5044,24 @@
       <c r="G79" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H79" s="96" t="s">
-        <v>22</v>
+      <c r="H79" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I79" s="100"/>
     </row>
     <row r="80" ht="18" customHeight="1" spans="1:9">
-      <c r="A80" s="107"/>
+      <c r="A80" s="108"/>
       <c r="B80" s="91">
         <v>63</v>
       </c>
       <c r="C80" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D80" s="93" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E80" s="94" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F80" s="94">
         <v>13</v>
@@ -5047,24 +5069,24 @@
       <c r="G80" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H80" s="96" t="s">
-        <v>22</v>
+      <c r="H80" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I80" s="97"/>
     </row>
     <row r="81" ht="18" customHeight="1" spans="1:9">
-      <c r="A81" s="107"/>
+      <c r="A81" s="108"/>
       <c r="B81" s="98">
         <v>64</v>
       </c>
       <c r="C81" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D81" s="99" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E81" s="94" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F81" s="94">
         <v>13</v>
@@ -5072,24 +5094,24 @@
       <c r="G81" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H81" s="96" t="s">
-        <v>22</v>
+      <c r="H81" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I81" s="100"/>
     </row>
     <row r="82" ht="18" customHeight="1" spans="1:9">
-      <c r="A82" s="107"/>
+      <c r="A82" s="108"/>
       <c r="B82" s="91">
         <v>65</v>
       </c>
       <c r="C82" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D82" s="93" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E82" s="94" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F82" s="94">
         <v>13</v>
@@ -5097,37 +5119,37 @@
       <c r="G82" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H82" s="96" t="s">
-        <v>22</v>
+      <c r="H82" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I82" s="97"/>
     </row>
     <row r="83" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A83" s="108" t="s">
-        <v>115</v>
-      </c>
-      <c r="B83" s="108"/>
-      <c r="C83" s="108"/>
-      <c r="D83" s="108"/>
-      <c r="E83" s="108"/>
-      <c r="F83" s="108"/>
-      <c r="G83" s="108"/>
-      <c r="H83" s="108"/>
-      <c r="I83" s="108"/>
+      <c r="A83" s="109" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" s="109"/>
+      <c r="C83" s="109"/>
+      <c r="D83" s="109"/>
+      <c r="E83" s="109"/>
+      <c r="F83" s="109"/>
+      <c r="G83" s="109"/>
+      <c r="H83" s="109"/>
+      <c r="I83" s="109"/>
     </row>
     <row r="84" ht="18" customHeight="1" spans="1:9">
-      <c r="A84" s="107"/>
+      <c r="A84" s="108"/>
       <c r="B84" s="91">
         <v>66</v>
       </c>
       <c r="C84" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D84" s="93" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E84" s="94" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F84" s="94">
         <v>14</v>
@@ -5135,24 +5157,24 @@
       <c r="G84" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H84" s="96" t="s">
-        <v>22</v>
+      <c r="H84" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I84" s="97"/>
     </row>
     <row r="85" ht="18" customHeight="1" spans="1:9">
-      <c r="A85" s="107"/>
+      <c r="A85" s="108"/>
       <c r="B85" s="98">
         <v>67</v>
       </c>
       <c r="C85" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D85" s="99" t="s">
+        <v>119</v>
+      </c>
+      <c r="E85" s="94" t="s">
         <v>118</v>
-      </c>
-      <c r="E85" s="94" t="s">
-        <v>117</v>
       </c>
       <c r="F85" s="94">
         <v>14</v>
@@ -5160,24 +5182,24 @@
       <c r="G85" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H85" s="96" t="s">
-        <v>22</v>
+      <c r="H85" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I85" s="100"/>
     </row>
     <row r="86" ht="18" customHeight="1" spans="1:9">
-      <c r="A86" s="107"/>
+      <c r="A86" s="108"/>
       <c r="B86" s="91">
         <v>68</v>
       </c>
       <c r="C86" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D86" s="93" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E86" s="94" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F86" s="94">
         <v>14</v>
@@ -5185,24 +5207,24 @@
       <c r="G86" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H86" s="96" t="s">
-        <v>22</v>
+      <c r="H86" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I86" s="97"/>
     </row>
     <row r="87" ht="18" customHeight="1" spans="1:9">
-      <c r="A87" s="107"/>
+      <c r="A87" s="108"/>
       <c r="B87" s="98">
         <v>69</v>
       </c>
       <c r="C87" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D87" s="99" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E87" s="94" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F87" s="94">
         <v>14</v>
@@ -5210,24 +5232,24 @@
       <c r="G87" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H87" s="96" t="s">
-        <v>22</v>
+      <c r="H87" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I87" s="100"/>
     </row>
     <row r="88" ht="18" customHeight="1" spans="1:9">
-      <c r="A88" s="107"/>
+      <c r="A88" s="108"/>
       <c r="B88" s="91">
         <v>70</v>
       </c>
       <c r="C88" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D88" s="93" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E88" s="94" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F88" s="94">
         <v>14</v>
@@ -5235,37 +5257,37 @@
       <c r="G88" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H88" s="96" t="s">
-        <v>22</v>
+      <c r="H88" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I88" s="97"/>
     </row>
     <row r="89" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A89" s="108" t="s">
-        <v>122</v>
-      </c>
-      <c r="B89" s="108"/>
-      <c r="C89" s="108"/>
-      <c r="D89" s="108"/>
-      <c r="E89" s="108"/>
-      <c r="F89" s="108"/>
-      <c r="G89" s="108"/>
-      <c r="H89" s="108"/>
-      <c r="I89" s="108"/>
+      <c r="A89" s="109" t="s">
+        <v>123</v>
+      </c>
+      <c r="B89" s="109"/>
+      <c r="C89" s="109"/>
+      <c r="D89" s="109"/>
+      <c r="E89" s="109"/>
+      <c r="F89" s="109"/>
+      <c r="G89" s="109"/>
+      <c r="H89" s="109"/>
+      <c r="I89" s="109"/>
     </row>
     <row r="90" ht="18" customHeight="1" spans="1:9">
-      <c r="A90" s="107"/>
+      <c r="A90" s="108"/>
       <c r="B90" s="91">
         <v>71</v>
       </c>
       <c r="C90" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D90" s="93" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E90" s="94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F90" s="94">
         <v>15</v>
@@ -5273,24 +5295,24 @@
       <c r="G90" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H90" s="96" t="s">
-        <v>22</v>
+      <c r="H90" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I90" s="97"/>
     </row>
     <row r="91" ht="18" customHeight="1" spans="1:9">
-      <c r="A91" s="107"/>
+      <c r="A91" s="108"/>
       <c r="B91" s="98">
         <v>72</v>
       </c>
       <c r="C91" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D91" s="99" t="s">
+        <v>126</v>
+      </c>
+      <c r="E91" s="94" t="s">
         <v>125</v>
-      </c>
-      <c r="E91" s="94" t="s">
-        <v>124</v>
       </c>
       <c r="F91" s="94">
         <v>15</v>
@@ -5298,24 +5320,24 @@
       <c r="G91" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H91" s="96" t="s">
-        <v>22</v>
+      <c r="H91" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I91" s="100"/>
     </row>
     <row r="92" ht="18" customHeight="1" spans="1:9">
-      <c r="A92" s="107"/>
+      <c r="A92" s="108"/>
       <c r="B92" s="91">
         <v>73</v>
       </c>
       <c r="C92" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D92" s="93" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E92" s="94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F92" s="94">
         <v>15</v>
@@ -5323,24 +5345,24 @@
       <c r="G92" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H92" s="96" t="s">
-        <v>22</v>
+      <c r="H92" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I92" s="97"/>
     </row>
     <row r="93" ht="18" customHeight="1" spans="1:9">
-      <c r="A93" s="107"/>
+      <c r="A93" s="108"/>
       <c r="B93" s="98">
         <v>74</v>
       </c>
       <c r="C93" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D93" s="99" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E93" s="94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F93" s="94">
         <v>15</v>
@@ -5348,24 +5370,24 @@
       <c r="G93" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H93" s="96" t="s">
-        <v>22</v>
+      <c r="H93" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I93" s="100"/>
     </row>
     <row r="94" ht="18" customHeight="1" spans="1:9">
-      <c r="A94" s="109"/>
+      <c r="A94" s="110"/>
       <c r="B94" s="91">
         <v>75</v>
       </c>
       <c r="C94" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D94" s="93" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E94" s="94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F94" s="94">
         <v>15</v>
@@ -5373,37 +5395,37 @@
       <c r="G94" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H94" s="96" t="s">
-        <v>22</v>
+      <c r="H94" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I94" s="97"/>
     </row>
     <row r="95" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A95" s="110" t="s">
-        <v>130</v>
-      </c>
-      <c r="B95" s="110"/>
-      <c r="C95" s="110"/>
-      <c r="D95" s="110"/>
-      <c r="E95" s="110"/>
-      <c r="F95" s="110"/>
-      <c r="G95" s="110"/>
-      <c r="H95" s="110"/>
-      <c r="I95" s="110"/>
+      <c r="A95" s="111" t="s">
+        <v>131</v>
+      </c>
+      <c r="B95" s="111"/>
+      <c r="C95" s="111"/>
+      <c r="D95" s="111"/>
+      <c r="E95" s="111"/>
+      <c r="F95" s="111"/>
+      <c r="G95" s="111"/>
+      <c r="H95" s="111"/>
+      <c r="I95" s="111"/>
     </row>
     <row r="96" ht="18" customHeight="1" spans="1:9">
-      <c r="A96" s="109"/>
+      <c r="A96" s="110"/>
       <c r="B96" s="91">
         <v>76</v>
       </c>
       <c r="C96" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D96" s="93" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E96" s="94" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F96" s="94">
         <v>16</v>
@@ -5411,24 +5433,24 @@
       <c r="G96" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H96" s="96" t="s">
-        <v>22</v>
+      <c r="H96" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I96" s="97"/>
     </row>
     <row r="97" ht="18" customHeight="1" spans="1:9">
-      <c r="A97" s="109"/>
+      <c r="A97" s="110"/>
       <c r="B97" s="98">
         <v>77</v>
       </c>
       <c r="C97" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D97" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="E97" s="94" t="s">
         <v>133</v>
-      </c>
-      <c r="E97" s="94" t="s">
-        <v>132</v>
       </c>
       <c r="F97" s="94">
         <v>16</v>
@@ -5436,24 +5458,24 @@
       <c r="G97" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H97" s="96" t="s">
-        <v>22</v>
+      <c r="H97" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I97" s="100"/>
     </row>
     <row r="98" ht="18" customHeight="1" spans="1:9">
-      <c r="A98" s="109"/>
+      <c r="A98" s="110"/>
       <c r="B98" s="91">
         <v>78</v>
       </c>
       <c r="C98" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D98" s="93" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E98" s="94" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F98" s="94">
         <v>16</v>
@@ -5461,24 +5483,24 @@
       <c r="G98" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H98" s="96" t="s">
-        <v>22</v>
+      <c r="H98" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I98" s="97"/>
     </row>
     <row r="99" ht="18" customHeight="1" spans="1:9">
-      <c r="A99" s="109"/>
+      <c r="A99" s="110"/>
       <c r="B99" s="98">
         <v>79</v>
       </c>
       <c r="C99" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D99" s="99" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E99" s="94" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F99" s="94">
         <v>16</v>
@@ -5486,24 +5508,24 @@
       <c r="G99" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H99" s="96" t="s">
-        <v>22</v>
+      <c r="H99" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I99" s="100"/>
     </row>
     <row r="100" ht="18" customHeight="1" spans="1:9">
-      <c r="A100" s="109"/>
+      <c r="A100" s="110"/>
       <c r="B100" s="91">
         <v>80</v>
       </c>
       <c r="C100" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D100" s="93" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E100" s="94" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F100" s="94">
         <v>16</v>
@@ -5511,37 +5533,37 @@
       <c r="G100" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H100" s="96" t="s">
-        <v>22</v>
+      <c r="H100" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I100" s="97"/>
     </row>
     <row r="101" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A101" s="110" t="s">
-        <v>137</v>
-      </c>
-      <c r="B101" s="110"/>
-      <c r="C101" s="110"/>
-      <c r="D101" s="110"/>
-      <c r="E101" s="110"/>
-      <c r="F101" s="110"/>
-      <c r="G101" s="110"/>
-      <c r="H101" s="110"/>
-      <c r="I101" s="110"/>
+      <c r="A101" s="111" t="s">
+        <v>138</v>
+      </c>
+      <c r="B101" s="111"/>
+      <c r="C101" s="111"/>
+      <c r="D101" s="111"/>
+      <c r="E101" s="111"/>
+      <c r="F101" s="111"/>
+      <c r="G101" s="111"/>
+      <c r="H101" s="111"/>
+      <c r="I101" s="111"/>
     </row>
     <row r="102" ht="18" customHeight="1" spans="1:9">
-      <c r="A102" s="109"/>
+      <c r="A102" s="110"/>
       <c r="B102" s="91">
         <v>81</v>
       </c>
       <c r="C102" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D102" s="93" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E102" s="94" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F102" s="94">
         <v>17</v>
@@ -5549,24 +5571,24 @@
       <c r="G102" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H102" s="96" t="s">
-        <v>22</v>
+      <c r="H102" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I102" s="97"/>
     </row>
     <row r="103" ht="18" customHeight="1" spans="1:9">
-      <c r="A103" s="109"/>
+      <c r="A103" s="110"/>
       <c r="B103" s="98">
         <v>82</v>
       </c>
       <c r="C103" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D103" s="99" t="s">
+        <v>141</v>
+      </c>
+      <c r="E103" s="94" t="s">
         <v>140</v>
-      </c>
-      <c r="E103" s="94" t="s">
-        <v>139</v>
       </c>
       <c r="F103" s="94">
         <v>17</v>
@@ -5574,24 +5596,24 @@
       <c r="G103" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H103" s="96" t="s">
-        <v>22</v>
+      <c r="H103" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I103" s="100"/>
     </row>
     <row r="104" ht="18" customHeight="1" spans="1:9">
-      <c r="A104" s="109"/>
+      <c r="A104" s="110"/>
       <c r="B104" s="91">
         <v>83</v>
       </c>
       <c r="C104" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D104" s="93" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E104" s="94" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F104" s="94">
         <v>17</v>
@@ -5599,24 +5621,24 @@
       <c r="G104" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H104" s="96" t="s">
-        <v>22</v>
+      <c r="H104" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I104" s="97"/>
     </row>
     <row r="105" ht="18" customHeight="1" spans="1:9">
-      <c r="A105" s="109"/>
+      <c r="A105" s="110"/>
       <c r="B105" s="98">
         <v>84</v>
       </c>
       <c r="C105" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D105" s="99" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E105" s="94" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F105" s="94">
         <v>17</v>
@@ -5624,24 +5646,24 @@
       <c r="G105" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H105" s="96" t="s">
-        <v>22</v>
+      <c r="H105" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I105" s="100"/>
     </row>
     <row r="106" ht="18" customHeight="1" spans="1:9">
-      <c r="A106" s="109"/>
+      <c r="A106" s="110"/>
       <c r="B106" s="91">
         <v>85</v>
       </c>
       <c r="C106" s="92" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D106" s="93" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E106" s="94" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F106" s="94">
         <v>17</v>
@@ -5649,37 +5671,37 @@
       <c r="G106" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H106" s="96" t="s">
-        <v>22</v>
+      <c r="H106" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I106" s="97"/>
     </row>
     <row r="107" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A107" s="111" t="s">
-        <v>144</v>
-      </c>
-      <c r="B107" s="111"/>
-      <c r="C107" s="111"/>
-      <c r="D107" s="111"/>
-      <c r="E107" s="111"/>
-      <c r="F107" s="111"/>
-      <c r="G107" s="111"/>
-      <c r="H107" s="111"/>
-      <c r="I107" s="111"/>
+      <c r="A107" s="112" t="s">
+        <v>145</v>
+      </c>
+      <c r="B107" s="112"/>
+      <c r="C107" s="112"/>
+      <c r="D107" s="112"/>
+      <c r="E107" s="112"/>
+      <c r="F107" s="112"/>
+      <c r="G107" s="112"/>
+      <c r="H107" s="112"/>
+      <c r="I107" s="112"/>
     </row>
     <row r="108" ht="18" customHeight="1" spans="1:9">
-      <c r="A108" s="112"/>
+      <c r="A108" s="113"/>
       <c r="B108" s="91">
         <v>86</v>
       </c>
       <c r="C108" s="92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D108" s="93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E108" s="94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F108" s="94">
         <v>18</v>
@@ -5687,24 +5709,24 @@
       <c r="G108" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H108" s="96" t="s">
-        <v>22</v>
+      <c r="H108" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I108" s="97"/>
     </row>
     <row r="109" ht="18" customHeight="1" spans="1:9">
-      <c r="A109" s="112"/>
+      <c r="A109" s="113"/>
       <c r="B109" s="98">
         <v>87</v>
       </c>
       <c r="C109" s="92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D109" s="99" t="s">
+        <v>148</v>
+      </c>
+      <c r="E109" s="94" t="s">
         <v>147</v>
-      </c>
-      <c r="E109" s="94" t="s">
-        <v>146</v>
       </c>
       <c r="F109" s="94">
         <v>18</v>
@@ -5712,24 +5734,24 @@
       <c r="G109" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H109" s="96" t="s">
-        <v>22</v>
+      <c r="H109" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I109" s="100"/>
     </row>
     <row r="110" ht="18" customHeight="1" spans="1:9">
-      <c r="A110" s="112"/>
+      <c r="A110" s="113"/>
       <c r="B110" s="91">
         <v>88</v>
       </c>
       <c r="C110" s="92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D110" s="93" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E110" s="94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F110" s="94">
         <v>18</v>
@@ -5737,24 +5759,24 @@
       <c r="G110" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H110" s="96" t="s">
-        <v>22</v>
+      <c r="H110" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I110" s="97"/>
     </row>
     <row r="111" ht="18" customHeight="1" spans="1:9">
-      <c r="A111" s="112"/>
+      <c r="A111" s="113"/>
       <c r="B111" s="98">
         <v>89</v>
       </c>
       <c r="C111" s="92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D111" s="99" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E111" s="94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F111" s="94">
         <v>18</v>
@@ -5762,24 +5784,24 @@
       <c r="G111" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H111" s="96" t="s">
-        <v>22</v>
+      <c r="H111" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I111" s="100"/>
     </row>
     <row r="112" ht="18" customHeight="1" spans="1:9">
-      <c r="A112" s="112"/>
+      <c r="A112" s="113"/>
       <c r="B112" s="91">
         <v>90</v>
       </c>
       <c r="C112" s="92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D112" s="93" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E112" s="94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F112" s="94">
         <v>18</v>
@@ -5787,37 +5809,37 @@
       <c r="G112" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H112" s="96" t="s">
-        <v>22</v>
+      <c r="H112" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I112" s="97"/>
     </row>
     <row r="113" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A113" s="111" t="s">
-        <v>151</v>
-      </c>
-      <c r="B113" s="111"/>
-      <c r="C113" s="111"/>
-      <c r="D113" s="111"/>
-      <c r="E113" s="111"/>
-      <c r="F113" s="111"/>
-      <c r="G113" s="111"/>
-      <c r="H113" s="111"/>
-      <c r="I113" s="111"/>
+      <c r="A113" s="112" t="s">
+        <v>152</v>
+      </c>
+      <c r="B113" s="112"/>
+      <c r="C113" s="112"/>
+      <c r="D113" s="112"/>
+      <c r="E113" s="112"/>
+      <c r="F113" s="112"/>
+      <c r="G113" s="112"/>
+      <c r="H113" s="112"/>
+      <c r="I113" s="112"/>
     </row>
     <row r="114" ht="18" customHeight="1" spans="1:9">
-      <c r="A114" s="112"/>
+      <c r="A114" s="113"/>
       <c r="B114" s="91">
         <v>91</v>
       </c>
       <c r="C114" s="92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D114" s="93" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E114" s="94" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F114" s="94">
         <v>19</v>
@@ -5825,24 +5847,24 @@
       <c r="G114" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H114" s="96" t="s">
-        <v>22</v>
+      <c r="H114" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I114" s="97"/>
     </row>
     <row r="115" ht="18" customHeight="1" spans="1:9">
-      <c r="A115" s="112"/>
+      <c r="A115" s="113"/>
       <c r="B115" s="98">
         <v>92</v>
       </c>
       <c r="C115" s="92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D115" s="99" t="s">
+        <v>155</v>
+      </c>
+      <c r="E115" s="94" t="s">
         <v>154</v>
-      </c>
-      <c r="E115" s="94" t="s">
-        <v>153</v>
       </c>
       <c r="F115" s="94">
         <v>19</v>
@@ -5850,24 +5872,24 @@
       <c r="G115" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H115" s="96" t="s">
-        <v>22</v>
+      <c r="H115" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I115" s="100"/>
     </row>
     <row r="116" ht="18" customHeight="1" spans="1:9">
-      <c r="A116" s="112"/>
+      <c r="A116" s="113"/>
       <c r="B116" s="91">
         <v>93</v>
       </c>
       <c r="C116" s="92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D116" s="93" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E116" s="94" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F116" s="94">
         <v>19</v>
@@ -5875,24 +5897,24 @@
       <c r="G116" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H116" s="96" t="s">
-        <v>22</v>
+      <c r="H116" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I116" s="97"/>
     </row>
     <row r="117" ht="18" customHeight="1" spans="1:9">
-      <c r="A117" s="113"/>
+      <c r="A117" s="114"/>
       <c r="B117" s="98">
         <v>94</v>
       </c>
       <c r="C117" s="92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D117" s="99" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E117" s="94" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F117" s="94">
         <v>19</v>
@@ -5900,24 +5922,24 @@
       <c r="G117" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H117" s="96" t="s">
-        <v>22</v>
+      <c r="H117" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I117" s="100"/>
     </row>
     <row r="118" ht="18" customHeight="1" spans="1:9">
-      <c r="A118" s="113"/>
+      <c r="A118" s="114"/>
       <c r="B118" s="91">
         <v>95</v>
       </c>
       <c r="C118" s="92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D118" s="93" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E118" s="94" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F118" s="94">
         <v>19</v>
@@ -5925,37 +5947,37 @@
       <c r="G118" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H118" s="96" t="s">
-        <v>22</v>
+      <c r="H118" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I118" s="97"/>
     </row>
     <row r="119" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A119" s="114" t="s">
-        <v>159</v>
-      </c>
-      <c r="B119" s="114"/>
-      <c r="C119" s="114"/>
-      <c r="D119" s="114"/>
-      <c r="E119" s="114"/>
-      <c r="F119" s="114"/>
-      <c r="G119" s="114"/>
-      <c r="H119" s="114"/>
-      <c r="I119" s="114"/>
+      <c r="A119" s="115" t="s">
+        <v>160</v>
+      </c>
+      <c r="B119" s="115"/>
+      <c r="C119" s="115"/>
+      <c r="D119" s="115"/>
+      <c r="E119" s="115"/>
+      <c r="F119" s="115"/>
+      <c r="G119" s="115"/>
+      <c r="H119" s="115"/>
+      <c r="I119" s="115"/>
     </row>
     <row r="120" ht="18" customHeight="1" spans="1:9">
-      <c r="A120" s="113"/>
+      <c r="A120" s="114"/>
       <c r="B120" s="91">
         <v>96</v>
       </c>
       <c r="C120" s="92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D120" s="93" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E120" s="94" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F120" s="94">
         <v>20</v>
@@ -5963,24 +5985,24 @@
       <c r="G120" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H120" s="96" t="s">
-        <v>22</v>
+      <c r="H120" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I120" s="97"/>
     </row>
     <row r="121" ht="18" customHeight="1" spans="1:9">
-      <c r="A121" s="113"/>
+      <c r="A121" s="114"/>
       <c r="B121" s="98">
         <v>97</v>
       </c>
       <c r="C121" s="92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D121" s="99" t="s">
+        <v>163</v>
+      </c>
+      <c r="E121" s="94" t="s">
         <v>162</v>
-      </c>
-      <c r="E121" s="94" t="s">
-        <v>161</v>
       </c>
       <c r="F121" s="94">
         <v>20</v>
@@ -5988,24 +6010,24 @@
       <c r="G121" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H121" s="96" t="s">
-        <v>22</v>
+      <c r="H121" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I121" s="100"/>
     </row>
     <row r="122" ht="18" customHeight="1" spans="1:9">
-      <c r="A122" s="113"/>
+      <c r="A122" s="114"/>
       <c r="B122" s="91">
         <v>98</v>
       </c>
       <c r="C122" s="92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D122" s="93" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E122" s="94" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F122" s="94">
         <v>20</v>
@@ -6013,24 +6035,24 @@
       <c r="G122" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H122" s="96" t="s">
-        <v>22</v>
+      <c r="H122" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I122" s="97"/>
     </row>
     <row r="123" ht="18" customHeight="1" spans="1:9">
-      <c r="A123" s="113"/>
+      <c r="A123" s="114"/>
       <c r="B123" s="98">
         <v>99</v>
       </c>
       <c r="C123" s="92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D123" s="99" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E123" s="94" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F123" s="94">
         <v>20</v>
@@ -6038,24 +6060,24 @@
       <c r="G123" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H123" s="96" t="s">
-        <v>22</v>
+      <c r="H123" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I123" s="100"/>
     </row>
     <row r="124" ht="18" customHeight="1" spans="1:9">
-      <c r="A124" s="113"/>
+      <c r="A124" s="114"/>
       <c r="B124" s="91">
         <v>100</v>
       </c>
       <c r="C124" s="92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D124" s="93" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E124" s="94" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F124" s="94">
         <v>20</v>
@@ -6063,37 +6085,37 @@
       <c r="G124" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H124" s="96" t="s">
-        <v>22</v>
+      <c r="H124" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I124" s="97"/>
     </row>
     <row r="125" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A125" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="B125" s="115"/>
-      <c r="C125" s="115"/>
-      <c r="D125" s="115"/>
-      <c r="E125" s="115"/>
-      <c r="F125" s="115"/>
-      <c r="G125" s="115"/>
-      <c r="H125" s="115"/>
-      <c r="I125" s="115"/>
+      <c r="A125" s="116" t="s">
+        <v>167</v>
+      </c>
+      <c r="B125" s="116"/>
+      <c r="C125" s="116"/>
+      <c r="D125" s="116"/>
+      <c r="E125" s="116"/>
+      <c r="F125" s="116"/>
+      <c r="G125" s="116"/>
+      <c r="H125" s="116"/>
+      <c r="I125" s="116"/>
     </row>
     <row r="126" ht="18" customHeight="1" spans="1:9">
-      <c r="A126" s="116"/>
+      <c r="A126" s="117"/>
       <c r="B126" s="91">
         <v>101</v>
       </c>
       <c r="C126" s="92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D126" s="93" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E126" s="94" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F126" s="94">
         <v>21</v>
@@ -6101,24 +6123,24 @@
       <c r="G126" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H126" s="96" t="s">
-        <v>22</v>
+      <c r="H126" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I126" s="97"/>
     </row>
     <row r="127" ht="18" customHeight="1" spans="1:9">
-      <c r="A127" s="116"/>
+      <c r="A127" s="117"/>
       <c r="B127" s="98">
         <v>102</v>
       </c>
       <c r="C127" s="92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D127" s="99" t="s">
+        <v>171</v>
+      </c>
+      <c r="E127" s="94" t="s">
         <v>170</v>
-      </c>
-      <c r="E127" s="94" t="s">
-        <v>169</v>
       </c>
       <c r="F127" s="94">
         <v>21</v>
@@ -6126,24 +6148,24 @@
       <c r="G127" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H127" s="96" t="s">
-        <v>22</v>
+      <c r="H127" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I127" s="100"/>
     </row>
     <row r="128" ht="18" customHeight="1" spans="1:9">
-      <c r="A128" s="116"/>
+      <c r="A128" s="117"/>
       <c r="B128" s="91">
         <v>103</v>
       </c>
       <c r="C128" s="92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D128" s="93" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E128" s="94" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F128" s="94">
         <v>21</v>
@@ -6151,24 +6173,24 @@
       <c r="G128" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H128" s="96" t="s">
-        <v>22</v>
+      <c r="H128" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I128" s="97"/>
     </row>
     <row r="129" ht="18" customHeight="1" spans="1:9">
-      <c r="A129" s="116"/>
+      <c r="A129" s="117"/>
       <c r="B129" s="98">
         <v>104</v>
       </c>
       <c r="C129" s="92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D129" s="99" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E129" s="94" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F129" s="94">
         <v>21</v>
@@ -6176,24 +6198,24 @@
       <c r="G129" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H129" s="96" t="s">
-        <v>22</v>
+      <c r="H129" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I129" s="100"/>
     </row>
     <row r="130" ht="18" customHeight="1" spans="1:9">
-      <c r="A130" s="116"/>
+      <c r="A130" s="117"/>
       <c r="B130" s="91">
         <v>105</v>
       </c>
       <c r="C130" s="92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D130" s="93" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E130" s="94" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F130" s="94">
         <v>21</v>
@@ -6201,37 +6223,37 @@
       <c r="G130" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H130" s="96" t="s">
-        <v>22</v>
+      <c r="H130" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I130" s="97"/>
     </row>
     <row r="131" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A131" s="115" t="s">
-        <v>174</v>
-      </c>
-      <c r="B131" s="115"/>
-      <c r="C131" s="115"/>
-      <c r="D131" s="115"/>
-      <c r="E131" s="115"/>
-      <c r="F131" s="115"/>
-      <c r="G131" s="115"/>
-      <c r="H131" s="115"/>
-      <c r="I131" s="115"/>
+      <c r="A131" s="116" t="s">
+        <v>175</v>
+      </c>
+      <c r="B131" s="116"/>
+      <c r="C131" s="116"/>
+      <c r="D131" s="116"/>
+      <c r="E131" s="116"/>
+      <c r="F131" s="116"/>
+      <c r="G131" s="116"/>
+      <c r="H131" s="116"/>
+      <c r="I131" s="116"/>
     </row>
     <row r="132" ht="18" customHeight="1" spans="1:9">
-      <c r="A132" s="116"/>
+      <c r="A132" s="117"/>
       <c r="B132" s="91">
         <v>106</v>
       </c>
       <c r="C132" s="92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D132" s="93" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E132" s="94" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F132" s="94">
         <v>22</v>
@@ -6239,24 +6261,24 @@
       <c r="G132" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H132" s="96" t="s">
-        <v>22</v>
+      <c r="H132" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I132" s="97"/>
     </row>
     <row r="133" ht="18" customHeight="1" spans="1:9">
-      <c r="A133" s="116"/>
+      <c r="A133" s="117"/>
       <c r="B133" s="98">
         <v>107</v>
       </c>
       <c r="C133" s="92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D133" s="99" t="s">
+        <v>178</v>
+      </c>
+      <c r="E133" s="94" t="s">
         <v>177</v>
-      </c>
-      <c r="E133" s="94" t="s">
-        <v>176</v>
       </c>
       <c r="F133" s="94">
         <v>22</v>
@@ -6264,24 +6286,24 @@
       <c r="G133" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H133" s="96" t="s">
-        <v>22</v>
+      <c r="H133" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I133" s="100"/>
     </row>
     <row r="134" ht="18" customHeight="1" spans="1:9">
-      <c r="A134" s="116"/>
+      <c r="A134" s="117"/>
       <c r="B134" s="91">
         <v>108</v>
       </c>
       <c r="C134" s="92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D134" s="93" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E134" s="94" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F134" s="94">
         <v>22</v>
@@ -6289,24 +6311,24 @@
       <c r="G134" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H134" s="96" t="s">
-        <v>22</v>
+      <c r="H134" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I134" s="97"/>
     </row>
     <row r="135" ht="18" customHeight="1" spans="1:9">
-      <c r="A135" s="116"/>
+      <c r="A135" s="117"/>
       <c r="B135" s="98">
         <v>109</v>
       </c>
       <c r="C135" s="92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D135" s="99" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E135" s="94" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F135" s="94">
         <v>22</v>
@@ -6314,24 +6336,24 @@
       <c r="G135" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H135" s="96" t="s">
-        <v>22</v>
+      <c r="H135" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I135" s="100"/>
     </row>
     <row r="136" ht="18" customHeight="1" spans="1:9">
-      <c r="A136" s="117"/>
+      <c r="A136" s="118"/>
       <c r="B136" s="91">
         <v>110</v>
       </c>
       <c r="C136" s="92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D136" s="93" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E136" s="94" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F136" s="94">
         <v>22</v>
@@ -6339,37 +6361,37 @@
       <c r="G136" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H136" s="96" t="s">
-        <v>22</v>
+      <c r="H136" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I136" s="97"/>
     </row>
     <row r="137" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A137" s="118" t="s">
-        <v>182</v>
-      </c>
-      <c r="B137" s="118"/>
-      <c r="C137" s="118"/>
-      <c r="D137" s="118"/>
-      <c r="E137" s="118"/>
-      <c r="F137" s="118"/>
-      <c r="G137" s="118"/>
-      <c r="H137" s="118"/>
-      <c r="I137" s="118"/>
+      <c r="A137" s="119" t="s">
+        <v>183</v>
+      </c>
+      <c r="B137" s="119"/>
+      <c r="C137" s="119"/>
+      <c r="D137" s="119"/>
+      <c r="E137" s="119"/>
+      <c r="F137" s="119"/>
+      <c r="G137" s="119"/>
+      <c r="H137" s="119"/>
+      <c r="I137" s="119"/>
     </row>
     <row r="138" ht="18" customHeight="1" spans="1:9">
-      <c r="A138" s="117"/>
+      <c r="A138" s="118"/>
       <c r="B138" s="91">
         <v>111</v>
       </c>
       <c r="C138" s="92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D138" s="93" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E138" s="94" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F138" s="94">
         <v>23</v>
@@ -6377,24 +6399,24 @@
       <c r="G138" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H138" s="96" t="s">
-        <v>22</v>
+      <c r="H138" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I138" s="97"/>
     </row>
     <row r="139" ht="18" customHeight="1" spans="1:9">
-      <c r="A139" s="117"/>
+      <c r="A139" s="118"/>
       <c r="B139" s="98">
         <v>112</v>
       </c>
       <c r="C139" s="92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D139" s="99" t="s">
+        <v>186</v>
+      </c>
+      <c r="E139" s="94" t="s">
         <v>185</v>
-      </c>
-      <c r="E139" s="94" t="s">
-        <v>184</v>
       </c>
       <c r="F139" s="94">
         <v>23</v>
@@ -6402,24 +6424,24 @@
       <c r="G139" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H139" s="96" t="s">
-        <v>22</v>
+      <c r="H139" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I139" s="100"/>
     </row>
     <row r="140" ht="18" customHeight="1" spans="1:9">
-      <c r="A140" s="117"/>
+      <c r="A140" s="118"/>
       <c r="B140" s="91">
         <v>113</v>
       </c>
       <c r="C140" s="92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D140" s="93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E140" s="94" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F140" s="94">
         <v>23</v>
@@ -6427,24 +6449,24 @@
       <c r="G140" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H140" s="96" t="s">
-        <v>22</v>
+      <c r="H140" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I140" s="97"/>
     </row>
     <row r="141" ht="18" customHeight="1" spans="1:9">
-      <c r="A141" s="117"/>
+      <c r="A141" s="118"/>
       <c r="B141" s="98">
         <v>114</v>
       </c>
       <c r="C141" s="92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D141" s="99" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E141" s="94" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F141" s="94">
         <v>23</v>
@@ -6452,24 +6474,24 @@
       <c r="G141" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H141" s="96" t="s">
-        <v>22</v>
+      <c r="H141" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I141" s="100"/>
     </row>
     <row r="142" ht="18" customHeight="1" spans="1:9">
-      <c r="A142" s="119"/>
+      <c r="A142" s="120"/>
       <c r="B142" s="91">
         <v>115</v>
       </c>
       <c r="C142" s="92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D142" s="93" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E142" s="94" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F142" s="94">
         <v>23</v>
@@ -6477,37 +6499,37 @@
       <c r="G142" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H142" s="96" t="s">
-        <v>22</v>
+      <c r="H142" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I142" s="97"/>
     </row>
     <row r="143" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A143" s="120" t="s">
-        <v>190</v>
-      </c>
-      <c r="B143" s="120"/>
-      <c r="C143" s="120"/>
-      <c r="D143" s="120"/>
-      <c r="E143" s="120"/>
-      <c r="F143" s="120"/>
-      <c r="G143" s="120"/>
-      <c r="H143" s="120"/>
-      <c r="I143" s="120"/>
+      <c r="A143" s="121" t="s">
+        <v>191</v>
+      </c>
+      <c r="B143" s="121"/>
+      <c r="C143" s="121"/>
+      <c r="D143" s="121"/>
+      <c r="E143" s="121"/>
+      <c r="F143" s="121"/>
+      <c r="G143" s="121"/>
+      <c r="H143" s="121"/>
+      <c r="I143" s="121"/>
     </row>
     <row r="144" ht="18" customHeight="1" spans="1:9">
-      <c r="A144" s="119"/>
+      <c r="A144" s="120"/>
       <c r="B144" s="91">
         <v>116</v>
       </c>
       <c r="C144" s="92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D144" s="93" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E144" s="94" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F144" s="94">
         <v>24</v>
@@ -6515,24 +6537,24 @@
       <c r="G144" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H144" s="96" t="s">
-        <v>22</v>
+      <c r="H144" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I144" s="97"/>
     </row>
     <row r="145" ht="18" customHeight="1" spans="1:9">
-      <c r="A145" s="119"/>
+      <c r="A145" s="120"/>
       <c r="B145" s="98">
         <v>117</v>
       </c>
       <c r="C145" s="92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D145" s="99" t="s">
+        <v>194</v>
+      </c>
+      <c r="E145" s="94" t="s">
         <v>193</v>
-      </c>
-      <c r="E145" s="94" t="s">
-        <v>192</v>
       </c>
       <c r="F145" s="94">
         <v>24</v>
@@ -6540,24 +6562,24 @@
       <c r="G145" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H145" s="96" t="s">
-        <v>22</v>
+      <c r="H145" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I145" s="100"/>
     </row>
     <row r="146" ht="18" customHeight="1" spans="1:9">
-      <c r="A146" s="119"/>
+      <c r="A146" s="120"/>
       <c r="B146" s="91">
         <v>118</v>
       </c>
       <c r="C146" s="92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D146" s="93" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E146" s="94" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F146" s="94">
         <v>24</v>
@@ -6565,24 +6587,24 @@
       <c r="G146" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H146" s="96" t="s">
-        <v>22</v>
+      <c r="H146" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I146" s="97"/>
     </row>
     <row r="147" ht="18" customHeight="1" spans="1:9">
-      <c r="A147" s="119"/>
+      <c r="A147" s="120"/>
       <c r="B147" s="98">
         <v>119</v>
       </c>
       <c r="C147" s="92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D147" s="99" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E147" s="94" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F147" s="94">
         <v>24</v>
@@ -6590,24 +6612,24 @@
       <c r="G147" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H147" s="96" t="s">
-        <v>22</v>
+      <c r="H147" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I147" s="100"/>
     </row>
     <row r="148" ht="18" customHeight="1" spans="1:9">
-      <c r="A148" s="119"/>
+      <c r="A148" s="120"/>
       <c r="B148" s="91">
         <v>120</v>
       </c>
       <c r="C148" s="92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D148" s="93" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E148" s="94" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F148" s="94">
         <v>24</v>
@@ -6615,37 +6637,37 @@
       <c r="G148" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H148" s="96" t="s">
-        <v>22</v>
+      <c r="H148" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I148" s="97"/>
     </row>
     <row r="149" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A149" s="120" t="s">
-        <v>197</v>
-      </c>
-      <c r="B149" s="120"/>
-      <c r="C149" s="120"/>
-      <c r="D149" s="120"/>
-      <c r="E149" s="120"/>
-      <c r="F149" s="120"/>
-      <c r="G149" s="120"/>
-      <c r="H149" s="120"/>
-      <c r="I149" s="120"/>
+      <c r="A149" s="121" t="s">
+        <v>198</v>
+      </c>
+      <c r="B149" s="121"/>
+      <c r="C149" s="121"/>
+      <c r="D149" s="121"/>
+      <c r="E149" s="121"/>
+      <c r="F149" s="121"/>
+      <c r="G149" s="121"/>
+      <c r="H149" s="121"/>
+      <c r="I149" s="121"/>
     </row>
     <row r="150" ht="18" customHeight="1" spans="1:9">
-      <c r="A150" s="119"/>
+      <c r="A150" s="120"/>
       <c r="B150" s="91">
         <v>121</v>
       </c>
       <c r="C150" s="92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D150" s="93" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E150" s="94" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F150" s="94">
         <v>25</v>
@@ -6653,24 +6675,24 @@
       <c r="G150" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H150" s="96" t="s">
-        <v>22</v>
+      <c r="H150" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I150" s="97"/>
     </row>
     <row r="151" ht="18" customHeight="1" spans="1:9">
-      <c r="A151" s="119"/>
+      <c r="A151" s="120"/>
       <c r="B151" s="98">
         <v>122</v>
       </c>
       <c r="C151" s="92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D151" s="99" t="s">
+        <v>201</v>
+      </c>
+      <c r="E151" s="94" t="s">
         <v>200</v>
-      </c>
-      <c r="E151" s="94" t="s">
-        <v>199</v>
       </c>
       <c r="F151" s="94">
         <v>25</v>
@@ -6678,24 +6700,24 @@
       <c r="G151" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H151" s="96" t="s">
-        <v>22</v>
+      <c r="H151" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I151" s="100"/>
     </row>
     <row r="152" ht="18" customHeight="1" spans="1:9">
-      <c r="A152" s="119"/>
+      <c r="A152" s="120"/>
       <c r="B152" s="91">
         <v>123</v>
       </c>
       <c r="C152" s="92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D152" s="93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E152" s="94" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F152" s="94">
         <v>25</v>
@@ -6703,24 +6725,24 @@
       <c r="G152" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H152" s="96" t="s">
-        <v>22</v>
+      <c r="H152" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I152" s="97"/>
     </row>
     <row r="153" ht="18" customHeight="1" spans="1:9">
-      <c r="A153" s="121"/>
+      <c r="A153" s="122"/>
       <c r="B153" s="98">
         <v>124</v>
       </c>
       <c r="C153" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D153" s="99" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E153" s="94" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F153" s="94">
         <v>25</v>
@@ -6728,24 +6750,24 @@
       <c r="G153" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H153" s="96" t="s">
-        <v>22</v>
+      <c r="H153" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I153" s="100"/>
     </row>
     <row r="154" ht="18" customHeight="1" spans="1:9">
-      <c r="A154" s="121"/>
+      <c r="A154" s="122"/>
       <c r="B154" s="91">
         <v>125</v>
       </c>
       <c r="C154" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D154" s="93" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E154" s="94" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F154" s="94">
         <v>25</v>
@@ -6753,37 +6775,37 @@
       <c r="G154" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H154" s="96" t="s">
-        <v>22</v>
+      <c r="H154" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I154" s="97"/>
     </row>
     <row r="155" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A155" s="122" t="s">
-        <v>205</v>
-      </c>
-      <c r="B155" s="122"/>
-      <c r="C155" s="122"/>
-      <c r="D155" s="122"/>
-      <c r="E155" s="122"/>
-      <c r="F155" s="122"/>
-      <c r="G155" s="122"/>
-      <c r="H155" s="122"/>
-      <c r="I155" s="122"/>
+      <c r="A155" s="123" t="s">
+        <v>206</v>
+      </c>
+      <c r="B155" s="123"/>
+      <c r="C155" s="123"/>
+      <c r="D155" s="123"/>
+      <c r="E155" s="123"/>
+      <c r="F155" s="123"/>
+      <c r="G155" s="123"/>
+      <c r="H155" s="123"/>
+      <c r="I155" s="123"/>
     </row>
     <row r="156" ht="18" customHeight="1" spans="1:9">
-      <c r="A156" s="121"/>
+      <c r="A156" s="122"/>
       <c r="B156" s="91">
         <v>126</v>
       </c>
       <c r="C156" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D156" s="93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E156" s="94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F156" s="94">
         <v>26</v>
@@ -6791,24 +6813,24 @@
       <c r="G156" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H156" s="96" t="s">
-        <v>22</v>
+      <c r="H156" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I156" s="97"/>
     </row>
     <row r="157" ht="18" customHeight="1" spans="1:9">
-      <c r="A157" s="121"/>
+      <c r="A157" s="122"/>
       <c r="B157" s="98">
         <v>127</v>
       </c>
       <c r="C157" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D157" s="99" t="s">
+        <v>209</v>
+      </c>
+      <c r="E157" s="94" t="s">
         <v>208</v>
-      </c>
-      <c r="E157" s="94" t="s">
-        <v>207</v>
       </c>
       <c r="F157" s="94">
         <v>26</v>
@@ -6816,24 +6838,24 @@
       <c r="G157" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H157" s="96" t="s">
-        <v>22</v>
+      <c r="H157" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I157" s="100"/>
     </row>
     <row r="158" ht="18" customHeight="1" spans="1:9">
-      <c r="A158" s="121"/>
+      <c r="A158" s="122"/>
       <c r="B158" s="91">
         <v>128</v>
       </c>
       <c r="C158" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D158" s="93" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E158" s="94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F158" s="94">
         <v>26</v>
@@ -6841,24 +6863,24 @@
       <c r="G158" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H158" s="96" t="s">
-        <v>22</v>
+      <c r="H158" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I158" s="97"/>
     </row>
     <row r="159" ht="18" customHeight="1" spans="1:9">
-      <c r="A159" s="121"/>
+      <c r="A159" s="122"/>
       <c r="B159" s="98">
         <v>129</v>
       </c>
       <c r="C159" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D159" s="99" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E159" s="94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F159" s="94">
         <v>26</v>
@@ -6866,24 +6888,24 @@
       <c r="G159" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H159" s="96" t="s">
-        <v>22</v>
+      <c r="H159" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I159" s="100"/>
     </row>
     <row r="160" ht="18" customHeight="1" spans="1:9">
-      <c r="A160" s="121"/>
+      <c r="A160" s="122"/>
       <c r="B160" s="91">
         <v>130</v>
       </c>
       <c r="C160" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D160" s="93" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E160" s="94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F160" s="94">
         <v>26</v>
@@ -6891,37 +6913,37 @@
       <c r="G160" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H160" s="96" t="s">
-        <v>22</v>
+      <c r="H160" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I160" s="97"/>
     </row>
     <row r="161" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A161" s="122" t="s">
-        <v>212</v>
-      </c>
-      <c r="B161" s="122"/>
-      <c r="C161" s="122"/>
-      <c r="D161" s="122"/>
-      <c r="E161" s="122"/>
-      <c r="F161" s="122"/>
-      <c r="G161" s="122"/>
-      <c r="H161" s="122"/>
-      <c r="I161" s="122"/>
+      <c r="A161" s="123" t="s">
+        <v>213</v>
+      </c>
+      <c r="B161" s="123"/>
+      <c r="C161" s="123"/>
+      <c r="D161" s="123"/>
+      <c r="E161" s="123"/>
+      <c r="F161" s="123"/>
+      <c r="G161" s="123"/>
+      <c r="H161" s="123"/>
+      <c r="I161" s="123"/>
     </row>
     <row r="162" ht="18" customHeight="1" spans="1:9">
-      <c r="A162" s="121"/>
+      <c r="A162" s="122"/>
       <c r="B162" s="91">
         <v>131</v>
       </c>
       <c r="C162" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D162" s="93" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E162" s="94" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F162" s="94">
         <v>27</v>
@@ -6929,24 +6951,24 @@
       <c r="G162" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H162" s="96" t="s">
-        <v>22</v>
+      <c r="H162" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I162" s="97"/>
     </row>
     <row r="163" ht="18" customHeight="1" spans="1:9">
-      <c r="A163" s="121"/>
+      <c r="A163" s="122"/>
       <c r="B163" s="98">
         <v>132</v>
       </c>
       <c r="C163" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D163" s="99" t="s">
+        <v>216</v>
+      </c>
+      <c r="E163" s="94" t="s">
         <v>215</v>
-      </c>
-      <c r="E163" s="94" t="s">
-        <v>214</v>
       </c>
       <c r="F163" s="94">
         <v>27</v>
@@ -6954,24 +6976,24 @@
       <c r="G163" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H163" s="96" t="s">
-        <v>22</v>
+      <c r="H163" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I163" s="100"/>
     </row>
     <row r="164" ht="18" customHeight="1" spans="1:9">
-      <c r="A164" s="121"/>
+      <c r="A164" s="122"/>
       <c r="B164" s="91">
         <v>133</v>
       </c>
       <c r="C164" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D164" s="93" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E164" s="94" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F164" s="94">
         <v>27</v>
@@ -6979,24 +7001,24 @@
       <c r="G164" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H164" s="96" t="s">
-        <v>22</v>
+      <c r="H164" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I164" s="97"/>
     </row>
     <row r="165" ht="18" customHeight="1" spans="1:9">
-      <c r="A165" s="121"/>
+      <c r="A165" s="122"/>
       <c r="B165" s="98">
         <v>134</v>
       </c>
       <c r="C165" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D165" s="99" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E165" s="94" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F165" s="94">
         <v>27</v>
@@ -7004,24 +7026,24 @@
       <c r="G165" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H165" s="96" t="s">
-        <v>22</v>
+      <c r="H165" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I165" s="100"/>
     </row>
     <row r="166" ht="18" customHeight="1" spans="1:9">
-      <c r="A166" s="121"/>
+      <c r="A166" s="122"/>
       <c r="B166" s="91">
         <v>135</v>
       </c>
       <c r="C166" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D166" s="93" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E166" s="94" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F166" s="94">
         <v>27</v>
@@ -7029,37 +7051,37 @@
       <c r="G166" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H166" s="96" t="s">
-        <v>22</v>
+      <c r="H166" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I166" s="97"/>
     </row>
     <row r="167" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A167" s="122" t="s">
-        <v>219</v>
-      </c>
-      <c r="B167" s="122"/>
-      <c r="C167" s="122"/>
-      <c r="D167" s="122"/>
-      <c r="E167" s="122"/>
-      <c r="F167" s="122"/>
-      <c r="G167" s="122"/>
-      <c r="H167" s="122"/>
-      <c r="I167" s="122"/>
+      <c r="A167" s="123" t="s">
+        <v>220</v>
+      </c>
+      <c r="B167" s="123"/>
+      <c r="C167" s="123"/>
+      <c r="D167" s="123"/>
+      <c r="E167" s="123"/>
+      <c r="F167" s="123"/>
+      <c r="G167" s="123"/>
+      <c r="H167" s="123"/>
+      <c r="I167" s="123"/>
     </row>
     <row r="168" ht="18" customHeight="1" spans="1:9">
-      <c r="A168" s="121"/>
+      <c r="A168" s="122"/>
       <c r="B168" s="91">
         <v>136</v>
       </c>
       <c r="C168" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D168" s="93" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E168" s="94" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F168" s="94">
         <v>28</v>
@@ -7067,24 +7089,24 @@
       <c r="G168" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H168" s="96" t="s">
-        <v>22</v>
+      <c r="H168" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I168" s="97"/>
     </row>
     <row r="169" ht="18" customHeight="1" spans="1:9">
-      <c r="A169" s="121"/>
+      <c r="A169" s="122"/>
       <c r="B169" s="98">
         <v>137</v>
       </c>
       <c r="C169" s="92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D169" s="99" t="s">
+        <v>223</v>
+      </c>
+      <c r="E169" s="94" t="s">
         <v>222</v>
-      </c>
-      <c r="E169" s="94" t="s">
-        <v>221</v>
       </c>
       <c r="F169" s="94">
         <v>28</v>
@@ -7092,24 +7114,24 @@
       <c r="G169" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H169" s="96" t="s">
-        <v>22</v>
+      <c r="H169" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I169" s="100"/>
     </row>
     <row r="170" ht="18" customHeight="1" spans="1:9">
-      <c r="A170" s="123"/>
+      <c r="A170" s="124"/>
       <c r="B170" s="91">
         <v>138</v>
       </c>
       <c r="C170" s="92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D170" s="93" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E170" s="94" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F170" s="94">
         <v>28</v>
@@ -7117,24 +7139,24 @@
       <c r="G170" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H170" s="96" t="s">
-        <v>22</v>
+      <c r="H170" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I170" s="97"/>
     </row>
     <row r="171" ht="18" customHeight="1" spans="1:9">
-      <c r="A171" s="123"/>
+      <c r="A171" s="124"/>
       <c r="B171" s="98">
         <v>139</v>
       </c>
       <c r="C171" s="92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D171" s="99" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E171" s="94" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F171" s="94">
         <v>28</v>
@@ -7142,24 +7164,24 @@
       <c r="G171" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H171" s="96" t="s">
-        <v>22</v>
+      <c r="H171" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I171" s="100"/>
     </row>
     <row r="172" ht="18" customHeight="1" spans="1:9">
-      <c r="A172" s="123"/>
+      <c r="A172" s="124"/>
       <c r="B172" s="91">
         <v>140</v>
       </c>
       <c r="C172" s="92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D172" s="93" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E172" s="94" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F172" s="94">
         <v>28</v>
@@ -7167,37 +7189,37 @@
       <c r="G172" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H172" s="96" t="s">
-        <v>22</v>
+      <c r="H172" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I172" s="97"/>
     </row>
     <row r="173" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A173" s="124" t="s">
-        <v>227</v>
-      </c>
-      <c r="B173" s="124"/>
-      <c r="C173" s="124"/>
-      <c r="D173" s="124"/>
-      <c r="E173" s="124"/>
-      <c r="F173" s="124"/>
-      <c r="G173" s="124"/>
-      <c r="H173" s="124"/>
-      <c r="I173" s="124"/>
+      <c r="A173" s="125" t="s">
+        <v>228</v>
+      </c>
+      <c r="B173" s="125"/>
+      <c r="C173" s="125"/>
+      <c r="D173" s="125"/>
+      <c r="E173" s="125"/>
+      <c r="F173" s="125"/>
+      <c r="G173" s="125"/>
+      <c r="H173" s="125"/>
+      <c r="I173" s="125"/>
     </row>
     <row r="174" ht="18" customHeight="1" spans="1:9">
-      <c r="A174" s="123"/>
+      <c r="A174" s="124"/>
       <c r="B174" s="91">
         <v>141</v>
       </c>
       <c r="C174" s="92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D174" s="93" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E174" s="94" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F174" s="94">
         <v>29</v>
@@ -7205,24 +7227,24 @@
       <c r="G174" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H174" s="96" t="s">
-        <v>22</v>
+      <c r="H174" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I174" s="97"/>
     </row>
     <row r="175" ht="18" customHeight="1" spans="1:9">
-      <c r="A175" s="123"/>
+      <c r="A175" s="124"/>
       <c r="B175" s="98">
         <v>142</v>
       </c>
       <c r="C175" s="92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D175" s="99" t="s">
+        <v>231</v>
+      </c>
+      <c r="E175" s="94" t="s">
         <v>230</v>
-      </c>
-      <c r="E175" s="94" t="s">
-        <v>229</v>
       </c>
       <c r="F175" s="94">
         <v>29</v>
@@ -7230,24 +7252,24 @@
       <c r="G175" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H175" s="96" t="s">
-        <v>22</v>
+      <c r="H175" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I175" s="100"/>
     </row>
     <row r="176" ht="18" customHeight="1" spans="1:9">
-      <c r="A176" s="125"/>
+      <c r="A176" s="126"/>
       <c r="B176" s="91">
         <v>143</v>
       </c>
       <c r="C176" s="92" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D176" s="93" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E176" s="94" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F176" s="94">
         <v>29</v>
@@ -7255,24 +7277,24 @@
       <c r="G176" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H176" s="96" t="s">
-        <v>22</v>
+      <c r="H176" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I176" s="97"/>
     </row>
     <row r="177" ht="18" customHeight="1" spans="1:9">
-      <c r="A177" s="125"/>
+      <c r="A177" s="126"/>
       <c r="B177" s="98">
         <v>144</v>
       </c>
       <c r="C177" s="92" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D177" s="99" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E177" s="94" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F177" s="94">
         <v>29</v>
@@ -7280,24 +7302,24 @@
       <c r="G177" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H177" s="96" t="s">
-        <v>22</v>
+      <c r="H177" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I177" s="100"/>
     </row>
     <row r="178" ht="18" customHeight="1" spans="1:9">
-      <c r="A178" s="125"/>
+      <c r="A178" s="126"/>
       <c r="B178" s="91">
         <v>145</v>
       </c>
       <c r="C178" s="92" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D178" s="93" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E178" s="94" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F178" s="94">
         <v>29</v>
@@ -7305,37 +7327,37 @@
       <c r="G178" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H178" s="96" t="s">
-        <v>22</v>
+      <c r="H178" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I178" s="97"/>
     </row>
     <row r="179" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A179" s="126" t="s">
-        <v>235</v>
-      </c>
-      <c r="B179" s="126"/>
-      <c r="C179" s="126"/>
-      <c r="D179" s="126"/>
-      <c r="E179" s="126"/>
-      <c r="F179" s="126"/>
-      <c r="G179" s="126"/>
-      <c r="H179" s="126"/>
-      <c r="I179" s="126"/>
+      <c r="A179" s="127" t="s">
+        <v>236</v>
+      </c>
+      <c r="B179" s="127"/>
+      <c r="C179" s="127"/>
+      <c r="D179" s="127"/>
+      <c r="E179" s="127"/>
+      <c r="F179" s="127"/>
+      <c r="G179" s="127"/>
+      <c r="H179" s="127"/>
+      <c r="I179" s="127"/>
     </row>
     <row r="180" ht="18" customHeight="1" spans="1:9">
-      <c r="A180" s="125"/>
+      <c r="A180" s="126"/>
       <c r="B180" s="91">
         <v>146</v>
       </c>
       <c r="C180" s="92" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D180" s="93" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E180" s="94" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F180" s="94">
         <v>30</v>
@@ -7343,24 +7365,24 @@
       <c r="G180" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H180" s="96" t="s">
-        <v>22</v>
+      <c r="H180" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I180" s="97"/>
     </row>
     <row r="181" ht="18" customHeight="1" spans="1:9">
-      <c r="A181" s="125"/>
+      <c r="A181" s="126"/>
       <c r="B181" s="98">
         <v>147</v>
       </c>
       <c r="C181" s="92" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D181" s="99" t="s">
+        <v>239</v>
+      </c>
+      <c r="E181" s="94" t="s">
         <v>238</v>
-      </c>
-      <c r="E181" s="94" t="s">
-        <v>237</v>
       </c>
       <c r="F181" s="94">
         <v>30</v>
@@ -7368,24 +7390,24 @@
       <c r="G181" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H181" s="96" t="s">
-        <v>22</v>
+      <c r="H181" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I181" s="100"/>
     </row>
     <row r="182" ht="18" customHeight="1" spans="1:9">
-      <c r="A182" s="127"/>
+      <c r="A182" s="128"/>
       <c r="B182" s="91">
         <v>148</v>
       </c>
       <c r="C182" s="92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D182" s="93" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E182" s="94" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F182" s="94">
         <v>30</v>
@@ -7393,24 +7415,24 @@
       <c r="G182" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H182" s="96" t="s">
-        <v>22</v>
+      <c r="H182" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I182" s="97"/>
     </row>
     <row r="183" ht="18" customHeight="1" spans="1:9">
-      <c r="A183" s="127"/>
+      <c r="A183" s="128"/>
       <c r="B183" s="98">
         <v>149</v>
       </c>
       <c r="C183" s="92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D183" s="99" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E183" s="94" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F183" s="94">
         <v>30</v>
@@ -7418,24 +7440,24 @@
       <c r="G183" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H183" s="96" t="s">
-        <v>22</v>
+      <c r="H183" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I183" s="100"/>
     </row>
     <row r="184" ht="18" customHeight="1" spans="1:9">
-      <c r="A184" s="127"/>
+      <c r="A184" s="128"/>
       <c r="B184" s="91">
         <v>150</v>
       </c>
       <c r="C184" s="92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D184" s="93" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E184" s="94" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F184" s="94">
         <v>30</v>
@@ -7443,37 +7465,37 @@
       <c r="G184" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H184" s="96" t="s">
-        <v>22</v>
+      <c r="H184" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I184" s="97"/>
     </row>
     <row r="185" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A185" s="128" t="s">
-        <v>243</v>
-      </c>
-      <c r="B185" s="128"/>
-      <c r="C185" s="128"/>
-      <c r="D185" s="128"/>
-      <c r="E185" s="128"/>
-      <c r="F185" s="128"/>
-      <c r="G185" s="128"/>
-      <c r="H185" s="128"/>
-      <c r="I185" s="128"/>
+      <c r="A185" s="129" t="s">
+        <v>244</v>
+      </c>
+      <c r="B185" s="129"/>
+      <c r="C185" s="129"/>
+      <c r="D185" s="129"/>
+      <c r="E185" s="129"/>
+      <c r="F185" s="129"/>
+      <c r="G185" s="129"/>
+      <c r="H185" s="129"/>
+      <c r="I185" s="129"/>
     </row>
     <row r="186" ht="18" customHeight="1" spans="1:9">
-      <c r="A186" s="127"/>
+      <c r="A186" s="128"/>
       <c r="B186" s="91">
         <v>151</v>
       </c>
       <c r="C186" s="92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D186" s="93" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E186" s="94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F186" s="94">
         <v>31</v>
@@ -7481,24 +7503,24 @@
       <c r="G186" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H186" s="96" t="s">
-        <v>22</v>
+      <c r="H186" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I186" s="97"/>
     </row>
     <row r="187" ht="18" customHeight="1" spans="1:9">
-      <c r="A187" s="127"/>
+      <c r="A187" s="128"/>
       <c r="B187" s="98">
         <v>152</v>
       </c>
       <c r="C187" s="92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D187" s="99" t="s">
+        <v>247</v>
+      </c>
+      <c r="E187" s="94" t="s">
         <v>246</v>
-      </c>
-      <c r="E187" s="94" t="s">
-        <v>245</v>
       </c>
       <c r="F187" s="94">
         <v>31</v>
@@ -7506,24 +7528,24 @@
       <c r="G187" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H187" s="96" t="s">
-        <v>22</v>
+      <c r="H187" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I187" s="100"/>
     </row>
     <row r="188" ht="18" customHeight="1" spans="1:9">
-      <c r="A188" s="127"/>
+      <c r="A188" s="128"/>
       <c r="B188" s="91">
         <v>153</v>
       </c>
       <c r="C188" s="92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D188" s="93" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E188" s="94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F188" s="94">
         <v>31</v>
@@ -7531,8 +7553,8 @@
       <c r="G188" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H188" s="96" t="s">
-        <v>22</v>
+      <c r="H188" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I188" s="97"/>
     </row>
@@ -7542,13 +7564,13 @@
         <v>154</v>
       </c>
       <c r="C189" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D189" s="99" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E189" s="94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F189" s="94">
         <v>31</v>
@@ -7556,8 +7578,8 @@
       <c r="G189" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H189" s="96" t="s">
-        <v>22</v>
+      <c r="H189" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I189" s="100"/>
     </row>
@@ -7567,13 +7589,13 @@
         <v>155</v>
       </c>
       <c r="C190" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D190" s="93" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E190" s="94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F190" s="94">
         <v>31</v>
@@ -7581,14 +7603,14 @@
       <c r="G190" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H190" s="96" t="s">
-        <v>22</v>
+      <c r="H190" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I190" s="97"/>
     </row>
     <row r="191" ht="16.5" customHeight="1" spans="1:9">
       <c r="A191" s="89" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B191" s="89"/>
       <c r="C191" s="89"/>
@@ -7605,13 +7627,13 @@
         <v>156</v>
       </c>
       <c r="C192" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D192" s="93" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E192" s="94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F192" s="94">
         <v>32</v>
@@ -7619,8 +7641,8 @@
       <c r="G192" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H192" s="96" t="s">
-        <v>22</v>
+      <c r="H192" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I192" s="97"/>
     </row>
@@ -7630,13 +7652,13 @@
         <v>157</v>
       </c>
       <c r="C193" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D193" s="99" t="s">
+        <v>255</v>
+      </c>
+      <c r="E193" s="94" t="s">
         <v>254</v>
-      </c>
-      <c r="E193" s="94" t="s">
-        <v>253</v>
       </c>
       <c r="F193" s="94">
         <v>32</v>
@@ -7644,8 +7666,8 @@
       <c r="G193" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H193" s="96" t="s">
-        <v>22</v>
+      <c r="H193" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I193" s="100"/>
     </row>
@@ -7655,13 +7677,13 @@
         <v>158</v>
       </c>
       <c r="C194" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D194" s="93" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E194" s="94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F194" s="94">
         <v>32</v>
@@ -7669,8 +7691,8 @@
       <c r="G194" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H194" s="96" t="s">
-        <v>22</v>
+      <c r="H194" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I194" s="97"/>
     </row>
@@ -7680,13 +7702,13 @@
         <v>159</v>
       </c>
       <c r="C195" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D195" s="99" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E195" s="94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F195" s="94">
         <v>32</v>
@@ -7694,8 +7716,8 @@
       <c r="G195" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H195" s="96" t="s">
-        <v>22</v>
+      <c r="H195" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I195" s="100"/>
     </row>
@@ -7705,13 +7727,13 @@
         <v>160</v>
       </c>
       <c r="C196" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D196" s="93" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E196" s="94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F196" s="94">
         <v>32</v>
@@ -7719,14 +7741,14 @@
       <c r="G196" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H196" s="96" t="s">
-        <v>22</v>
+      <c r="H196" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I196" s="97"/>
     </row>
     <row r="197" ht="16.5" customHeight="1" spans="1:9">
       <c r="A197" s="89" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B197" s="89"/>
       <c r="C197" s="89"/>
@@ -7743,13 +7765,13 @@
         <v>161</v>
       </c>
       <c r="C198" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D198" s="93" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E198" s="94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F198" s="94">
         <v>33</v>
@@ -7757,8 +7779,8 @@
       <c r="G198" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H198" s="96" t="s">
-        <v>22</v>
+      <c r="H198" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I198" s="97"/>
     </row>
@@ -7768,13 +7790,13 @@
         <v>162</v>
       </c>
       <c r="C199" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D199" s="99" t="s">
+        <v>262</v>
+      </c>
+      <c r="E199" s="94" t="s">
         <v>261</v>
-      </c>
-      <c r="E199" s="94" t="s">
-        <v>260</v>
       </c>
       <c r="F199" s="94">
         <v>33</v>
@@ -7782,8 +7804,8 @@
       <c r="G199" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H199" s="96" t="s">
-        <v>22</v>
+      <c r="H199" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I199" s="100"/>
     </row>
@@ -7793,13 +7815,13 @@
         <v>163</v>
       </c>
       <c r="C200" s="92" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D200" s="93" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E200" s="94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F200" s="94">
         <v>33</v>
@@ -7807,24 +7829,24 @@
       <c r="G200" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H200" s="96" t="s">
-        <v>22</v>
+      <c r="H200" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I200" s="97"/>
     </row>
     <row r="201" ht="18" customHeight="1" spans="1:9">
-      <c r="A201" s="101"/>
+      <c r="A201" s="102"/>
       <c r="B201" s="98">
         <v>164</v>
       </c>
       <c r="C201" s="92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D201" s="99" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E201" s="94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F201" s="94">
         <v>33</v>
@@ -7832,24 +7854,24 @@
       <c r="G201" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H201" s="96" t="s">
-        <v>22</v>
+      <c r="H201" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I201" s="100"/>
     </row>
     <row r="202" ht="18" customHeight="1" spans="1:9">
-      <c r="A202" s="101"/>
+      <c r="A202" s="102"/>
       <c r="B202" s="91">
         <v>165</v>
       </c>
       <c r="C202" s="92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D202" s="93" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E202" s="94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F202" s="94">
         <v>33</v>
@@ -7857,37 +7879,37 @@
       <c r="G202" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H202" s="96" t="s">
-        <v>22</v>
+      <c r="H202" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I202" s="97"/>
     </row>
     <row r="203" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A203" s="102" t="s">
-        <v>266</v>
-      </c>
-      <c r="B203" s="102"/>
-      <c r="C203" s="102"/>
-      <c r="D203" s="102"/>
-      <c r="E203" s="102"/>
-      <c r="F203" s="102"/>
-      <c r="G203" s="102"/>
-      <c r="H203" s="102"/>
-      <c r="I203" s="102"/>
+      <c r="A203" s="103" t="s">
+        <v>267</v>
+      </c>
+      <c r="B203" s="103"/>
+      <c r="C203" s="103"/>
+      <c r="D203" s="103"/>
+      <c r="E203" s="103"/>
+      <c r="F203" s="103"/>
+      <c r="G203" s="103"/>
+      <c r="H203" s="103"/>
+      <c r="I203" s="103"/>
     </row>
     <row r="204" ht="18" customHeight="1" spans="1:9">
-      <c r="A204" s="101"/>
+      <c r="A204" s="102"/>
       <c r="B204" s="91">
         <v>166</v>
       </c>
       <c r="C204" s="92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D204" s="93" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E204" s="94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F204" s="94">
         <v>34</v>
@@ -7895,24 +7917,24 @@
       <c r="G204" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H204" s="96" t="s">
-        <v>22</v>
+      <c r="H204" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I204" s="97"/>
     </row>
     <row r="205" ht="18" customHeight="1" spans="1:9">
-      <c r="A205" s="101"/>
+      <c r="A205" s="102"/>
       <c r="B205" s="98">
         <v>167</v>
       </c>
       <c r="C205" s="92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D205" s="99" t="s">
+        <v>270</v>
+      </c>
+      <c r="E205" s="94" t="s">
         <v>269</v>
-      </c>
-      <c r="E205" s="94" t="s">
-        <v>268</v>
       </c>
       <c r="F205" s="94">
         <v>34</v>
@@ -7920,24 +7942,24 @@
       <c r="G205" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H205" s="96" t="s">
-        <v>22</v>
+      <c r="H205" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I205" s="100"/>
     </row>
     <row r="206" ht="18" customHeight="1" spans="1:9">
-      <c r="A206" s="101"/>
+      <c r="A206" s="102"/>
       <c r="B206" s="91">
         <v>168</v>
       </c>
       <c r="C206" s="92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D206" s="93" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E206" s="94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F206" s="94">
         <v>34</v>
@@ -7945,24 +7967,24 @@
       <c r="G206" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H206" s="96" t="s">
-        <v>22</v>
+      <c r="H206" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I206" s="97"/>
     </row>
     <row r="207" ht="18" customHeight="1" spans="1:9">
-      <c r="A207" s="101"/>
+      <c r="A207" s="102"/>
       <c r="B207" s="98">
         <v>169</v>
       </c>
       <c r="C207" s="92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D207" s="99" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E207" s="94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F207" s="94">
         <v>34</v>
@@ -7970,24 +7992,24 @@
       <c r="G207" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H207" s="96" t="s">
-        <v>22</v>
+      <c r="H207" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I207" s="100"/>
     </row>
     <row r="208" ht="18" customHeight="1" spans="1:9">
-      <c r="A208" s="101"/>
+      <c r="A208" s="102"/>
       <c r="B208" s="91">
         <v>170</v>
       </c>
       <c r="C208" s="92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D208" s="93" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E208" s="94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F208" s="94">
         <v>34</v>
@@ -7995,37 +8017,37 @@
       <c r="G208" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H208" s="96" t="s">
-        <v>22</v>
+      <c r="H208" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I208" s="97"/>
     </row>
     <row r="209" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A209" s="104" t="s">
-        <v>273</v>
-      </c>
-      <c r="B209" s="104"/>
-      <c r="C209" s="104"/>
-      <c r="D209" s="104"/>
-      <c r="E209" s="104"/>
-      <c r="F209" s="104"/>
-      <c r="G209" s="104"/>
-      <c r="H209" s="104"/>
-      <c r="I209" s="104"/>
+      <c r="A209" s="105" t="s">
+        <v>274</v>
+      </c>
+      <c r="B209" s="105"/>
+      <c r="C209" s="105"/>
+      <c r="D209" s="105"/>
+      <c r="E209" s="105"/>
+      <c r="F209" s="105"/>
+      <c r="G209" s="105"/>
+      <c r="H209" s="105"/>
+      <c r="I209" s="105"/>
     </row>
     <row r="210" ht="18" customHeight="1" spans="1:9">
-      <c r="A210" s="103"/>
+      <c r="A210" s="104"/>
       <c r="B210" s="91">
         <v>171</v>
       </c>
       <c r="C210" s="92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D210" s="93" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E210" s="94" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F210" s="94">
         <v>35</v>
@@ -8033,24 +8055,24 @@
       <c r="G210" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H210" s="96" t="s">
-        <v>22</v>
+      <c r="H210" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I210" s="97"/>
     </row>
     <row r="211" ht="18" customHeight="1" spans="1:9">
-      <c r="A211" s="103"/>
+      <c r="A211" s="104"/>
       <c r="B211" s="98">
         <v>172</v>
       </c>
       <c r="C211" s="92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D211" s="99" t="s">
+        <v>278</v>
+      </c>
+      <c r="E211" s="94" t="s">
         <v>277</v>
-      </c>
-      <c r="E211" s="94" t="s">
-        <v>276</v>
       </c>
       <c r="F211" s="94">
         <v>35</v>
@@ -8058,24 +8080,24 @@
       <c r="G211" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H211" s="96" t="s">
-        <v>22</v>
+      <c r="H211" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I211" s="100"/>
     </row>
     <row r="212" ht="18" customHeight="1" spans="1:9">
-      <c r="A212" s="103"/>
+      <c r="A212" s="104"/>
       <c r="B212" s="91">
         <v>173</v>
       </c>
       <c r="C212" s="92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D212" s="93" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E212" s="94" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F212" s="94">
         <v>35</v>
@@ -8083,24 +8105,24 @@
       <c r="G212" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H212" s="96" t="s">
-        <v>22</v>
+      <c r="H212" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I212" s="97"/>
     </row>
     <row r="213" ht="18" customHeight="1" spans="1:9">
-      <c r="A213" s="103"/>
+      <c r="A213" s="104"/>
       <c r="B213" s="98">
         <v>174</v>
       </c>
       <c r="C213" s="92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D213" s="99" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E213" s="94" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F213" s="94">
         <v>35</v>
@@ -8108,24 +8130,24 @@
       <c r="G213" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H213" s="96" t="s">
-        <v>22</v>
+      <c r="H213" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I213" s="100"/>
     </row>
     <row r="214" ht="18" customHeight="1" spans="1:9">
-      <c r="A214" s="103"/>
+      <c r="A214" s="104"/>
       <c r="B214" s="91">
         <v>175</v>
       </c>
       <c r="C214" s="92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D214" s="93" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E214" s="94" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F214" s="94">
         <v>35</v>
@@ -8133,37 +8155,37 @@
       <c r="G214" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H214" s="96" t="s">
-        <v>22</v>
+      <c r="H214" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I214" s="97"/>
     </row>
     <row r="215" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A215" s="104" t="s">
-        <v>281</v>
-      </c>
-      <c r="B215" s="104"/>
-      <c r="C215" s="104"/>
-      <c r="D215" s="104"/>
-      <c r="E215" s="104"/>
-      <c r="F215" s="104"/>
-      <c r="G215" s="104"/>
-      <c r="H215" s="104"/>
-      <c r="I215" s="104"/>
+      <c r="A215" s="105" t="s">
+        <v>282</v>
+      </c>
+      <c r="B215" s="105"/>
+      <c r="C215" s="105"/>
+      <c r="D215" s="105"/>
+      <c r="E215" s="105"/>
+      <c r="F215" s="105"/>
+      <c r="G215" s="105"/>
+      <c r="H215" s="105"/>
+      <c r="I215" s="105"/>
     </row>
     <row r="216" ht="18" customHeight="1" spans="1:9">
-      <c r="A216" s="103"/>
+      <c r="A216" s="104"/>
       <c r="B216" s="91">
         <v>176</v>
       </c>
       <c r="C216" s="92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D216" s="93" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E216" s="94" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F216" s="94">
         <v>36</v>
@@ -8171,8 +8193,8 @@
       <c r="G216" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H216" s="96" t="s">
-        <v>22</v>
+      <c r="H216" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="I216" s="97"/>
     </row>
@@ -8219,8 +8241,18 @@
     <mergeCell ref="A209:I209"/>
     <mergeCell ref="A215:I215"/>
   </mergeCells>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"✅ Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H$1:H$1048576">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Done+$H$12"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Use dropdown options only" sqref="H5:H217">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Use dropdown options only" sqref="H5 H17 H23 H24 H25 H6:H7 H8:H11 H12:H16 H18:H22 H26:H217">
       <formula1>"✅ Done,🔄 In Progress,⏸ Paused,❌ Skipped,⬜ Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8244,7 +8276,7 @@
   <sheetData>
     <row r="1" ht="25.9" spans="1:10">
       <c r="A1" s="42" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -8258,19 +8290,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="C4" s="43" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D4" s="43"/>
       <c r="E4" s="44" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="45" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H4" s="45"/>
       <c r="I4" s="46" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J4" s="46"/>
     </row>
@@ -8286,12 +8318,12 @@
     </row>
     <row r="6" ht="32.8" spans="1:10">
       <c r="C6" s="47" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D6" s="47"/>
       <c r="E6" s="48">
         <f>COUNTIF('📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="49">
@@ -8301,13 +8333,13 @@
       <c r="H6" s="49"/>
       <c r="I6" s="50">
         <f>COUNTIF('📚 Study Plan'!H:H,"⬜ Not Started")</f>
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J6" s="50"/>
     </row>
     <row r="8" spans="1:10">
       <c r="C8" s="51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D8" s="51"/>
       <c r="E8" s="51"/>
@@ -8320,7 +8352,7 @@
     <row r="9" ht="35.1" spans="1:10">
       <c r="C9" s="52">
         <f>COUNTIF('📚 Study Plan'!H:H,"✅ Done")/176</f>
-        <v>0.0113636363636364</v>
+        <v>0.0738636363636364</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -8332,7 +8364,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="C11" s="51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
@@ -8347,22 +8379,22 @@
         <v>5</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H12" s="53" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I12" s="53" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J12" s="53"/>
     </row>
@@ -8375,7 +8407,7 @@
       </c>
       <c r="E13" s="55">
         <f>COUNTIFS('📚 Study Plan'!C:C,C13,'📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F13" s="56">
         <f>COUNTIFS('📚 Study Plan'!C:C,C13,'📚 Study Plan'!H:H,"🔄 In Progress")</f>
@@ -8387,17 +8419,17 @@
       </c>
       <c r="H13" s="58">
         <f>COUNTIFS('📚 Study Plan'!C:C,C13,'📚 Study Plan'!H:H,"❌ Skipped")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" s="59">
         <f t="shared" ref="I13:I30" si="0">D13-E13-F13-G13-H13</f>
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J13" s="59"/>
     </row>
     <row r="14" ht="24.2" spans="1:10">
       <c r="C14" s="60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" s="9">
         <v>7</v>
@@ -8426,7 +8458,7 @@
     </row>
     <row r="15" ht="36.3" spans="1:10">
       <c r="C15" s="66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" s="5">
         <v>19</v>
@@ -8455,7 +8487,7 @@
     </row>
     <row r="16" ht="24.2" spans="1:10">
       <c r="C16" s="67" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D16" s="9">
         <v>12</v>
@@ -8484,7 +8516,7 @@
     </row>
     <row r="17" ht="24.2" spans="3:10">
       <c r="C17" s="68" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D17" s="5">
         <v>17</v>
@@ -8513,7 +8545,7 @@
     </row>
     <row r="18" ht="24.2" spans="3:10">
       <c r="C18" s="69" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D18" s="9">
         <v>11</v>
@@ -8542,7 +8574,7 @@
     </row>
     <row r="19" ht="24.2" spans="3:10">
       <c r="C19" s="70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D19" s="5">
         <v>8</v>
@@ -8571,7 +8603,7 @@
     </row>
     <row r="20" ht="24.2" spans="3:10">
       <c r="C20" s="71" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D20" s="9">
         <v>7</v>
@@ -8600,7 +8632,7 @@
     </row>
     <row r="21" ht="24.2" spans="3:10">
       <c r="C21" s="72" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D21" s="5">
         <v>9</v>
@@ -8629,7 +8661,7 @@
     </row>
     <row r="22" ht="24.2" spans="3:10">
       <c r="C22" s="73" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D22" s="9">
         <v>5</v>
@@ -8658,7 +8690,7 @@
     </row>
     <row r="23" ht="24.2" spans="3:10">
       <c r="C23" s="74" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D23" s="5">
         <v>9</v>
@@ -8687,7 +8719,7 @@
     </row>
     <row r="24" ht="24.2" spans="3:10">
       <c r="C24" s="75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D24" s="9">
         <v>14</v>
@@ -8716,7 +8748,7 @@
     </row>
     <row r="25" spans="3:10">
       <c r="C25" s="76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D25" s="5">
         <v>5</v>
@@ -8745,7 +8777,7 @@
     </row>
     <row r="26" ht="24.2" spans="3:10">
       <c r="C26" s="77" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D26" s="9">
         <v>5</v>
@@ -8774,7 +8806,7 @@
     </row>
     <row r="27" ht="24.2" spans="3:10">
       <c r="C27" s="78" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D27" s="5">
         <v>6</v>
@@ -8803,7 +8835,7 @@
     </row>
     <row r="28" ht="24.2" spans="3:10">
       <c r="C28" s="54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D28" s="9">
         <v>10</v>
@@ -8832,7 +8864,7 @@
     </row>
     <row r="29" ht="24.2" spans="3:10">
       <c r="C29" s="60" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D29" s="5">
         <v>7</v>
@@ -8861,7 +8893,7 @@
     </row>
     <row r="30" ht="24.2" spans="3:10">
       <c r="C30" s="66" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D30" s="9">
         <v>6</v>
@@ -8890,7 +8922,7 @@
     </row>
     <row r="31" spans="3:10">
       <c r="C31" s="41" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D31" s="41">
         <f t="shared" ref="D31:I31" si="1">SUM(D13:D30)</f>
@@ -8898,7 +8930,7 @@
       </c>
       <c r="E31" s="41">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F31" s="41">
         <f t="shared" si="1"/>
@@ -8910,17 +8942,17 @@
       </c>
       <c r="H31" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I31" s="41">
         <f t="shared" si="1"/>
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J31" s="41"/>
     </row>
     <row r="33" spans="3:10">
       <c r="C33" s="79" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D33" s="79"/>
       <c r="E33" s="79"/>
@@ -8986,7 +9018,7 @@
   <sheetData>
     <row r="1" ht="20.7" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8999,13 +9031,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -9020,13 +9052,13 @@
         <v>4</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7"/>
       <c r="B4" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="9">
         <v>7</v>
@@ -9035,13 +9067,13 @@
         <v>2</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" ht="24.2" spans="1:5">
       <c r="A5" s="11"/>
       <c r="B5" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" s="5">
         <v>19</v>
@@ -9050,13 +9082,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="9">
         <v>12</v>
@@ -9065,13 +9097,13 @@
         <v>3</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="15"/>
       <c r="B7" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="5">
         <v>17</v>
@@ -9080,13 +9112,13 @@
         <v>4</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="17"/>
       <c r="B8" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="9">
         <v>11</v>
@@ -9095,13 +9127,13 @@
         <v>3</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="19"/>
       <c r="B9" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C9" s="5">
         <v>8</v>
@@ -9110,13 +9142,13 @@
         <v>2</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="21"/>
       <c r="B10" s="22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C10" s="9">
         <v>7</v>
@@ -9125,13 +9157,13 @@
         <v>2</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="23"/>
       <c r="B11" s="24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C11" s="5">
         <v>9</v>
@@ -9140,13 +9172,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="25"/>
       <c r="B12" s="26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C12" s="9">
         <v>5</v>
@@ -9155,13 +9187,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="27"/>
       <c r="B13" s="28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C13" s="5">
         <v>9</v>
@@ -9170,13 +9202,13 @@
         <v>2</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="29"/>
       <c r="B14" s="30" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C14" s="9">
         <v>14</v>
@@ -9185,13 +9217,13 @@
         <v>3</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="31"/>
       <c r="B15" s="32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C15" s="5">
         <v>5</v>
@@ -9200,13 +9232,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="33"/>
       <c r="B16" s="34" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C16" s="9">
         <v>5</v>
@@ -9215,13 +9247,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="35"/>
       <c r="B17" s="36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C17" s="5">
         <v>6</v>
@@ -9230,13 +9262,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3"/>
       <c r="B18" s="37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C18" s="9">
         <v>10</v>
@@ -9245,13 +9277,13 @@
         <v>2</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7"/>
       <c r="B19" s="38" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C19" s="5">
         <v>7</v>
@@ -9260,13 +9292,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="11"/>
       <c r="B20" s="39" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C20" s="9">
         <v>6</v>
@@ -9275,13 +9307,13 @@
         <v>2</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="40"/>
       <c r="B21" s="41" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C21" s="41">
         <v>176</v>

--- a/01.Study Plan/02_aspnet_study_plan_v2.xlsx
+++ b/01.Study Plan/02_aspnet_study_plan_v2.xlsx
@@ -169,136 +169,136 @@
     <t>Singleton vs Scoped vs Transient in ASP.NET Core Web API</t>
   </si>
   <si>
+    <t>Swagger API in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>ASP.NET Core Web API – Routing</t>
+  </si>
+  <si>
+    <t>Routing in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 5  —  Friday, 22 May 2026   ·   Topics 21 – 25</t>
+  </si>
+  <si>
+    <t>Route Parameters and Query Strings in Routing</t>
+  </si>
+  <si>
+    <t>22-May-2026</t>
+  </si>
+  <si>
+    <t>Multiple URLs for a Single Resource in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>Token Replacement in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>Route Prefix in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>Route Constraints in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 6  —  Saturday, 23 May 2026   ·   Topics 26 – 30</t>
+  </si>
+  <si>
+    <t>How Routing Works in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>23-May-2026</t>
+  </si>
+  <si>
+    <t>ASP.NET Core Web API – Return Types and Status Codes</t>
+  </si>
+  <si>
+    <t>Action Return Types in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>HTTP Status Codes in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>200 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>201 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 7  —  Sunday, 24 May 2026   ·   Topics 31 – 35</t>
+  </si>
+  <si>
+    <t>202 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>24-May-2026</t>
+  </si>
+  <si>
+    <t>204 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>301 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>302 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>304 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 8  —  Monday, 25 May 2026   ·   Topics 36 – 40</t>
+  </si>
+  <si>
+    <t>400 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>25-May-2026</t>
+  </si>
+  <si>
+    <t>401 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>403 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>404 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>405 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 9  —  Tuesday, 26 May 2026   ·   Topics 41 – 45</t>
+  </si>
+  <si>
+    <t>Configure Allowed HTTP Methods Globally in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>26-May-2026</t>
+  </si>
+  <si>
+    <t>500 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>501 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>503 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>504 HTTP Status Code in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 10  —  Wednesday, 27 May 2026   ·   Topics 46 – 50</t>
+  </si>
+  <si>
+    <t>ASP.NET Core Web API – Model Binding</t>
+  </si>
+  <si>
+    <t>Model Binding in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>27-May-2026</t>
+  </si>
+  <si>
     <t>⬜ Not Started</t>
-  </si>
-  <si>
-    <t>Swagger API in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>ASP.NET Core Web API – Routing</t>
-  </si>
-  <si>
-    <t>Routing in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 5  —  Friday, 22 May 2026   ·   Topics 21 – 25</t>
-  </si>
-  <si>
-    <t>Route Parameters and Query Strings in Routing</t>
-  </si>
-  <si>
-    <t>22-May-2026</t>
-  </si>
-  <si>
-    <t>Multiple URLs for a Single Resource in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>Token Replacement in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>Route Prefix in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>Route Constraints in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 6  —  Saturday, 23 May 2026   ·   Topics 26 – 30</t>
-  </si>
-  <si>
-    <t>How Routing Works in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>23-May-2026</t>
-  </si>
-  <si>
-    <t>ASP.NET Core Web API – Return Types and Status Codes</t>
-  </si>
-  <si>
-    <t>Action Return Types in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>HTTP Status Codes in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>200 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>201 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 7  —  Sunday, 24 May 2026   ·   Topics 31 – 35</t>
-  </si>
-  <si>
-    <t>202 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>24-May-2026</t>
-  </si>
-  <si>
-    <t>204 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>301 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>302 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>304 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 8  —  Monday, 25 May 2026   ·   Topics 36 – 40</t>
-  </si>
-  <si>
-    <t>400 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>25-May-2026</t>
-  </si>
-  <si>
-    <t>401 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>403 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>404 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>405 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 9  —  Tuesday, 26 May 2026   ·   Topics 41 – 45</t>
-  </si>
-  <si>
-    <t>Configure Allowed HTTP Methods Globally in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>26-May-2026</t>
-  </si>
-  <si>
-    <t>500 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>501 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>503 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>504 HTTP Status Code in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 10  —  Wednesday, 27 May 2026   ·   Topics 46 – 50</t>
-  </si>
-  <si>
-    <t>ASP.NET Core Web API – Model Binding</t>
-  </si>
-  <si>
-    <t>Model Binding in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>27-May-2026</t>
   </si>
   <si>
     <t>Model Binding using FromForm in ASP.NET Core Web API</t>
@@ -3827,8 +3827,8 @@
       <c r="G26" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="101" t="s">
-        <v>46</v>
+      <c r="H26" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I26" s="97"/>
     </row>
@@ -3841,7 +3841,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" s="94" t="s">
         <v>43</v>
@@ -3852,8 +3852,8 @@
       <c r="G27" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H27" s="101" t="s">
-        <v>46</v>
+      <c r="H27" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I27" s="100"/>
     </row>
@@ -3863,10 +3863,10 @@
         <v>20</v>
       </c>
       <c r="C28" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="93" t="s">
         <v>48</v>
-      </c>
-      <c r="D28" s="93" t="s">
-        <v>49</v>
       </c>
       <c r="E28" s="94" t="s">
         <v>43</v>
@@ -3877,14 +3877,14 @@
       <c r="G28" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="101" t="s">
-        <v>46</v>
+      <c r="H28" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I28" s="97"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:9">
       <c r="A29" s="103" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" s="103"/>
       <c r="C29" s="103"/>
@@ -3901,13 +3901,13 @@
         <v>21</v>
       </c>
       <c r="C30" s="92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D30" s="93" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="94" t="s">
         <v>51</v>
-      </c>
-      <c r="E30" s="94" t="s">
-        <v>52</v>
       </c>
       <c r="F30" s="94">
         <v>5</v>
@@ -3915,8 +3915,8 @@
       <c r="G30" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H30" s="101" t="s">
-        <v>46</v>
+      <c r="H30" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I30" s="97"/>
     </row>
@@ -3926,13 +3926,13 @@
         <v>22</v>
       </c>
       <c r="C31" s="92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D31" s="99" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" s="94" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F31" s="94">
         <v>5</v>
@@ -3940,8 +3940,8 @@
       <c r="G31" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H31" s="101" t="s">
-        <v>46</v>
+      <c r="H31" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I31" s="100"/>
     </row>
@@ -3951,13 +3951,13 @@
         <v>23</v>
       </c>
       <c r="C32" s="92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D32" s="93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E32" s="94" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F32" s="94">
         <v>5</v>
@@ -3965,8 +3965,8 @@
       <c r="G32" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="101" t="s">
-        <v>46</v>
+      <c r="H32" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I32" s="97"/>
     </row>
@@ -3976,13 +3976,13 @@
         <v>24</v>
       </c>
       <c r="C33" s="92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D33" s="99" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E33" s="94" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F33" s="94">
         <v>5</v>
@@ -3990,8 +3990,8 @@
       <c r="G33" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H33" s="101" t="s">
-        <v>46</v>
+      <c r="H33" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I33" s="100"/>
     </row>
@@ -4001,13 +4001,13 @@
         <v>25</v>
       </c>
       <c r="C34" s="92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D34" s="93" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E34" s="94" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F34" s="94">
         <v>5</v>
@@ -4016,13 +4016,13 @@
         <v>26</v>
       </c>
       <c r="H34" s="101" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I34" s="97"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:9">
       <c r="A35" s="103" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" s="103"/>
       <c r="C35" s="103"/>
@@ -4033,19 +4033,19 @@
       <c r="H35" s="103"/>
       <c r="I35" s="103"/>
     </row>
-    <row r="36" ht="18" customHeight="1" spans="1:9">
+    <row r="36" ht="25" customHeight="1" spans="1:9">
       <c r="A36" s="102"/>
       <c r="B36" s="91">
         <v>26</v>
       </c>
       <c r="C36" s="92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D36" s="93" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="94" t="s">
         <v>58</v>
-      </c>
-      <c r="E36" s="94" t="s">
-        <v>59</v>
       </c>
       <c r="F36" s="94">
         <v>6</v>
@@ -4054,23 +4054,23 @@
         <v>16</v>
       </c>
       <c r="H36" s="101" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I36" s="97"/>
     </row>
-    <row r="37" ht="18" customHeight="1" spans="1:9">
+    <row r="37" ht="23.05" spans="1:9">
       <c r="A37" s="104"/>
       <c r="B37" s="98">
         <v>27</v>
       </c>
       <c r="C37" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="99" t="s">
-        <v>61</v>
-      </c>
       <c r="E37" s="94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F37" s="94">
         <v>6</v>
@@ -4078,24 +4078,24 @@
       <c r="G37" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H37" s="101" t="s">
-        <v>46</v>
+      <c r="H37" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I37" s="100"/>
     </row>
-    <row r="38" ht="18" customHeight="1" spans="1:9">
+    <row r="38" ht="23.05" spans="1:9">
       <c r="A38" s="104"/>
       <c r="B38" s="91">
         <v>28</v>
       </c>
       <c r="C38" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D38" s="93" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E38" s="94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F38" s="94">
         <v>6</v>
@@ -4103,24 +4103,24 @@
       <c r="G38" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H38" s="101" t="s">
-        <v>46</v>
+      <c r="H38" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I38" s="97"/>
     </row>
-    <row r="39" ht="18" customHeight="1" spans="1:9">
+    <row r="39" ht="23.05" spans="1:9">
       <c r="A39" s="104"/>
       <c r="B39" s="98">
         <v>29</v>
       </c>
       <c r="C39" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D39" s="99" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E39" s="94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F39" s="94">
         <v>6</v>
@@ -4128,8 +4128,8 @@
       <c r="G39" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="101" t="s">
-        <v>46</v>
+      <c r="H39" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I39" s="100"/>
     </row>
@@ -4139,13 +4139,13 @@
         <v>30</v>
       </c>
       <c r="C40" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D40" s="93" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E40" s="94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F40" s="94">
         <v>6</v>
@@ -4153,14 +4153,14 @@
       <c r="G40" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H40" s="101" t="s">
-        <v>46</v>
+      <c r="H40" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I40" s="97"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:9">
       <c r="A41" s="105" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B41" s="105"/>
       <c r="C41" s="105"/>
@@ -4171,19 +4171,19 @@
       <c r="H41" s="105"/>
       <c r="I41" s="105"/>
     </row>
-    <row r="42" ht="18" customHeight="1" spans="1:9">
+    <row r="42" ht="23.05" spans="1:9">
       <c r="A42" s="104"/>
       <c r="B42" s="91">
         <v>31</v>
       </c>
       <c r="C42" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D42" s="93" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" s="94" t="s">
         <v>66</v>
-      </c>
-      <c r="E42" s="94" t="s">
-        <v>67</v>
       </c>
       <c r="F42" s="94">
         <v>7</v>
@@ -4191,24 +4191,24 @@
       <c r="G42" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="101" t="s">
-        <v>46</v>
+      <c r="H42" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I42" s="97"/>
     </row>
-    <row r="43" ht="18" customHeight="1" spans="1:9">
+    <row r="43" ht="23.05" spans="1:9">
       <c r="A43" s="104"/>
       <c r="B43" s="98">
         <v>32</v>
       </c>
       <c r="C43" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D43" s="99" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E43" s="94" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F43" s="94">
         <v>7</v>
@@ -4216,8 +4216,8 @@
       <c r="G43" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H43" s="101" t="s">
-        <v>46</v>
+      <c r="H43" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I43" s="100"/>
     </row>
@@ -4227,13 +4227,13 @@
         <v>33</v>
       </c>
       <c r="C44" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D44" s="93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E44" s="94" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F44" s="94">
         <v>7</v>
@@ -4241,8 +4241,8 @@
       <c r="G44" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H44" s="101" t="s">
-        <v>46</v>
+      <c r="H44" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I44" s="97"/>
     </row>
@@ -4252,13 +4252,13 @@
         <v>34</v>
       </c>
       <c r="C45" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D45" s="99" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E45" s="94" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F45" s="94">
         <v>7</v>
@@ -4266,8 +4266,8 @@
       <c r="G45" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="101" t="s">
-        <v>46</v>
+      <c r="H45" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I45" s="100"/>
     </row>
@@ -4277,13 +4277,13 @@
         <v>35</v>
       </c>
       <c r="C46" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D46" s="93" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E46" s="94" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F46" s="94">
         <v>7</v>
@@ -4291,14 +4291,14 @@
       <c r="G46" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H46" s="101" t="s">
-        <v>46</v>
+      <c r="H46" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I46" s="97"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:9">
       <c r="A47" s="105" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B47" s="105"/>
       <c r="C47" s="105"/>
@@ -4315,13 +4315,13 @@
         <v>36</v>
       </c>
       <c r="C48" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D48" s="93" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="94" t="s">
         <v>73</v>
-      </c>
-      <c r="E48" s="94" t="s">
-        <v>74</v>
       </c>
       <c r="F48" s="94">
         <v>8</v>
@@ -4329,8 +4329,8 @@
       <c r="G48" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="101" t="s">
-        <v>46</v>
+      <c r="H48" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I48" s="97"/>
     </row>
@@ -4340,13 +4340,13 @@
         <v>37</v>
       </c>
       <c r="C49" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D49" s="99" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E49" s="94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F49" s="94">
         <v>8</v>
@@ -4354,8 +4354,8 @@
       <c r="G49" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H49" s="101" t="s">
-        <v>46</v>
+      <c r="H49" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I49" s="100"/>
     </row>
@@ -4365,13 +4365,13 @@
         <v>38</v>
       </c>
       <c r="C50" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D50" s="93" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E50" s="94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F50" s="94">
         <v>8</v>
@@ -4379,8 +4379,8 @@
       <c r="G50" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H50" s="101" t="s">
-        <v>46</v>
+      <c r="H50" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I50" s="97"/>
     </row>
@@ -4390,13 +4390,13 @@
         <v>39</v>
       </c>
       <c r="C51" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D51" s="99" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E51" s="94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F51" s="94">
         <v>8</v>
@@ -4404,8 +4404,8 @@
       <c r="G51" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="101" t="s">
-        <v>46</v>
+      <c r="H51" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I51" s="100"/>
     </row>
@@ -4415,13 +4415,13 @@
         <v>40</v>
       </c>
       <c r="C52" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D52" s="93" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E52" s="94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F52" s="94">
         <v>8</v>
@@ -4429,14 +4429,14 @@
       <c r="G52" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H52" s="101" t="s">
-        <v>46</v>
+      <c r="H52" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I52" s="97"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:9">
       <c r="A53" s="105" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B53" s="105"/>
       <c r="C53" s="105"/>
@@ -4453,13 +4453,13 @@
         <v>41</v>
       </c>
       <c r="C54" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D54" s="93" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="94" t="s">
         <v>80</v>
-      </c>
-      <c r="E54" s="94" t="s">
-        <v>81</v>
       </c>
       <c r="F54" s="94">
         <v>9</v>
@@ -4468,7 +4468,7 @@
         <v>16</v>
       </c>
       <c r="H54" s="101" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I54" s="97"/>
     </row>
@@ -4478,13 +4478,13 @@
         <v>42</v>
       </c>
       <c r="C55" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D55" s="99" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E55" s="94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F55" s="94">
         <v>9</v>
@@ -4492,8 +4492,8 @@
       <c r="G55" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H55" s="101" t="s">
-        <v>46</v>
+      <c r="H55" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I55" s="100"/>
     </row>
@@ -4503,13 +4503,13 @@
         <v>43</v>
       </c>
       <c r="C56" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D56" s="93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E56" s="94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F56" s="94">
         <v>9</v>
@@ -4517,8 +4517,8 @@
       <c r="G56" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H56" s="101" t="s">
-        <v>46</v>
+      <c r="H56" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I56" s="97"/>
     </row>
@@ -4528,13 +4528,13 @@
         <v>44</v>
       </c>
       <c r="C57" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D57" s="99" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E57" s="94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F57" s="94">
         <v>9</v>
@@ -4542,8 +4542,8 @@
       <c r="G57" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H57" s="101" t="s">
-        <v>46</v>
+      <c r="H57" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I57" s="100"/>
     </row>
@@ -4553,13 +4553,13 @@
         <v>45</v>
       </c>
       <c r="C58" s="92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D58" s="93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E58" s="94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F58" s="94">
         <v>9</v>
@@ -4567,14 +4567,14 @@
       <c r="G58" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H58" s="101" t="s">
-        <v>46</v>
+      <c r="H58" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I58" s="97"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:9">
       <c r="A59" s="106" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B59" s="106"/>
       <c r="C59" s="106"/>
@@ -4591,13 +4591,13 @@
         <v>46</v>
       </c>
       <c r="C60" s="92" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="D60" s="93" t="s">
+      <c r="E60" s="94" t="s">
         <v>88</v>
-      </c>
-      <c r="E60" s="94" t="s">
-        <v>89</v>
       </c>
       <c r="F60" s="94">
         <v>10</v>
@@ -4606,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="H60" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I60" s="97"/>
     </row>
@@ -4616,13 +4616,13 @@
         <v>47</v>
       </c>
       <c r="C61" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D61" s="99" t="s">
         <v>90</v>
       </c>
       <c r="E61" s="94" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F61" s="94">
         <v>10</v>
@@ -4631,7 +4631,7 @@
         <v>19</v>
       </c>
       <c r="H61" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I61" s="100"/>
     </row>
@@ -4641,13 +4641,13 @@
         <v>48</v>
       </c>
       <c r="C62" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D62" s="93" t="s">
         <v>91</v>
       </c>
       <c r="E62" s="94" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F62" s="94">
         <v>10</v>
@@ -4656,7 +4656,7 @@
         <v>21</v>
       </c>
       <c r="H62" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I62" s="97"/>
     </row>
@@ -4666,13 +4666,13 @@
         <v>49</v>
       </c>
       <c r="C63" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D63" s="99" t="s">
         <v>92</v>
       </c>
       <c r="E63" s="94" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F63" s="94">
         <v>10</v>
@@ -4681,7 +4681,7 @@
         <v>24</v>
       </c>
       <c r="H63" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I63" s="100"/>
     </row>
@@ -4691,13 +4691,13 @@
         <v>50</v>
       </c>
       <c r="C64" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D64" s="93" t="s">
         <v>93</v>
       </c>
       <c r="E64" s="94" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F64" s="94">
         <v>10</v>
@@ -4706,7 +4706,7 @@
         <v>26</v>
       </c>
       <c r="H64" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I64" s="97"/>
     </row>
@@ -4729,7 +4729,7 @@
         <v>51</v>
       </c>
       <c r="C66" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D66" s="93" t="s">
         <v>95</v>
@@ -4744,7 +4744,7 @@
         <v>16</v>
       </c>
       <c r="H66" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I66" s="97"/>
     </row>
@@ -4754,7 +4754,7 @@
         <v>52</v>
       </c>
       <c r="C67" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D67" s="99" t="s">
         <v>97</v>
@@ -4769,7 +4769,7 @@
         <v>19</v>
       </c>
       <c r="H67" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I67" s="100"/>
     </row>
@@ -4779,7 +4779,7 @@
         <v>53</v>
       </c>
       <c r="C68" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D68" s="93" t="s">
         <v>98</v>
@@ -4794,7 +4794,7 @@
         <v>21</v>
       </c>
       <c r="H68" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I68" s="97"/>
     </row>
@@ -4804,7 +4804,7 @@
         <v>54</v>
       </c>
       <c r="C69" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D69" s="99" t="s">
         <v>99</v>
@@ -4819,7 +4819,7 @@
         <v>24</v>
       </c>
       <c r="H69" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I69" s="100"/>
     </row>
@@ -4829,7 +4829,7 @@
         <v>55</v>
       </c>
       <c r="C70" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D70" s="93" t="s">
         <v>100</v>
@@ -4844,7 +4844,7 @@
         <v>26</v>
       </c>
       <c r="H70" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I70" s="97"/>
     </row>
@@ -4867,7 +4867,7 @@
         <v>56</v>
       </c>
       <c r="C72" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D72" s="93" t="s">
         <v>102</v>
@@ -4882,7 +4882,7 @@
         <v>16</v>
       </c>
       <c r="H72" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I72" s="97"/>
     </row>
@@ -4892,7 +4892,7 @@
         <v>57</v>
       </c>
       <c r="C73" s="92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D73" s="99" t="s">
         <v>104</v>
@@ -4907,7 +4907,7 @@
         <v>19</v>
       </c>
       <c r="H73" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I73" s="100"/>
     </row>
@@ -4932,7 +4932,7 @@
         <v>21</v>
       </c>
       <c r="H74" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I74" s="97"/>
     </row>
@@ -4957,7 +4957,7 @@
         <v>24</v>
       </c>
       <c r="H75" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I75" s="100"/>
     </row>
@@ -4982,7 +4982,7 @@
         <v>26</v>
       </c>
       <c r="H76" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I76" s="97"/>
     </row>
@@ -5020,7 +5020,7 @@
         <v>16</v>
       </c>
       <c r="H78" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I78" s="97"/>
     </row>
@@ -5045,7 +5045,7 @@
         <v>19</v>
       </c>
       <c r="H79" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I79" s="100"/>
     </row>
@@ -5070,7 +5070,7 @@
         <v>21</v>
       </c>
       <c r="H80" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I80" s="97"/>
     </row>
@@ -5095,7 +5095,7 @@
         <v>24</v>
       </c>
       <c r="H81" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I81" s="100"/>
     </row>
@@ -5120,7 +5120,7 @@
         <v>26</v>
       </c>
       <c r="H82" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I82" s="97"/>
     </row>
@@ -5158,7 +5158,7 @@
         <v>16</v>
       </c>
       <c r="H84" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I84" s="97"/>
     </row>
@@ -5183,7 +5183,7 @@
         <v>19</v>
       </c>
       <c r="H85" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I85" s="100"/>
     </row>
@@ -5208,7 +5208,7 @@
         <v>21</v>
       </c>
       <c r="H86" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I86" s="97"/>
     </row>
@@ -5233,7 +5233,7 @@
         <v>24</v>
       </c>
       <c r="H87" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I87" s="100"/>
     </row>
@@ -5258,7 +5258,7 @@
         <v>26</v>
       </c>
       <c r="H88" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I88" s="97"/>
     </row>
@@ -5296,7 +5296,7 @@
         <v>16</v>
       </c>
       <c r="H90" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I90" s="97"/>
     </row>
@@ -5321,7 +5321,7 @@
         <v>19</v>
       </c>
       <c r="H91" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I91" s="100"/>
     </row>
@@ -5346,7 +5346,7 @@
         <v>21</v>
       </c>
       <c r="H92" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I92" s="97"/>
     </row>
@@ -5371,7 +5371,7 @@
         <v>24</v>
       </c>
       <c r="H93" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I93" s="100"/>
     </row>
@@ -5396,7 +5396,7 @@
         <v>26</v>
       </c>
       <c r="H94" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I94" s="97"/>
     </row>
@@ -5434,7 +5434,7 @@
         <v>16</v>
       </c>
       <c r="H96" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I96" s="97"/>
     </row>
@@ -5459,7 +5459,7 @@
         <v>19</v>
       </c>
       <c r="H97" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I97" s="100"/>
     </row>
@@ -5484,7 +5484,7 @@
         <v>21</v>
       </c>
       <c r="H98" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I98" s="97"/>
     </row>
@@ -5509,7 +5509,7 @@
         <v>24</v>
       </c>
       <c r="H99" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I99" s="100"/>
     </row>
@@ -5534,7 +5534,7 @@
         <v>26</v>
       </c>
       <c r="H100" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I100" s="97"/>
     </row>
@@ -5572,7 +5572,7 @@
         <v>16</v>
       </c>
       <c r="H102" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I102" s="97"/>
     </row>
@@ -5597,7 +5597,7 @@
         <v>19</v>
       </c>
       <c r="H103" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I103" s="100"/>
     </row>
@@ -5622,7 +5622,7 @@
         <v>21</v>
       </c>
       <c r="H104" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I104" s="97"/>
     </row>
@@ -5647,7 +5647,7 @@
         <v>24</v>
       </c>
       <c r="H105" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I105" s="100"/>
     </row>
@@ -5672,7 +5672,7 @@
         <v>26</v>
       </c>
       <c r="H106" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I106" s="97"/>
     </row>
@@ -5710,7 +5710,7 @@
         <v>16</v>
       </c>
       <c r="H108" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I108" s="97"/>
     </row>
@@ -5735,7 +5735,7 @@
         <v>19</v>
       </c>
       <c r="H109" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I109" s="100"/>
     </row>
@@ -5760,7 +5760,7 @@
         <v>21</v>
       </c>
       <c r="H110" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I110" s="97"/>
     </row>
@@ -5785,7 +5785,7 @@
         <v>24</v>
       </c>
       <c r="H111" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I111" s="100"/>
     </row>
@@ -5810,7 +5810,7 @@
         <v>26</v>
       </c>
       <c r="H112" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I112" s="97"/>
     </row>
@@ -5848,7 +5848,7 @@
         <v>16</v>
       </c>
       <c r="H114" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I114" s="97"/>
     </row>
@@ -5873,7 +5873,7 @@
         <v>19</v>
       </c>
       <c r="H115" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I115" s="100"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>21</v>
       </c>
       <c r="H116" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I116" s="97"/>
     </row>
@@ -5923,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="H117" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I117" s="100"/>
     </row>
@@ -5948,7 +5948,7 @@
         <v>26</v>
       </c>
       <c r="H118" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I118" s="97"/>
     </row>
@@ -5986,7 +5986,7 @@
         <v>16</v>
       </c>
       <c r="H120" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I120" s="97"/>
     </row>
@@ -6011,7 +6011,7 @@
         <v>19</v>
       </c>
       <c r="H121" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I121" s="100"/>
     </row>
@@ -6036,7 +6036,7 @@
         <v>21</v>
       </c>
       <c r="H122" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I122" s="97"/>
     </row>
@@ -6061,7 +6061,7 @@
         <v>24</v>
       </c>
       <c r="H123" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I123" s="100"/>
     </row>
@@ -6086,7 +6086,7 @@
         <v>26</v>
       </c>
       <c r="H124" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I124" s="97"/>
     </row>
@@ -6124,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="H126" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I126" s="97"/>
     </row>
@@ -6149,7 +6149,7 @@
         <v>19</v>
       </c>
       <c r="H127" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I127" s="100"/>
     </row>
@@ -6174,7 +6174,7 @@
         <v>21</v>
       </c>
       <c r="H128" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I128" s="97"/>
     </row>
@@ -6199,7 +6199,7 @@
         <v>24</v>
       </c>
       <c r="H129" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I129" s="100"/>
     </row>
@@ -6224,7 +6224,7 @@
         <v>26</v>
       </c>
       <c r="H130" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I130" s="97"/>
     </row>
@@ -6262,7 +6262,7 @@
         <v>16</v>
       </c>
       <c r="H132" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I132" s="97"/>
     </row>
@@ -6287,7 +6287,7 @@
         <v>19</v>
       </c>
       <c r="H133" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I133" s="100"/>
     </row>
@@ -6312,7 +6312,7 @@
         <v>21</v>
       </c>
       <c r="H134" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I134" s="97"/>
     </row>
@@ -6337,7 +6337,7 @@
         <v>24</v>
       </c>
       <c r="H135" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I135" s="100"/>
     </row>
@@ -6362,7 +6362,7 @@
         <v>26</v>
       </c>
       <c r="H136" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I136" s="97"/>
     </row>
@@ -6400,7 +6400,7 @@
         <v>16</v>
       </c>
       <c r="H138" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I138" s="97"/>
     </row>
@@ -6425,7 +6425,7 @@
         <v>19</v>
       </c>
       <c r="H139" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I139" s="100"/>
     </row>
@@ -6450,7 +6450,7 @@
         <v>21</v>
       </c>
       <c r="H140" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I140" s="97"/>
     </row>
@@ -6475,7 +6475,7 @@
         <v>24</v>
       </c>
       <c r="H141" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I141" s="100"/>
     </row>
@@ -6500,7 +6500,7 @@
         <v>26</v>
       </c>
       <c r="H142" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I142" s="97"/>
     </row>
@@ -6538,7 +6538,7 @@
         <v>16</v>
       </c>
       <c r="H144" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I144" s="97"/>
     </row>
@@ -6563,7 +6563,7 @@
         <v>19</v>
       </c>
       <c r="H145" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I145" s="100"/>
     </row>
@@ -6588,7 +6588,7 @@
         <v>21</v>
       </c>
       <c r="H146" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I146" s="97"/>
     </row>
@@ -6613,7 +6613,7 @@
         <v>24</v>
       </c>
       <c r="H147" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I147" s="100"/>
     </row>
@@ -6638,7 +6638,7 @@
         <v>26</v>
       </c>
       <c r="H148" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I148" s="97"/>
     </row>
@@ -6676,7 +6676,7 @@
         <v>16</v>
       </c>
       <c r="H150" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I150" s="97"/>
     </row>
@@ -6701,7 +6701,7 @@
         <v>19</v>
       </c>
       <c r="H151" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I151" s="100"/>
     </row>
@@ -6726,7 +6726,7 @@
         <v>21</v>
       </c>
       <c r="H152" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I152" s="97"/>
     </row>
@@ -6751,7 +6751,7 @@
         <v>24</v>
       </c>
       <c r="H153" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I153" s="100"/>
     </row>
@@ -6776,7 +6776,7 @@
         <v>26</v>
       </c>
       <c r="H154" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I154" s="97"/>
     </row>
@@ -6814,7 +6814,7 @@
         <v>16</v>
       </c>
       <c r="H156" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I156" s="97"/>
     </row>
@@ -6839,7 +6839,7 @@
         <v>19</v>
       </c>
       <c r="H157" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I157" s="100"/>
     </row>
@@ -6864,7 +6864,7 @@
         <v>21</v>
       </c>
       <c r="H158" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I158" s="97"/>
     </row>
@@ -6889,7 +6889,7 @@
         <v>24</v>
       </c>
       <c r="H159" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I159" s="100"/>
     </row>
@@ -6914,7 +6914,7 @@
         <v>26</v>
       </c>
       <c r="H160" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I160" s="97"/>
     </row>
@@ -6952,7 +6952,7 @@
         <v>16</v>
       </c>
       <c r="H162" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I162" s="97"/>
     </row>
@@ -6977,7 +6977,7 @@
         <v>19</v>
       </c>
       <c r="H163" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I163" s="100"/>
     </row>
@@ -7002,7 +7002,7 @@
         <v>21</v>
       </c>
       <c r="H164" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I164" s="97"/>
     </row>
@@ -7027,7 +7027,7 @@
         <v>24</v>
       </c>
       <c r="H165" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I165" s="100"/>
     </row>
@@ -7052,7 +7052,7 @@
         <v>26</v>
       </c>
       <c r="H166" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I166" s="97"/>
     </row>
@@ -7090,7 +7090,7 @@
         <v>16</v>
       </c>
       <c r="H168" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I168" s="97"/>
     </row>
@@ -7115,7 +7115,7 @@
         <v>19</v>
       </c>
       <c r="H169" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I169" s="100"/>
     </row>
@@ -7140,7 +7140,7 @@
         <v>21</v>
       </c>
       <c r="H170" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I170" s="97"/>
     </row>
@@ -7165,7 +7165,7 @@
         <v>24</v>
       </c>
       <c r="H171" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I171" s="100"/>
     </row>
@@ -7190,7 +7190,7 @@
         <v>26</v>
       </c>
       <c r="H172" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I172" s="97"/>
     </row>
@@ -7228,7 +7228,7 @@
         <v>16</v>
       </c>
       <c r="H174" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I174" s="97"/>
     </row>
@@ -7253,7 +7253,7 @@
         <v>19</v>
       </c>
       <c r="H175" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I175" s="100"/>
     </row>
@@ -7278,7 +7278,7 @@
         <v>21</v>
       </c>
       <c r="H176" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I176" s="97"/>
     </row>
@@ -7303,7 +7303,7 @@
         <v>24</v>
       </c>
       <c r="H177" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I177" s="100"/>
     </row>
@@ -7328,7 +7328,7 @@
         <v>26</v>
       </c>
       <c r="H178" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I178" s="97"/>
     </row>
@@ -7366,7 +7366,7 @@
         <v>16</v>
       </c>
       <c r="H180" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I180" s="97"/>
     </row>
@@ -7391,7 +7391,7 @@
         <v>19</v>
       </c>
       <c r="H181" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I181" s="100"/>
     </row>
@@ -7416,7 +7416,7 @@
         <v>21</v>
       </c>
       <c r="H182" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I182" s="97"/>
     </row>
@@ -7441,7 +7441,7 @@
         <v>24</v>
       </c>
       <c r="H183" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I183" s="100"/>
     </row>
@@ -7466,7 +7466,7 @@
         <v>26</v>
       </c>
       <c r="H184" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I184" s="97"/>
     </row>
@@ -7504,7 +7504,7 @@
         <v>16</v>
       </c>
       <c r="H186" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I186" s="97"/>
     </row>
@@ -7529,7 +7529,7 @@
         <v>19</v>
       </c>
       <c r="H187" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I187" s="100"/>
     </row>
@@ -7554,7 +7554,7 @@
         <v>21</v>
       </c>
       <c r="H188" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I188" s="97"/>
     </row>
@@ -7579,7 +7579,7 @@
         <v>24</v>
       </c>
       <c r="H189" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I189" s="100"/>
     </row>
@@ -7604,7 +7604,7 @@
         <v>26</v>
       </c>
       <c r="H190" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I190" s="97"/>
     </row>
@@ -7642,7 +7642,7 @@
         <v>16</v>
       </c>
       <c r="H192" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I192" s="97"/>
     </row>
@@ -7667,7 +7667,7 @@
         <v>19</v>
       </c>
       <c r="H193" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I193" s="100"/>
     </row>
@@ -7692,7 +7692,7 @@
         <v>21</v>
       </c>
       <c r="H194" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I194" s="97"/>
     </row>
@@ -7717,7 +7717,7 @@
         <v>24</v>
       </c>
       <c r="H195" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I195" s="100"/>
     </row>
@@ -7742,7 +7742,7 @@
         <v>26</v>
       </c>
       <c r="H196" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I196" s="97"/>
     </row>
@@ -7780,7 +7780,7 @@
         <v>16</v>
       </c>
       <c r="H198" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I198" s="97"/>
     </row>
@@ -7805,7 +7805,7 @@
         <v>19</v>
       </c>
       <c r="H199" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I199" s="100"/>
     </row>
@@ -7830,7 +7830,7 @@
         <v>21</v>
       </c>
       <c r="H200" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I200" s="97"/>
     </row>
@@ -7855,7 +7855,7 @@
         <v>24</v>
       </c>
       <c r="H201" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I201" s="100"/>
     </row>
@@ -7880,7 +7880,7 @@
         <v>26</v>
       </c>
       <c r="H202" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I202" s="97"/>
     </row>
@@ -7918,7 +7918,7 @@
         <v>16</v>
       </c>
       <c r="H204" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I204" s="97"/>
     </row>
@@ -7943,7 +7943,7 @@
         <v>19</v>
       </c>
       <c r="H205" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I205" s="100"/>
     </row>
@@ -7968,7 +7968,7 @@
         <v>21</v>
       </c>
       <c r="H206" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I206" s="97"/>
     </row>
@@ -7993,7 +7993,7 @@
         <v>24</v>
       </c>
       <c r="H207" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I207" s="100"/>
     </row>
@@ -8018,7 +8018,7 @@
         <v>26</v>
       </c>
       <c r="H208" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I208" s="97"/>
     </row>
@@ -8056,7 +8056,7 @@
         <v>16</v>
       </c>
       <c r="H210" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I210" s="97"/>
     </row>
@@ -8081,7 +8081,7 @@
         <v>19</v>
       </c>
       <c r="H211" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I211" s="100"/>
     </row>
@@ -8106,7 +8106,7 @@
         <v>21</v>
       </c>
       <c r="H212" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I212" s="97"/>
     </row>
@@ -8131,7 +8131,7 @@
         <v>24</v>
       </c>
       <c r="H213" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I213" s="100"/>
     </row>
@@ -8156,7 +8156,7 @@
         <v>26</v>
       </c>
       <c r="H214" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I214" s="97"/>
     </row>
@@ -8194,7 +8194,7 @@
         <v>16</v>
       </c>
       <c r="H216" s="101" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I216" s="97"/>
     </row>
@@ -8252,7 +8252,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Use dropdown options only" sqref="H5 H17 H23 H24 H25 H6:H7 H8:H11 H12:H16 H18:H22 H26:H217">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Use dropdown options only" sqref="H37 H38 H41 H47 H5:H36 H39:H40 H42:H46 H48:H52 H53:H54 H55:H58 H59:H217">
       <formula1>"✅ Done,🔄 In Progress,⏸ Paused,❌ Skipped,⬜ Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8323,7 +8323,7 @@
       <c r="D6" s="47"/>
       <c r="E6" s="48">
         <f>COUNTIF('📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="49">
@@ -8333,7 +8333,7 @@
       <c r="H6" s="49"/>
       <c r="I6" s="50">
         <f>COUNTIF('📚 Study Plan'!H:H,"⬜ Not Started")</f>
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="J6" s="50"/>
     </row>
@@ -8352,7 +8352,7 @@
     <row r="9" ht="35.1" spans="1:10">
       <c r="C9" s="52">
         <f>COUNTIF('📚 Study Plan'!H:H,"✅ Done")/176</f>
-        <v>0.0738636363636364</v>
+        <v>0.215909090909091</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="E13" s="55">
         <f>COUNTIFS('📚 Study Plan'!C:C,C13,'📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13" s="56">
         <f>COUNTIFS('📚 Study Plan'!C:C,C13,'📚 Study Plan'!H:H,"🔄 In Progress")</f>
@@ -8423,20 +8423,20 @@
       </c>
       <c r="I13" s="59">
         <f t="shared" ref="I13:I30" si="0">D13-E13-F13-G13-H13</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="59"/>
     </row>
     <row r="14" ht="24.2" spans="1:10">
       <c r="C14" s="60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="9">
         <v>7</v>
       </c>
       <c r="E14" s="61">
         <f>COUNTIFS('📚 Study Plan'!C:C,C14,'📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F14" s="62">
         <f>COUNTIFS('📚 Study Plan'!C:C,C14,'📚 Study Plan'!H:H,"🔄 In Progress")</f>
@@ -8448,24 +8448,24 @@
       </c>
       <c r="H14" s="64">
         <f>COUNTIFS('📚 Study Plan'!C:C,C14,'📚 Study Plan'!H:H,"❌ Skipped")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="65">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J14" s="65"/>
     </row>
     <row r="15" ht="36.3" spans="1:10">
       <c r="C15" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" s="5">
         <v>19</v>
       </c>
       <c r="E15" s="55">
         <f>COUNTIFS('📚 Study Plan'!C:C,C15,'📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F15" s="56">
         <f>COUNTIFS('📚 Study Plan'!C:C,C15,'📚 Study Plan'!H:H,"🔄 In Progress")</f>
@@ -8477,17 +8477,17 @@
       </c>
       <c r="H15" s="58">
         <f>COUNTIFS('📚 Study Plan'!C:C,C15,'📚 Study Plan'!H:H,"❌ Skipped")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="59">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J15" s="59"/>
     </row>
     <row r="16" ht="24.2" spans="1:10">
       <c r="C16" s="67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16" s="9">
         <v>12</v>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="E31" s="41">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F31" s="41">
         <f t="shared" si="1"/>
@@ -8942,11 +8942,11 @@
       </c>
       <c r="H31" s="41">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I31" s="41">
         <f t="shared" si="1"/>
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="J31" s="41"/>
     </row>
@@ -9058,7 +9058,7 @@
     <row r="4" spans="1:5">
       <c r="A4" s="7"/>
       <c r="B4" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="9">
         <v>7</v>
@@ -9073,7 +9073,7 @@
     <row r="5" ht="24.2" spans="1:5">
       <c r="A5" s="11"/>
       <c r="B5" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="5">
         <v>19</v>
@@ -9088,7 +9088,7 @@
     <row r="6" spans="1:5">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="9">
         <v>12</v>

--- a/01.Study Plan/02_aspnet_study_plan_v2.xlsx
+++ b/01.Study Plan/02_aspnet_study_plan_v2.xlsx
@@ -298,31 +298,31 @@
     <t>27-May-2026</t>
   </si>
   <si>
+    <t>Model Binding using FromForm in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>Model Binding using FromQuery in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>Model Binding Using FromRoute in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>Model Binding Using FromHeader in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   📅  Day 11  —  Thursday, 28 May 2026   ·   Topics 51 – 55</t>
+  </si>
+  <si>
+    <t>Model Binding Using FromBody in ASP.NET Core Web API</t>
+  </si>
+  <si>
+    <t>28-May-2026</t>
+  </si>
+  <si>
+    <t>Custom Model Binding in ASP.NET Core Web API</t>
+  </si>
+  <si>
     <t>⬜ Not Started</t>
-  </si>
-  <si>
-    <t>Model Binding using FromForm in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>Model Binding using FromQuery in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>Model Binding Using FromRoute in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>Model Binding Using FromHeader in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   📅  Day 11  —  Thursday, 28 May 2026   ·   Topics 51 – 55</t>
-  </si>
-  <si>
-    <t>Model Binding Using FromBody in ASP.NET Core Web API</t>
-  </si>
-  <si>
-    <t>28-May-2026</t>
-  </si>
-  <si>
-    <t>Custom Model Binding in ASP.NET Core Web API</t>
   </si>
   <si>
     <t>How to Apply Binding Attributes to Model Properties in ASP.NET Core Web API</t>
@@ -4605,8 +4605,8 @@
       <c r="G60" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H60" s="101" t="s">
-        <v>89</v>
+      <c r="H60" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I60" s="97"/>
     </row>
@@ -4619,7 +4619,7 @@
         <v>86</v>
       </c>
       <c r="D61" s="99" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E61" s="94" t="s">
         <v>88</v>
@@ -4630,8 +4630,8 @@
       <c r="G61" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="H61" s="101" t="s">
-        <v>89</v>
+      <c r="H61" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I61" s="100"/>
     </row>
@@ -4644,7 +4644,7 @@
         <v>86</v>
       </c>
       <c r="D62" s="93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E62" s="94" t="s">
         <v>88</v>
@@ -4655,8 +4655,8 @@
       <c r="G62" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H62" s="101" t="s">
-        <v>89</v>
+      <c r="H62" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I62" s="97"/>
     </row>
@@ -4669,7 +4669,7 @@
         <v>86</v>
       </c>
       <c r="D63" s="99" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E63" s="94" t="s">
         <v>88</v>
@@ -4680,8 +4680,8 @@
       <c r="G63" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H63" s="101" t="s">
-        <v>89</v>
+      <c r="H63" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I63" s="100"/>
     </row>
@@ -4694,7 +4694,7 @@
         <v>86</v>
       </c>
       <c r="D64" s="93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E64" s="94" t="s">
         <v>88</v>
@@ -4705,14 +4705,14 @@
       <c r="G64" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H64" s="101" t="s">
-        <v>89</v>
+      <c r="H64" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I64" s="97"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:9">
       <c r="A65" s="106" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B65" s="106"/>
       <c r="C65" s="106"/>
@@ -4732,10 +4732,10 @@
         <v>86</v>
       </c>
       <c r="D66" s="93" t="s">
+        <v>94</v>
+      </c>
+      <c r="E66" s="94" t="s">
         <v>95</v>
-      </c>
-      <c r="E66" s="94" t="s">
-        <v>96</v>
       </c>
       <c r="F66" s="94">
         <v>11</v>
@@ -4743,8 +4743,8 @@
       <c r="G66" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H66" s="101" t="s">
-        <v>89</v>
+      <c r="H66" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I66" s="97"/>
     </row>
@@ -4757,10 +4757,10 @@
         <v>86</v>
       </c>
       <c r="D67" s="99" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E67" s="94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F67" s="94">
         <v>11</v>
@@ -4769,7 +4769,7 @@
         <v>19</v>
       </c>
       <c r="H67" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I67" s="100"/>
     </row>
@@ -4785,7 +4785,7 @@
         <v>98</v>
       </c>
       <c r="E68" s="94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F68" s="94">
         <v>11</v>
@@ -4793,8 +4793,8 @@
       <c r="G68" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H68" s="101" t="s">
-        <v>89</v>
+      <c r="H68" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I68" s="97"/>
     </row>
@@ -4810,7 +4810,7 @@
         <v>99</v>
       </c>
       <c r="E69" s="94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F69" s="94">
         <v>11</v>
@@ -4818,8 +4818,8 @@
       <c r="G69" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="H69" s="101" t="s">
-        <v>89</v>
+      <c r="H69" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I69" s="100"/>
     </row>
@@ -4835,7 +4835,7 @@
         <v>100</v>
       </c>
       <c r="E70" s="94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F70" s="94">
         <v>11</v>
@@ -4843,8 +4843,8 @@
       <c r="G70" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="H70" s="101" t="s">
-        <v>89</v>
+      <c r="H70" s="96" t="s">
+        <v>17</v>
       </c>
       <c r="I70" s="97"/>
     </row>
@@ -4882,7 +4882,7 @@
         <v>16</v>
       </c>
       <c r="H72" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I72" s="97"/>
     </row>
@@ -4907,11 +4907,11 @@
         <v>19</v>
       </c>
       <c r="H73" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I73" s="100"/>
     </row>
-    <row r="74" ht="18" customHeight="1" spans="1:9">
+    <row r="74" ht="23.05" spans="1:9">
       <c r="A74" s="108"/>
       <c r="B74" s="91">
         <v>58</v>
@@ -4932,11 +4932,11 @@
         <v>21</v>
       </c>
       <c r="H74" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I74" s="97"/>
     </row>
-    <row r="75" ht="18" customHeight="1" spans="1:9">
+    <row r="75" ht="23.05" spans="1:9">
       <c r="A75" s="108"/>
       <c r="B75" s="98">
         <v>59</v>
@@ -4957,7 +4957,7 @@
         <v>24</v>
       </c>
       <c r="H75" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I75" s="100"/>
     </row>
@@ -4982,7 +4982,7 @@
         <v>26</v>
       </c>
       <c r="H76" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I76" s="97"/>
     </row>
@@ -5020,7 +5020,7 @@
         <v>16</v>
       </c>
       <c r="H78" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I78" s="97"/>
     </row>
@@ -5045,7 +5045,7 @@
         <v>19</v>
       </c>
       <c r="H79" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I79" s="100"/>
     </row>
@@ -5070,7 +5070,7 @@
         <v>21</v>
       </c>
       <c r="H80" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I80" s="97"/>
     </row>
@@ -5095,7 +5095,7 @@
         <v>24</v>
       </c>
       <c r="H81" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I81" s="100"/>
     </row>
@@ -5120,7 +5120,7 @@
         <v>26</v>
       </c>
       <c r="H82" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I82" s="97"/>
     </row>
@@ -5158,7 +5158,7 @@
         <v>16</v>
       </c>
       <c r="H84" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I84" s="97"/>
     </row>
@@ -5183,7 +5183,7 @@
         <v>19</v>
       </c>
       <c r="H85" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I85" s="100"/>
     </row>
@@ -5208,7 +5208,7 @@
         <v>21</v>
       </c>
       <c r="H86" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I86" s="97"/>
     </row>
@@ -5233,7 +5233,7 @@
         <v>24</v>
       </c>
       <c r="H87" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I87" s="100"/>
     </row>
@@ -5258,7 +5258,7 @@
         <v>26</v>
       </c>
       <c r="H88" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I88" s="97"/>
     </row>
@@ -5296,7 +5296,7 @@
         <v>16</v>
       </c>
       <c r="H90" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I90" s="97"/>
     </row>
@@ -5321,7 +5321,7 @@
         <v>19</v>
       </c>
       <c r="H91" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I91" s="100"/>
     </row>
@@ -5346,7 +5346,7 @@
         <v>21</v>
       </c>
       <c r="H92" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I92" s="97"/>
     </row>
@@ -5371,7 +5371,7 @@
         <v>24</v>
       </c>
       <c r="H93" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I93" s="100"/>
     </row>
@@ -5396,7 +5396,7 @@
         <v>26</v>
       </c>
       <c r="H94" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I94" s="97"/>
     </row>
@@ -5434,7 +5434,7 @@
         <v>16</v>
       </c>
       <c r="H96" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I96" s="97"/>
     </row>
@@ -5459,7 +5459,7 @@
         <v>19</v>
       </c>
       <c r="H97" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I97" s="100"/>
     </row>
@@ -5484,7 +5484,7 @@
         <v>21</v>
       </c>
       <c r="H98" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I98" s="97"/>
     </row>
@@ -5509,7 +5509,7 @@
         <v>24</v>
       </c>
       <c r="H99" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I99" s="100"/>
     </row>
@@ -5534,7 +5534,7 @@
         <v>26</v>
       </c>
       <c r="H100" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I100" s="97"/>
     </row>
@@ -5572,7 +5572,7 @@
         <v>16</v>
       </c>
       <c r="H102" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I102" s="97"/>
     </row>
@@ -5597,7 +5597,7 @@
         <v>19</v>
       </c>
       <c r="H103" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I103" s="100"/>
     </row>
@@ -5622,7 +5622,7 @@
         <v>21</v>
       </c>
       <c r="H104" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I104" s="97"/>
     </row>
@@ -5647,7 +5647,7 @@
         <v>24</v>
       </c>
       <c r="H105" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I105" s="100"/>
     </row>
@@ -5672,7 +5672,7 @@
         <v>26</v>
       </c>
       <c r="H106" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I106" s="97"/>
     </row>
@@ -5710,7 +5710,7 @@
         <v>16</v>
       </c>
       <c r="H108" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I108" s="97"/>
     </row>
@@ -5735,7 +5735,7 @@
         <v>19</v>
       </c>
       <c r="H109" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I109" s="100"/>
     </row>
@@ -5760,7 +5760,7 @@
         <v>21</v>
       </c>
       <c r="H110" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I110" s="97"/>
     </row>
@@ -5785,7 +5785,7 @@
         <v>24</v>
       </c>
       <c r="H111" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I111" s="100"/>
     </row>
@@ -5810,7 +5810,7 @@
         <v>26</v>
       </c>
       <c r="H112" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I112" s="97"/>
     </row>
@@ -5848,7 +5848,7 @@
         <v>16</v>
       </c>
       <c r="H114" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I114" s="97"/>
     </row>
@@ -5873,7 +5873,7 @@
         <v>19</v>
       </c>
       <c r="H115" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I115" s="100"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>21</v>
       </c>
       <c r="H116" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I116" s="97"/>
     </row>
@@ -5923,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="H117" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I117" s="100"/>
     </row>
@@ -5948,7 +5948,7 @@
         <v>26</v>
       </c>
       <c r="H118" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I118" s="97"/>
     </row>
@@ -5986,7 +5986,7 @@
         <v>16</v>
       </c>
       <c r="H120" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I120" s="97"/>
     </row>
@@ -6011,7 +6011,7 @@
         <v>19</v>
       </c>
       <c r="H121" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I121" s="100"/>
     </row>
@@ -6036,7 +6036,7 @@
         <v>21</v>
       </c>
       <c r="H122" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I122" s="97"/>
     </row>
@@ -6061,7 +6061,7 @@
         <v>24</v>
       </c>
       <c r="H123" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I123" s="100"/>
     </row>
@@ -6086,7 +6086,7 @@
         <v>26</v>
       </c>
       <c r="H124" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I124" s="97"/>
     </row>
@@ -6124,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="H126" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I126" s="97"/>
     </row>
@@ -6149,7 +6149,7 @@
         <v>19</v>
       </c>
       <c r="H127" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I127" s="100"/>
     </row>
@@ -6174,7 +6174,7 @@
         <v>21</v>
       </c>
       <c r="H128" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I128" s="97"/>
     </row>
@@ -6199,7 +6199,7 @@
         <v>24</v>
       </c>
       <c r="H129" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I129" s="100"/>
     </row>
@@ -6224,7 +6224,7 @@
         <v>26</v>
       </c>
       <c r="H130" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I130" s="97"/>
     </row>
@@ -6262,7 +6262,7 @@
         <v>16</v>
       </c>
       <c r="H132" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I132" s="97"/>
     </row>
@@ -6287,7 +6287,7 @@
         <v>19</v>
       </c>
       <c r="H133" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I133" s="100"/>
     </row>
@@ -6312,7 +6312,7 @@
         <v>21</v>
       </c>
       <c r="H134" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I134" s="97"/>
     </row>
@@ -6337,7 +6337,7 @@
         <v>24</v>
       </c>
       <c r="H135" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I135" s="100"/>
     </row>
@@ -6362,7 +6362,7 @@
         <v>26</v>
       </c>
       <c r="H136" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I136" s="97"/>
     </row>
@@ -6400,7 +6400,7 @@
         <v>16</v>
       </c>
       <c r="H138" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I138" s="97"/>
     </row>
@@ -6425,7 +6425,7 @@
         <v>19</v>
       </c>
       <c r="H139" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I139" s="100"/>
     </row>
@@ -6450,7 +6450,7 @@
         <v>21</v>
       </c>
       <c r="H140" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I140" s="97"/>
     </row>
@@ -6475,7 +6475,7 @@
         <v>24</v>
       </c>
       <c r="H141" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I141" s="100"/>
     </row>
@@ -6500,7 +6500,7 @@
         <v>26</v>
       </c>
       <c r="H142" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I142" s="97"/>
     </row>
@@ -6538,7 +6538,7 @@
         <v>16</v>
       </c>
       <c r="H144" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I144" s="97"/>
     </row>
@@ -6563,7 +6563,7 @@
         <v>19</v>
       </c>
       <c r="H145" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I145" s="100"/>
     </row>
@@ -6588,7 +6588,7 @@
         <v>21</v>
       </c>
       <c r="H146" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I146" s="97"/>
     </row>
@@ -6613,7 +6613,7 @@
         <v>24</v>
       </c>
       <c r="H147" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I147" s="100"/>
     </row>
@@ -6638,7 +6638,7 @@
         <v>26</v>
       </c>
       <c r="H148" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I148" s="97"/>
     </row>
@@ -6676,7 +6676,7 @@
         <v>16</v>
       </c>
       <c r="H150" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I150" s="97"/>
     </row>
@@ -6701,7 +6701,7 @@
         <v>19</v>
       </c>
       <c r="H151" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I151" s="100"/>
     </row>
@@ -6726,7 +6726,7 @@
         <v>21</v>
       </c>
       <c r="H152" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I152" s="97"/>
     </row>
@@ -6751,7 +6751,7 @@
         <v>24</v>
       </c>
       <c r="H153" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I153" s="100"/>
     </row>
@@ -6776,7 +6776,7 @@
         <v>26</v>
       </c>
       <c r="H154" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I154" s="97"/>
     </row>
@@ -6814,7 +6814,7 @@
         <v>16</v>
       </c>
       <c r="H156" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I156" s="97"/>
     </row>
@@ -6839,7 +6839,7 @@
         <v>19</v>
       </c>
       <c r="H157" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I157" s="100"/>
     </row>
@@ -6864,7 +6864,7 @@
         <v>21</v>
       </c>
       <c r="H158" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I158" s="97"/>
     </row>
@@ -6889,7 +6889,7 @@
         <v>24</v>
       </c>
       <c r="H159" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I159" s="100"/>
     </row>
@@ -6914,7 +6914,7 @@
         <v>26</v>
       </c>
       <c r="H160" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I160" s="97"/>
     </row>
@@ -6952,7 +6952,7 @@
         <v>16</v>
       </c>
       <c r="H162" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I162" s="97"/>
     </row>
@@ -6977,7 +6977,7 @@
         <v>19</v>
       </c>
       <c r="H163" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I163" s="100"/>
     </row>
@@ -7002,7 +7002,7 @@
         <v>21</v>
       </c>
       <c r="H164" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I164" s="97"/>
     </row>
@@ -7027,7 +7027,7 @@
         <v>24</v>
       </c>
       <c r="H165" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I165" s="100"/>
     </row>
@@ -7052,7 +7052,7 @@
         <v>26</v>
       </c>
       <c r="H166" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I166" s="97"/>
     </row>
@@ -7090,7 +7090,7 @@
         <v>16</v>
       </c>
       <c r="H168" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I168" s="97"/>
     </row>
@@ -7115,7 +7115,7 @@
         <v>19</v>
       </c>
       <c r="H169" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I169" s="100"/>
     </row>
@@ -7140,7 +7140,7 @@
         <v>21</v>
       </c>
       <c r="H170" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I170" s="97"/>
     </row>
@@ -7165,7 +7165,7 @@
         <v>24</v>
       </c>
       <c r="H171" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I171" s="100"/>
     </row>
@@ -7190,7 +7190,7 @@
         <v>26</v>
       </c>
       <c r="H172" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I172" s="97"/>
     </row>
@@ -7228,7 +7228,7 @@
         <v>16</v>
       </c>
       <c r="H174" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I174" s="97"/>
     </row>
@@ -7253,7 +7253,7 @@
         <v>19</v>
       </c>
       <c r="H175" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I175" s="100"/>
     </row>
@@ -7278,7 +7278,7 @@
         <v>21</v>
       </c>
       <c r="H176" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I176" s="97"/>
     </row>
@@ -7303,7 +7303,7 @@
         <v>24</v>
       </c>
       <c r="H177" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I177" s="100"/>
     </row>
@@ -7328,7 +7328,7 @@
         <v>26</v>
       </c>
       <c r="H178" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I178" s="97"/>
     </row>
@@ -7366,7 +7366,7 @@
         <v>16</v>
       </c>
       <c r="H180" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I180" s="97"/>
     </row>
@@ -7391,7 +7391,7 @@
         <v>19</v>
       </c>
       <c r="H181" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I181" s="100"/>
     </row>
@@ -7416,7 +7416,7 @@
         <v>21</v>
       </c>
       <c r="H182" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I182" s="97"/>
     </row>
@@ -7441,7 +7441,7 @@
         <v>24</v>
       </c>
       <c r="H183" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I183" s="100"/>
     </row>
@@ -7466,7 +7466,7 @@
         <v>26</v>
       </c>
       <c r="H184" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I184" s="97"/>
     </row>
@@ -7504,7 +7504,7 @@
         <v>16</v>
       </c>
       <c r="H186" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I186" s="97"/>
     </row>
@@ -7529,7 +7529,7 @@
         <v>19</v>
       </c>
       <c r="H187" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I187" s="100"/>
     </row>
@@ -7554,7 +7554,7 @@
         <v>21</v>
       </c>
       <c r="H188" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I188" s="97"/>
     </row>
@@ -7579,7 +7579,7 @@
         <v>24</v>
       </c>
       <c r="H189" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I189" s="100"/>
     </row>
@@ -7604,7 +7604,7 @@
         <v>26</v>
       </c>
       <c r="H190" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I190" s="97"/>
     </row>
@@ -7642,7 +7642,7 @@
         <v>16</v>
       </c>
       <c r="H192" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I192" s="97"/>
     </row>
@@ -7667,7 +7667,7 @@
         <v>19</v>
       </c>
       <c r="H193" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I193" s="100"/>
     </row>
@@ -7692,7 +7692,7 @@
         <v>21</v>
       </c>
       <c r="H194" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I194" s="97"/>
     </row>
@@ -7717,7 +7717,7 @@
         <v>24</v>
       </c>
       <c r="H195" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I195" s="100"/>
     </row>
@@ -7742,7 +7742,7 @@
         <v>26</v>
       </c>
       <c r="H196" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I196" s="97"/>
     </row>
@@ -7780,7 +7780,7 @@
         <v>16</v>
       </c>
       <c r="H198" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I198" s="97"/>
     </row>
@@ -7805,7 +7805,7 @@
         <v>19</v>
       </c>
       <c r="H199" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I199" s="100"/>
     </row>
@@ -7830,7 +7830,7 @@
         <v>21</v>
       </c>
       <c r="H200" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I200" s="97"/>
     </row>
@@ -7855,7 +7855,7 @@
         <v>24</v>
       </c>
       <c r="H201" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I201" s="100"/>
     </row>
@@ -7880,7 +7880,7 @@
         <v>26</v>
       </c>
       <c r="H202" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I202" s="97"/>
     </row>
@@ -7918,7 +7918,7 @@
         <v>16</v>
       </c>
       <c r="H204" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I204" s="97"/>
     </row>
@@ -7943,7 +7943,7 @@
         <v>19</v>
       </c>
       <c r="H205" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I205" s="100"/>
     </row>
@@ -7968,7 +7968,7 @@
         <v>21</v>
       </c>
       <c r="H206" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I206" s="97"/>
     </row>
@@ -7993,7 +7993,7 @@
         <v>24</v>
       </c>
       <c r="H207" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I207" s="100"/>
     </row>
@@ -8018,7 +8018,7 @@
         <v>26</v>
       </c>
       <c r="H208" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I208" s="97"/>
     </row>
@@ -8056,7 +8056,7 @@
         <v>16</v>
       </c>
       <c r="H210" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I210" s="97"/>
     </row>
@@ -8081,7 +8081,7 @@
         <v>19</v>
       </c>
       <c r="H211" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I211" s="100"/>
     </row>
@@ -8106,7 +8106,7 @@
         <v>21</v>
       </c>
       <c r="H212" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I212" s="97"/>
     </row>
@@ -8131,7 +8131,7 @@
         <v>24</v>
       </c>
       <c r="H213" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I213" s="100"/>
     </row>
@@ -8156,7 +8156,7 @@
         <v>26</v>
       </c>
       <c r="H214" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I214" s="97"/>
     </row>
@@ -8194,7 +8194,7 @@
         <v>16</v>
       </c>
       <c r="H216" s="101" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I216" s="97"/>
     </row>
@@ -8252,7 +8252,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Use dropdown options only" sqref="H37 H38 H41 H47 H5:H36 H39:H40 H42:H46 H48:H52 H53:H54 H55:H58 H59:H217">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Use dropdown options only" sqref="H68 H5:H67 H69:H70 H71:H217">
       <formula1>"✅ Done,🔄 In Progress,⏸ Paused,❌ Skipped,⬜ Not Started"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8323,7 +8323,7 @@
       <c r="D6" s="47"/>
       <c r="E6" s="48">
         <f>COUNTIF('📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="49">
@@ -8333,7 +8333,7 @@
       <c r="H6" s="49"/>
       <c r="I6" s="50">
         <f>COUNTIF('📚 Study Plan'!H:H,"⬜ Not Started")</f>
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="J6" s="50"/>
     </row>
@@ -8352,7 +8352,7 @@
     <row r="9" ht="35.1" spans="1:10">
       <c r="C9" s="52">
         <f>COUNTIF('📚 Study Plan'!H:H,"✅ Done")/176</f>
-        <v>0.215909090909091</v>
+        <v>0.267045454545455</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="E16" s="61">
         <f>COUNTIFS('📚 Study Plan'!C:C,C16,'📚 Study Plan'!H:H,"✅ Done")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F16" s="62">
         <f>COUNTIFS('📚 Study Plan'!C:C,C16,'📚 Study Plan'!H:H,"🔄 In Progress")</f>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="I16" s="65">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J16" s="65"/>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="E31" s="41">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F31" s="41">
         <f t="shared" si="1"/>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="I31" s="41">
         <f t="shared" si="1"/>
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="J31" s="41"/>
     </row>
